--- a/temp/diversos/Plastico.xlsx
+++ b/temp/diversos/Plastico.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1964" uniqueCount="499">
   <si>
     <t>ABS ALTO BRILHO PRETO</t>
   </si>
@@ -121,7 +121,7 @@
     <t>ALMA DO BOTÃO S500</t>
   </si>
   <si>
-    <t>ANEL ENCODER - ROUND MAGNET</t>
+    <t>ANEL ENCODER - IMÃ REDONDO (ROUND MAGNET)</t>
   </si>
   <si>
     <t>ARRUELA FIXAÇÃO 4MM VP4</t>
@@ -130,6 +130,9 @@
     <t>ARRUELA MAÇANETA PV</t>
   </si>
   <si>
+    <t>ATIVADOR MICRO SWICTH</t>
+  </si>
+  <si>
     <t>BASE BOBINA 12V / 24V / 110V</t>
   </si>
   <si>
@@ -487,9 +490,6 @@
     <t>PC</t>
   </si>
   <si>
-    <t>CARRETEL DA BOBINA 12V/24V/110V</t>
-  </si>
-  <si>
     <t>CARRETEL DA TRAVA ELETROMAGNÉTICA (MODELO NOVO)</t>
   </si>
   <si>
@@ -547,9 +547,6 @@
     <t>COROA DO MOVIMENTADOR BV/PIVO NYLON Ø 17MM</t>
   </si>
   <si>
-    <t>COROA DO MOVIMENTADOR BV/PIVO NYLON Ø 20MM</t>
-  </si>
-  <si>
     <t>DIFUSOR DE LUZ CERCA ELÉTRICA/NOBREAK</t>
   </si>
   <si>
@@ -766,6 +763,9 @@
     <t>FRISO PORTEIRO P10S / P20 / P200 - CINZA</t>
   </si>
   <si>
+    <t>FRISO PORTEIRO P10S / P20 / P200 - PRETO</t>
+  </si>
+  <si>
     <t>FUNDO ABS KIT SINALIZADOR PUXE/EMPURRE</t>
   </si>
   <si>
@@ -877,9 +877,15 @@
     <t>LINGUETA DE GANCHO P20 / P100 / P200 - CINZA</t>
   </si>
   <si>
+    <t>LINGUETA DE GANCHO P20 / P100 / P200 - VERDE</t>
+  </si>
+  <si>
     <t>LINGUETA DE GANCHO TDI100 / VP4 / VP7 - PRETO</t>
   </si>
   <si>
+    <t>MACAQUITO AGL MINI REVERSÍVEL</t>
+  </si>
+  <si>
     <t>MACAQUITO AL100R</t>
   </si>
   <si>
@@ -1187,6 +1193,9 @@
   </si>
   <si>
     <t>SUPORTE DA PLAQUETA TETRA AL100R</t>
+  </si>
+  <si>
+    <t>SUPORTE DE FIXAÇÃO DO LEITOR BIOMÉTRICO</t>
   </si>
   <si>
     <t>SUPORTE DE INSTALAÇÃO DO IMÃ DZ</t>
@@ -1600,7 +1609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J488"/>
+  <dimension ref="A1:J491"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" width="7.33203125" min="1" max="1"/>
@@ -1663,7 +1672,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>11362.435678</v>
+        <v>11185.651532</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -2143,7 +2152,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5349</v>
+        <v>4573</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0</v>
@@ -2207,7 +2216,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>11958</v>
+        <v>11868</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0</v>
@@ -2239,7 +2248,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3562</v>
+        <v>2162</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0</v>
@@ -2271,7 +2280,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2492</v>
+        <v>1766</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -2335,7 +2344,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>19726</v>
+        <v>19161</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0</v>
@@ -2495,7 +2504,7 @@
         <v>2</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>9402</v>
+        <v>7302</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
@@ -2591,7 +2600,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>16348</v>
+        <v>22460</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
@@ -2687,7 +2696,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>32553</v>
+        <v>27376</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
@@ -2704,7 +2713,7 @@
     </row>
     <row r="35" customHeight="1" ht="15" spans="1:10">
       <c r="A35" s="1" t="n">
-        <v>804084</v>
+        <v>804516</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>39</v>
@@ -2719,7 +2728,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>11498</v>
+        <v>3011</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
@@ -2736,7 +2745,7 @@
     </row>
     <row r="36" customHeight="1" ht="15" spans="1:10">
       <c r="A36" s="1" t="n">
-        <v>813503</v>
+        <v>804084</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>40</v>
@@ -2751,7 +2760,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>458</v>
+        <v>6121</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
@@ -2768,7 +2777,7 @@
     </row>
     <row r="37" customHeight="1" ht="15" spans="1:10">
       <c r="A37" s="1" t="n">
-        <v>813038</v>
+        <v>813503</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>41</v>
@@ -2783,7 +2792,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1959</v>
+        <v>458</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0</v>
@@ -2800,7 +2809,7 @@
     </row>
     <row r="38" customHeight="1" ht="15" spans="1:10">
       <c r="A38" s="1" t="n">
-        <v>813257</v>
+        <v>813038</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>42</v>
@@ -2815,7 +2824,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>3625</v>
+        <v>2778</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0</v>
@@ -2832,7 +2841,7 @@
     </row>
     <row r="39" customHeight="1" ht="15" spans="1:10">
       <c r="A39" s="1" t="n">
-        <v>804247</v>
+        <v>813257</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>43</v>
@@ -2847,7 +2856,7 @@
         <v>2</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>5843</v>
+        <v>3529</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
@@ -2864,7 +2873,7 @@
     </row>
     <row r="40" customHeight="1" ht="15" spans="1:10">
       <c r="A40" s="1" t="n">
-        <v>813152</v>
+        <v>804247</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>44</v>
@@ -2879,7 +2888,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1323</v>
+        <v>5335</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
@@ -2896,7 +2905,7 @@
     </row>
     <row r="41" customHeight="1" ht="15" spans="1:10">
       <c r="A41" s="1" t="n">
-        <v>804326</v>
+        <v>813152</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>45</v>
@@ -2911,7 +2920,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>3611</v>
+        <v>1323</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0</v>
@@ -2928,7 +2937,7 @@
     </row>
     <row r="42" customHeight="1" ht="15" spans="1:10">
       <c r="A42" s="1" t="n">
-        <v>804512</v>
+        <v>804326</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>46</v>
@@ -2943,7 +2952,7 @@
         <v>2</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>19555</v>
+        <v>3611</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>0</v>
@@ -2960,7 +2969,7 @@
     </row>
     <row r="43" customHeight="1" ht="15" spans="1:10">
       <c r="A43" s="1" t="n">
-        <v>804107</v>
+        <v>804512</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>47</v>
@@ -2975,7 +2984,7 @@
         <v>2</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>5521</v>
+        <v>19555</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>0</v>
@@ -2992,7 +3001,7 @@
     </row>
     <row r="44" customHeight="1" ht="15" spans="1:10">
       <c r="A44" s="1" t="n">
-        <v>804198</v>
+        <v>804107</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>48</v>
@@ -3007,7 +3016,7 @@
         <v>2</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>2048</v>
+        <v>5521</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>0</v>
@@ -3024,7 +3033,7 @@
     </row>
     <row r="45" customHeight="1" ht="15" spans="1:10">
       <c r="A45" s="1" t="n">
-        <v>804374</v>
+        <v>804198</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>49</v>
@@ -3039,7 +3048,7 @@
         <v>2</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>2228</v>
+        <v>2048</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>0</v>
@@ -3056,7 +3065,7 @@
     </row>
     <row r="46" customHeight="1" ht="15" spans="1:10">
       <c r="A46" s="1" t="n">
-        <v>804597</v>
+        <v>804374</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>50</v>
@@ -3071,7 +3080,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1492</v>
+        <v>2228</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>0</v>
@@ -3088,7 +3097,7 @@
     </row>
     <row r="47" customHeight="1" ht="15" spans="1:10">
       <c r="A47" s="1" t="n">
-        <v>804081</v>
+        <v>804597</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>51</v>
@@ -3103,7 +3112,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>1049</v>
+        <v>1492</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>0</v>
@@ -3120,7 +3129,7 @@
     </row>
     <row r="48" customHeight="1" ht="15" spans="1:10">
       <c r="A48" s="1" t="n">
-        <v>804166</v>
+        <v>804081</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>52</v>
@@ -3135,7 +3144,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>20586</v>
+        <v>1049</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -3152,7 +3161,7 @@
     </row>
     <row r="49" customHeight="1" ht="15" spans="1:10">
       <c r="A49" s="1" t="n">
-        <v>804165</v>
+        <v>804166</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>53</v>
@@ -3167,7 +3176,7 @@
         <v>2</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>52588</v>
+        <v>20586</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>0</v>
@@ -3184,7 +3193,7 @@
     </row>
     <row r="50" customHeight="1" ht="15" spans="1:10">
       <c r="A50" s="1" t="n">
-        <v>813151</v>
+        <v>804165</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>54</v>
@@ -3199,7 +3208,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>3365</v>
+        <v>52588</v>
       </c>
       <c r="G50" s="3" t="n">
         <v>0</v>
@@ -3216,7 +3225,7 @@
     </row>
     <row r="51" customHeight="1" ht="15" spans="1:10">
       <c r="A51" s="1" t="n">
-        <v>804542</v>
+        <v>813151</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>55</v>
@@ -3231,7 +3240,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>4678</v>
+        <v>3365</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>0</v>
@@ -3248,7 +3257,7 @@
     </row>
     <row r="52" customHeight="1" ht="15" spans="1:10">
       <c r="A52" s="1" t="n">
-        <v>804139</v>
+        <v>804542</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>56</v>
@@ -3263,7 +3272,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13305</v>
+        <v>3988</v>
       </c>
       <c r="G52" s="3" t="n">
         <v>0</v>
@@ -3280,7 +3289,7 @@
     </row>
     <row r="53" customHeight="1" ht="15" spans="1:10">
       <c r="A53" s="1" t="n">
-        <v>804140</v>
+        <v>804139</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>57</v>
@@ -3295,7 +3304,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1349</v>
+        <v>13305</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>0</v>
@@ -3312,7 +3321,7 @@
     </row>
     <row r="54" customHeight="1" ht="15" spans="1:10">
       <c r="A54" s="1" t="n">
-        <v>804006</v>
+        <v>804140</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>58</v>
@@ -3327,7 +3336,7 @@
         <v>2</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>4405</v>
+        <v>1349</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>0</v>
@@ -3344,7 +3353,7 @@
     </row>
     <row r="55" customHeight="1" ht="15" spans="1:10">
       <c r="A55" s="1" t="n">
-        <v>804013</v>
+        <v>804006</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>59</v>
@@ -3359,7 +3368,7 @@
         <v>2</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>2338</v>
+        <v>3175</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>0</v>
@@ -3376,7 +3385,7 @@
     </row>
     <row r="56" customHeight="1" ht="15" spans="1:10">
       <c r="A56" s="1" t="n">
-        <v>804194</v>
+        <v>804013</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>60</v>
@@ -3391,7 +3400,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>6850</v>
+        <v>2338</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>0</v>
@@ -3408,7 +3417,7 @@
     </row>
     <row r="57" customHeight="1" ht="15" spans="1:10">
       <c r="A57" s="1" t="n">
-        <v>804519</v>
+        <v>804194</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>61</v>
@@ -3423,7 +3432,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>117</v>
+        <v>6850</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0</v>
@@ -3440,7 +3449,7 @@
     </row>
     <row r="58" customHeight="1" ht="15" spans="1:10">
       <c r="A58" s="1" t="n">
-        <v>804138</v>
+        <v>804519</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>62</v>
@@ -3455,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>5437</v>
+        <v>117</v>
       </c>
       <c r="G58" s="3" t="n">
         <v>0</v>
@@ -3472,7 +3481,7 @@
     </row>
     <row r="59" customHeight="1" ht="15" spans="1:10">
       <c r="A59" s="1" t="n">
-        <v>804329</v>
+        <v>804138</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>63</v>
@@ -3487,7 +3496,7 @@
         <v>2</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>10638</v>
+        <v>5437</v>
       </c>
       <c r="G59" s="3" t="n">
         <v>0</v>
@@ -3504,7 +3513,7 @@
     </row>
     <row r="60" customHeight="1" ht="15" spans="1:10">
       <c r="A60" s="1" t="n">
-        <v>804005</v>
+        <v>804329</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>64</v>
@@ -3519,7 +3528,7 @@
         <v>2</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>11199</v>
+        <v>8066</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>0</v>
@@ -3536,7 +3545,7 @@
     </row>
     <row r="61" customHeight="1" ht="15" spans="1:10">
       <c r="A61" s="1" t="n">
-        <v>804011</v>
+        <v>804005</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>65</v>
@@ -3551,7 +3560,7 @@
         <v>2</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2027</v>
+        <v>11199</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>0</v>
@@ -3568,7 +3577,7 @@
     </row>
     <row r="62" customHeight="1" ht="15" spans="1:10">
       <c r="A62" s="1" t="n">
-        <v>804472</v>
+        <v>804011</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>66</v>
@@ -3583,7 +3592,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>1213</v>
+        <v>2027</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>0</v>
@@ -3600,7 +3609,7 @@
     </row>
     <row r="63" customHeight="1" ht="15" spans="1:10">
       <c r="A63" s="1" t="n">
-        <v>804459</v>
+        <v>804472</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>67</v>
@@ -3615,7 +3624,7 @@
         <v>2</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>1413</v>
+        <v>1213</v>
       </c>
       <c r="G63" s="3" t="n">
         <v>0</v>
@@ -3632,7 +3641,7 @@
     </row>
     <row r="64" customHeight="1" ht="15" spans="1:10">
       <c r="A64" s="1" t="n">
-        <v>804142</v>
+        <v>804459</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>68</v>
@@ -3647,7 +3656,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>6455</v>
+        <v>1413</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -3664,7 +3673,7 @@
     </row>
     <row r="65" customHeight="1" ht="15" spans="1:10">
       <c r="A65" s="1" t="n">
-        <v>804123</v>
+        <v>804142</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>69</v>
@@ -3679,7 +3688,7 @@
         <v>2</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>53172</v>
+        <v>6455</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>0</v>
@@ -3696,7 +3705,7 @@
     </row>
     <row r="66" customHeight="1" ht="15" spans="1:10">
       <c r="A66" s="1" t="n">
-        <v>804080</v>
+        <v>804123</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>70</v>
@@ -3711,7 +3720,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>102</v>
+        <v>53172</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>0</v>
@@ -3728,7 +3737,7 @@
     </row>
     <row r="67" customHeight="1" ht="15" spans="1:10">
       <c r="A67" s="1" t="n">
-        <v>804246</v>
+        <v>804080</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>71</v>
@@ -3743,7 +3752,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>4776</v>
+        <v>102</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -3760,7 +3769,7 @@
     </row>
     <row r="68" customHeight="1" ht="15" spans="1:10">
       <c r="A68" s="1" t="n">
-        <v>804261</v>
+        <v>804246</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>72</v>
@@ -3775,7 +3784,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>1436</v>
+        <v>4317</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0</v>
@@ -3792,7 +3801,7 @@
     </row>
     <row r="69" customHeight="1" ht="15" spans="1:10">
       <c r="A69" s="1" t="n">
-        <v>804540</v>
+        <v>804261</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>73</v>
@@ -3807,7 +3816,7 @@
         <v>2</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>4878</v>
+        <v>1436</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>0</v>
@@ -3824,7 +3833,7 @@
     </row>
     <row r="70" customHeight="1" ht="15" spans="1:10">
       <c r="A70" s="1" t="n">
-        <v>804541</v>
+        <v>804540</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>74</v>
@@ -3839,7 +3848,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>47</v>
+        <v>4188</v>
       </c>
       <c r="G70" s="3" t="n">
         <v>0</v>
@@ -3856,7 +3865,7 @@
     </row>
     <row r="71" customHeight="1" ht="15" spans="1:10">
       <c r="A71" s="1" t="n">
-        <v>804310</v>
+        <v>804541</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>75</v>
@@ -3871,7 +3880,7 @@
         <v>2</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2194</v>
+        <v>47</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>0</v>
@@ -3888,7 +3897,7 @@
     </row>
     <row r="72" customHeight="1" ht="15" spans="1:10">
       <c r="A72" s="1" t="n">
-        <v>804259</v>
+        <v>804310</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>76</v>
@@ -3903,7 +3912,7 @@
         <v>2</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>5996</v>
+        <v>2194</v>
       </c>
       <c r="G72" s="3" t="n">
         <v>0</v>
@@ -3920,7 +3929,7 @@
     </row>
     <row r="73" customHeight="1" ht="15" spans="1:10">
       <c r="A73" s="1" t="n">
-        <v>804276</v>
+        <v>804259</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>77</v>
@@ -3935,7 +3944,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>2325</v>
+        <v>5996</v>
       </c>
       <c r="G73" s="3" t="n">
         <v>0</v>
@@ -3952,7 +3961,7 @@
     </row>
     <row r="74" customHeight="1" ht="15" spans="1:10">
       <c r="A74" s="1" t="n">
-        <v>804324</v>
+        <v>804276</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>78</v>
@@ -3967,7 +3976,7 @@
         <v>2</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>11431</v>
+        <v>489</v>
       </c>
       <c r="G74" s="3" t="n">
         <v>0</v>
@@ -3984,7 +3993,7 @@
     </row>
     <row r="75" customHeight="1" ht="15" spans="1:10">
       <c r="A75" s="1" t="n">
-        <v>804118</v>
+        <v>804324</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>79</v>
@@ -3999,7 +4008,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>26637</v>
+        <v>11431</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>0</v>
@@ -4016,7 +4025,7 @@
     </row>
     <row r="76" customHeight="1" ht="15" spans="1:10">
       <c r="A76" s="1" t="n">
-        <v>804604</v>
+        <v>804118</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>80</v>
@@ -4031,7 +4040,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>200</v>
+        <v>16220</v>
       </c>
       <c r="G76" s="3" t="n">
         <v>0</v>
@@ -4048,7 +4057,7 @@
     </row>
     <row r="77" customHeight="1" ht="15" spans="1:10">
       <c r="A77" s="1" t="n">
-        <v>804595</v>
+        <v>804604</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>81</v>
@@ -4063,7 +4072,7 @@
         <v>2</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>2235</v>
+        <v>200</v>
       </c>
       <c r="G77" s="3" t="n">
         <v>0</v>
@@ -4080,7 +4089,7 @@
     </row>
     <row r="78" customHeight="1" ht="15" spans="1:10">
       <c r="A78" s="1" t="n">
-        <v>804224</v>
+        <v>804595</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>82</v>
@@ -4095,7 +4104,7 @@
         <v>2</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>2240</v>
+        <v>3891</v>
       </c>
       <c r="G78" s="3" t="n">
         <v>0</v>
@@ -4112,7 +4121,7 @@
     </row>
     <row r="79" customHeight="1" ht="15" spans="1:10">
       <c r="A79" s="1" t="n">
-        <v>804225</v>
+        <v>804224</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>83</v>
@@ -4127,7 +4136,7 @@
         <v>2</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>200</v>
+        <v>1235</v>
       </c>
       <c r="G79" s="3" t="n">
         <v>0</v>
@@ -4144,7 +4153,7 @@
     </row>
     <row r="80" customHeight="1" ht="15" spans="1:10">
       <c r="A80" s="1" t="n">
-        <v>804603</v>
+        <v>804225</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>84</v>
@@ -4159,7 +4168,7 @@
         <v>2</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2088</v>
+        <v>2160</v>
       </c>
       <c r="G80" s="3" t="n">
         <v>0</v>
@@ -4176,7 +4185,7 @@
     </row>
     <row r="81" customHeight="1" ht="15" spans="1:10">
       <c r="A81" s="1" t="n">
-        <v>804596</v>
+        <v>804603</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>85</v>
@@ -4191,7 +4200,7 @@
         <v>2</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>4657</v>
+        <v>2549</v>
       </c>
       <c r="G81" s="3" t="n">
         <v>0</v>
@@ -4208,7 +4217,7 @@
     </row>
     <row r="82" customHeight="1" ht="15" spans="1:10">
       <c r="A82" s="1" t="n">
-        <v>804226</v>
+        <v>804596</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>86</v>
@@ -4223,7 +4232,7 @@
         <v>2</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>4186</v>
+        <v>4284</v>
       </c>
       <c r="G82" s="3" t="n">
         <v>0</v>
@@ -4240,7 +4249,7 @@
     </row>
     <row r="83" customHeight="1" ht="15" spans="1:10">
       <c r="A83" s="1" t="n">
-        <v>804227</v>
+        <v>804226</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>87</v>
@@ -4255,7 +4264,7 @@
         <v>2</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>7564</v>
+        <v>5313</v>
       </c>
       <c r="G83" s="3" t="n">
         <v>0</v>
@@ -4272,7 +4281,7 @@
     </row>
     <row r="84" customHeight="1" ht="15" spans="1:10">
       <c r="A84" s="1" t="n">
-        <v>804111</v>
+        <v>804227</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>88</v>
@@ -4287,7 +4296,7 @@
         <v>2</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>5100</v>
+        <v>7564</v>
       </c>
       <c r="G84" s="3" t="n">
         <v>0</v>
@@ -4304,7 +4313,7 @@
     </row>
     <row r="85" customHeight="1" ht="15" spans="1:10">
       <c r="A85" s="1" t="n">
-        <v>804127</v>
+        <v>804111</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>89</v>
@@ -4319,7 +4328,7 @@
         <v>2</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="G85" s="3" t="n">
         <v>0</v>
@@ -4336,7 +4345,7 @@
     </row>
     <row r="86" customHeight="1" ht="15" spans="1:10">
       <c r="A86" s="1" t="n">
-        <v>804477</v>
+        <v>804127</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>90</v>
@@ -4351,7 +4360,7 @@
         <v>2</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>27529</v>
+        <v>4500</v>
       </c>
       <c r="G86" s="3" t="n">
         <v>0</v>
@@ -4368,7 +4377,7 @@
     </row>
     <row r="87" customHeight="1" ht="15" spans="1:10">
       <c r="A87" s="1" t="n">
-        <v>804357</v>
+        <v>804477</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>91</v>
@@ -4383,7 +4392,7 @@
         <v>2</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>73934</v>
+        <v>30368</v>
       </c>
       <c r="G87" s="3" t="n">
         <v>0</v>
@@ -4400,7 +4409,7 @@
     </row>
     <row r="88" customHeight="1" ht="15" spans="1:10">
       <c r="A88" s="1" t="n">
-        <v>804204</v>
+        <v>804357</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>92</v>
@@ -4415,7 +4424,7 @@
         <v>2</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>1273</v>
+        <v>92540</v>
       </c>
       <c r="G88" s="3" t="n">
         <v>0</v>
@@ -4432,7 +4441,7 @@
     </row>
     <row r="89" customHeight="1" ht="15" spans="1:10">
       <c r="A89" s="1" t="n">
-        <v>804205</v>
+        <v>804204</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>93</v>
@@ -4447,7 +4456,7 @@
         <v>2</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>5105</v>
+        <v>2745</v>
       </c>
       <c r="G89" s="3" t="n">
         <v>0</v>
@@ -4464,7 +4473,7 @@
     </row>
     <row r="90" customHeight="1" ht="15" spans="1:10">
       <c r="A90" s="1" t="n">
-        <v>804236</v>
+        <v>804205</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>94</v>
@@ -4479,7 +4488,7 @@
         <v>2</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>220</v>
+        <v>18351</v>
       </c>
       <c r="G90" s="3" t="n">
         <v>0</v>
@@ -4496,7 +4505,7 @@
     </row>
     <row r="91" customHeight="1" ht="15" spans="1:10">
       <c r="A91" s="1" t="n">
-        <v>804237</v>
+        <v>804236</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>95</v>
@@ -4511,7 +4520,7 @@
         <v>2</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>1068</v>
+        <v>220</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>0</v>
@@ -4528,7 +4537,7 @@
     </row>
     <row r="92" customHeight="1" ht="15" spans="1:10">
       <c r="A92" s="1" t="n">
-        <v>804353</v>
+        <v>804237</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>96</v>
@@ -4543,7 +4552,7 @@
         <v>2</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>25600</v>
+        <v>8680</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
@@ -4560,7 +4569,7 @@
     </row>
     <row r="93" customHeight="1" ht="15" spans="1:10">
       <c r="A93" s="1" t="n">
-        <v>804007</v>
+        <v>804353</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>97</v>
@@ -4575,7 +4584,7 @@
         <v>2</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>22081</v>
+        <v>21425</v>
       </c>
       <c r="G93" s="3" t="n">
         <v>0</v>
@@ -4592,7 +4601,7 @@
     </row>
     <row r="94" customHeight="1" ht="15" spans="1:10">
       <c r="A94" s="1" t="n">
-        <v>804316</v>
+        <v>804007</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>98</v>
@@ -4607,7 +4616,7 @@
         <v>2</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>12000</v>
+        <v>21131</v>
       </c>
       <c r="G94" s="3" t="n">
         <v>0</v>
@@ -4624,7 +4633,7 @@
     </row>
     <row r="95" customHeight="1" ht="15" spans="1:10">
       <c r="A95" s="1" t="n">
-        <v>804478</v>
+        <v>804316</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>99</v>
@@ -4639,7 +4648,7 @@
         <v>2</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>73028</v>
+        <v>24500</v>
       </c>
       <c r="G95" s="3" t="n">
         <v>0</v>
@@ -4656,7 +4665,7 @@
     </row>
     <row r="96" customHeight="1" ht="15" spans="1:10">
       <c r="A96" s="1" t="n">
-        <v>804358</v>
+        <v>804478</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>100</v>
@@ -4671,7 +4680,7 @@
         <v>2</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>3491</v>
+        <v>58857</v>
       </c>
       <c r="G96" s="3" t="n">
         <v>0</v>
@@ -4688,7 +4697,7 @@
     </row>
     <row r="97" customHeight="1" ht="15" spans="1:10">
       <c r="A97" s="1" t="n">
-        <v>804503</v>
+        <v>804358</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>101</v>
@@ -4703,7 +4712,7 @@
         <v>2</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>7604</v>
+        <v>852</v>
       </c>
       <c r="G97" s="3" t="n">
         <v>0</v>
@@ -4720,7 +4729,7 @@
     </row>
     <row r="98" customHeight="1" ht="15" spans="1:10">
       <c r="A98" s="1" t="n">
-        <v>804029</v>
+        <v>804503</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>102</v>
@@ -4735,7 +4744,7 @@
         <v>2</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>1975</v>
+        <v>7604</v>
       </c>
       <c r="G98" s="3" t="n">
         <v>0</v>
@@ -4752,7 +4761,7 @@
     </row>
     <row r="99" customHeight="1" ht="15" spans="1:10">
       <c r="A99" s="1" t="n">
-        <v>804412</v>
+        <v>804029</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>103</v>
@@ -4767,7 +4776,7 @@
         <v>2</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>60400</v>
+        <v>28214</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>0</v>
@@ -4784,7 +4793,7 @@
     </row>
     <row r="100" customHeight="1" ht="15" spans="1:10">
       <c r="A100" s="1" t="n">
-        <v>804030</v>
+        <v>804412</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>104</v>
@@ -4799,7 +4808,7 @@
         <v>2</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>37191</v>
+        <v>59800</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -4816,7 +4825,7 @@
     </row>
     <row r="101" customHeight="1" ht="15" spans="1:10">
       <c r="A101" s="1" t="n">
-        <v>804033</v>
+        <v>804030</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>105</v>
@@ -4831,7 +4840,7 @@
         <v>2</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>11697</v>
+        <v>35763</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
@@ -4848,7 +4857,7 @@
     </row>
     <row r="102" customHeight="1" ht="15" spans="1:10">
       <c r="A102" s="1" t="n">
-        <v>804113</v>
+        <v>804033</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>106</v>
@@ -4863,7 +4872,7 @@
         <v>2</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>13762</v>
+        <v>11697</v>
       </c>
       <c r="G102" s="3" t="n">
         <v>0</v>
@@ -4880,7 +4889,7 @@
     </row>
     <row r="103" customHeight="1" ht="15" spans="1:10">
       <c r="A103" s="1" t="n">
-        <v>804001</v>
+        <v>804113</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>107</v>
@@ -4895,7 +4904,7 @@
         <v>2</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>1838</v>
+        <v>12615</v>
       </c>
       <c r="G103" s="3" t="n">
         <v>0</v>
@@ -4912,7 +4921,7 @@
     </row>
     <row r="104" customHeight="1" ht="15" spans="1:10">
       <c r="A104" s="1" t="n">
-        <v>813172</v>
+        <v>804001</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>108</v>
@@ -4927,7 +4936,7 @@
         <v>2</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>61360</v>
+        <v>1838</v>
       </c>
       <c r="G104" s="3" t="n">
         <v>0</v>
@@ -4944,7 +4953,7 @@
     </row>
     <row r="105" customHeight="1" ht="15" spans="1:10">
       <c r="A105" s="1" t="n">
-        <v>813410</v>
+        <v>813172</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>109</v>
@@ -4959,7 +4968,7 @@
         <v>2</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>26248</v>
+        <v>61360</v>
       </c>
       <c r="G105" s="3" t="n">
         <v>0</v>
@@ -4976,7 +4985,7 @@
     </row>
     <row r="106" customHeight="1" ht="15" spans="1:10">
       <c r="A106" s="1" t="n">
-        <v>813043</v>
+        <v>813410</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>110</v>
@@ -4991,7 +5000,7 @@
         <v>2</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>74035</v>
+        <v>25558</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>0</v>
@@ -5008,7 +5017,7 @@
     </row>
     <row r="107" customHeight="1" ht="15" spans="1:10">
       <c r="A107" s="1" t="n">
-        <v>813235</v>
+        <v>813043</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>111</v>
@@ -5023,7 +5032,7 @@
         <v>2</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>65172</v>
+        <v>74035</v>
       </c>
       <c r="G107" s="3" t="n">
         <v>0</v>
@@ -5040,7 +5049,7 @@
     </row>
     <row r="108" customHeight="1" ht="15" spans="1:10">
       <c r="A108" s="1" t="n">
-        <v>813006</v>
+        <v>813235</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>112</v>
@@ -5055,7 +5064,7 @@
         <v>2</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>9541</v>
+        <v>63037</v>
       </c>
       <c r="G108" s="3" t="n">
         <v>0</v>
@@ -5072,7 +5081,7 @@
     </row>
     <row r="109" customHeight="1" ht="15" spans="1:10">
       <c r="A109" s="1" t="n">
-        <v>804550</v>
+        <v>813006</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>113</v>
@@ -5087,7 +5096,7 @@
         <v>2</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>17074</v>
+        <v>9541</v>
       </c>
       <c r="G109" s="3" t="n">
         <v>0</v>
@@ -5104,7 +5113,7 @@
     </row>
     <row r="110" customHeight="1" ht="15" spans="1:10">
       <c r="A110" s="1" t="n">
-        <v>804615</v>
+        <v>804550</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>114</v>
@@ -5119,7 +5128,7 @@
         <v>2</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>31051</v>
+        <v>14574</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -5136,7 +5145,7 @@
     </row>
     <row r="111" customHeight="1" ht="15" spans="1:10">
       <c r="A111" s="1" t="n">
-        <v>402036</v>
+        <v>804615</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>115</v>
@@ -5151,7 +5160,7 @@
         <v>2</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>47408</v>
+        <v>42748</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -5168,7 +5177,7 @@
     </row>
     <row r="112" customHeight="1" ht="15" spans="1:10">
       <c r="A112" s="1" t="n">
-        <v>804564</v>
+        <v>402036</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>116</v>
@@ -5183,7 +5192,7 @@
         <v>2</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>1936</v>
+        <v>47408</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -5200,7 +5209,7 @@
     </row>
     <row r="113" customHeight="1" ht="15" spans="1:10">
       <c r="A113" s="1" t="n">
-        <v>804560</v>
+        <v>804564</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>117</v>
@@ -5215,7 +5224,7 @@
         <v>2</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>1013</v>
+        <v>1936</v>
       </c>
       <c r="G113" s="3" t="n">
         <v>0</v>
@@ -5232,7 +5241,7 @@
     </row>
     <row r="114" customHeight="1" ht="15" spans="1:10">
       <c r="A114" s="1" t="n">
-        <v>813260</v>
+        <v>804560</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>118</v>
@@ -5247,7 +5256,7 @@
         <v>2</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>8849</v>
+        <v>1013</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>0</v>
@@ -5264,7 +5273,7 @@
     </row>
     <row r="115" customHeight="1" ht="15" spans="1:10">
       <c r="A115" s="1" t="n">
-        <v>813515</v>
+        <v>813260</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>119</v>
@@ -5279,7 +5288,7 @@
         <v>2</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>13858</v>
+        <v>8849</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -5296,7 +5305,7 @@
     </row>
     <row r="116" customHeight="1" ht="15" spans="1:10">
       <c r="A116" s="1" t="n">
-        <v>804245</v>
+        <v>813515</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>120</v>
@@ -5311,7 +5320,7 @@
         <v>2</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>7100</v>
+        <v>13858</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
@@ -5328,7 +5337,7 @@
     </row>
     <row r="117" customHeight="1" ht="15" spans="1:10">
       <c r="A117" s="1" t="n">
-        <v>804575</v>
+        <v>804245</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>121</v>
@@ -5343,7 +5352,7 @@
         <v>2</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>4633</v>
+        <v>7100</v>
       </c>
       <c r="G117" s="3" t="n">
         <v>0</v>
@@ -5360,7 +5369,7 @@
     </row>
     <row r="118" customHeight="1" ht="15" spans="1:10">
       <c r="A118" s="1" t="n">
-        <v>804573</v>
+        <v>804575</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>122</v>
@@ -5375,7 +5384,7 @@
         <v>2</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>6291</v>
+        <v>5083</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0</v>
@@ -5392,7 +5401,7 @@
     </row>
     <row r="119" customHeight="1" ht="15" spans="1:10">
       <c r="A119" s="1" t="n">
-        <v>804574</v>
+        <v>804573</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>123</v>
@@ -5407,7 +5416,7 @@
         <v>2</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>3505</v>
+        <v>6291</v>
       </c>
       <c r="G119" s="3" t="n">
         <v>0</v>
@@ -5424,7 +5433,7 @@
     </row>
     <row r="120" customHeight="1" ht="15" spans="1:10">
       <c r="A120" s="1" t="n">
-        <v>804572</v>
+        <v>804574</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>124</v>
@@ -5439,7 +5448,7 @@
         <v>2</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>8528</v>
+        <v>3505</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>0</v>
@@ -5456,7 +5465,7 @@
     </row>
     <row r="121" customHeight="1" ht="15" spans="1:10">
       <c r="A121" s="1" t="n">
-        <v>804203</v>
+        <v>804572</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>125</v>
@@ -5471,7 +5480,7 @@
         <v>2</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>4090</v>
+        <v>8528</v>
       </c>
       <c r="G121" s="3" t="n">
         <v>0</v>
@@ -5488,7 +5497,7 @@
     </row>
     <row r="122" customHeight="1" ht="15" spans="1:10">
       <c r="A122" s="1" t="n">
-        <v>804202</v>
+        <v>804203</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>126</v>
@@ -5503,7 +5512,7 @@
         <v>2</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>9620</v>
+        <v>4090</v>
       </c>
       <c r="G122" s="3" t="n">
         <v>0</v>
@@ -5520,7 +5529,7 @@
     </row>
     <row r="123" customHeight="1" ht="15" spans="1:10">
       <c r="A123" s="1" t="n">
-        <v>804405</v>
+        <v>804202</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>127</v>
@@ -5535,7 +5544,7 @@
         <v>2</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>5978</v>
+        <v>8570</v>
       </c>
       <c r="G123" s="3" t="n">
         <v>0</v>
@@ -5552,7 +5561,7 @@
     </row>
     <row r="124" customHeight="1" ht="15" spans="1:10">
       <c r="A124" s="1" t="n">
-        <v>804281</v>
+        <v>804405</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>128</v>
@@ -5567,7 +5576,7 @@
         <v>2</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>1368</v>
+        <v>5978</v>
       </c>
       <c r="G124" s="3" t="n">
         <v>0</v>
@@ -5584,7 +5593,7 @@
     </row>
     <row r="125" customHeight="1" ht="15" spans="1:10">
       <c r="A125" s="1" t="n">
-        <v>804280</v>
+        <v>804281</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>129</v>
@@ -5599,7 +5608,7 @@
         <v>2</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>7620</v>
+        <v>1368</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
@@ -5616,7 +5625,7 @@
     </row>
     <row r="126" customHeight="1" ht="15" spans="1:10">
       <c r="A126" s="1" t="n">
-        <v>804124</v>
+        <v>804280</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>130</v>
@@ -5631,7 +5640,7 @@
         <v>2</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>6445</v>
+        <v>7620</v>
       </c>
       <c r="G126" s="3" t="n">
         <v>0</v>
@@ -5648,7 +5657,7 @@
     </row>
     <row r="127" customHeight="1" ht="15" spans="1:10">
       <c r="A127" s="1" t="n">
-        <v>804120</v>
+        <v>804124</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>131</v>
@@ -5663,7 +5672,7 @@
         <v>2</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>34798</v>
+        <v>6445</v>
       </c>
       <c r="G127" s="3" t="n">
         <v>0</v>
@@ -5680,7 +5689,7 @@
     </row>
     <row r="128" customHeight="1" ht="15" spans="1:10">
       <c r="A128" s="1" t="n">
-        <v>804493</v>
+        <v>804120</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>132</v>
@@ -5695,7 +5704,7 @@
         <v>2</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>540</v>
+        <v>34798</v>
       </c>
       <c r="G128" s="3" t="n">
         <v>0</v>
@@ -5712,7 +5721,7 @@
     </row>
     <row r="129" customHeight="1" ht="15" spans="1:10">
       <c r="A129" s="1" t="n">
-        <v>804492</v>
+        <v>804493</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>133</v>
@@ -5727,7 +5736,7 @@
         <v>2</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>10984</v>
+        <v>540</v>
       </c>
       <c r="G129" s="3" t="n">
         <v>0</v>
@@ -5744,7 +5753,7 @@
     </row>
     <row r="130" customHeight="1" ht="15" spans="1:10">
       <c r="A130" s="1" t="n">
-        <v>804121</v>
+        <v>804492</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>134</v>
@@ -5759,7 +5768,7 @@
         <v>2</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>9120</v>
+        <v>10984</v>
       </c>
       <c r="G130" s="3" t="n">
         <v>0</v>
@@ -5776,7 +5785,7 @@
     </row>
     <row r="131" customHeight="1" ht="15" spans="1:10">
       <c r="A131" s="1" t="n">
-        <v>804335</v>
+        <v>804121</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>135</v>
@@ -5791,7 +5800,7 @@
         <v>2</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>3486</v>
+        <v>9120</v>
       </c>
       <c r="G131" s="3" t="n">
         <v>0</v>
@@ -5808,7 +5817,7 @@
     </row>
     <row r="132" customHeight="1" ht="15" spans="1:10">
       <c r="A132" s="1" t="n">
-        <v>804215</v>
+        <v>804335</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>136</v>
@@ -5823,7 +5832,7 @@
         <v>2</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>340</v>
+        <v>3486</v>
       </c>
       <c r="G132" s="3" t="n">
         <v>0</v>
@@ -5840,7 +5849,7 @@
     </row>
     <row r="133" customHeight="1" ht="15" spans="1:10">
       <c r="A133" s="1" t="n">
-        <v>804491</v>
+        <v>804215</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>137</v>
@@ -5855,7 +5864,7 @@
         <v>2</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>1600</v>
+        <v>340</v>
       </c>
       <c r="G133" s="3" t="n">
         <v>0</v>
@@ -5872,7 +5881,7 @@
     </row>
     <row r="134" customHeight="1" ht="15" spans="1:10">
       <c r="A134" s="1" t="n">
-        <v>804211</v>
+        <v>804491</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>138</v>
@@ -5887,7 +5896,7 @@
         <v>2</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>1219</v>
+        <v>1600</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -5904,7 +5913,7 @@
     </row>
     <row r="135" customHeight="1" ht="15" spans="1:10">
       <c r="A135" s="1" t="n">
-        <v>804260</v>
+        <v>804211</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>139</v>
@@ -5919,7 +5928,7 @@
         <v>2</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>1349</v>
+        <v>1219</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>0</v>
@@ -5936,7 +5945,7 @@
     </row>
     <row r="136" customHeight="1" ht="15" spans="1:10">
       <c r="A136" s="1" t="n">
-        <v>804448</v>
+        <v>804260</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>140</v>
@@ -5951,7 +5960,7 @@
         <v>2</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>3000</v>
+        <v>1349</v>
       </c>
       <c r="G136" s="3" t="n">
         <v>0</v>
@@ -5968,7 +5977,7 @@
     </row>
     <row r="137" customHeight="1" ht="15" spans="1:10">
       <c r="A137" s="1" t="n">
-        <v>804104</v>
+        <v>804448</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>141</v>
@@ -5983,7 +5992,7 @@
         <v>2</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>1273</v>
+        <v>3000</v>
       </c>
       <c r="G137" s="3" t="n">
         <v>0</v>
@@ -6000,7 +6009,7 @@
     </row>
     <row r="138" customHeight="1" ht="15" spans="1:10">
       <c r="A138" s="1" t="n">
-        <v>804430</v>
+        <v>804104</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>142</v>
@@ -6015,7 +6024,7 @@
         <v>2</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>41478</v>
+        <v>1273</v>
       </c>
       <c r="G138" s="3" t="n">
         <v>0</v>
@@ -6032,7 +6041,7 @@
     </row>
     <row r="139" customHeight="1" ht="15" spans="1:10">
       <c r="A139" s="1" t="n">
-        <v>804282</v>
+        <v>804430</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>143</v>
@@ -6047,7 +6056,7 @@
         <v>2</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>5062</v>
+        <v>41478</v>
       </c>
       <c r="G139" s="3" t="n">
         <v>0</v>
@@ -6064,7 +6073,7 @@
     </row>
     <row r="140" customHeight="1" ht="15" spans="1:10">
       <c r="A140" s="1" t="n">
-        <v>804555</v>
+        <v>804282</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>144</v>
@@ -6079,7 +6088,7 @@
         <v>2</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>3228</v>
+        <v>5062</v>
       </c>
       <c r="G140" s="3" t="n">
         <v>0</v>
@@ -6096,7 +6105,7 @@
     </row>
     <row r="141" customHeight="1" ht="15" spans="1:10">
       <c r="A141" s="1" t="n">
-        <v>804220</v>
+        <v>804555</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>145</v>
@@ -6111,7 +6120,7 @@
         <v>2</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>775</v>
+        <v>3228</v>
       </c>
       <c r="G141" s="3" t="n">
         <v>0</v>
@@ -6128,7 +6137,7 @@
     </row>
     <row r="142" customHeight="1" ht="15" spans="1:10">
       <c r="A142" s="1" t="n">
-        <v>804601</v>
+        <v>804220</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>146</v>
@@ -6143,7 +6152,7 @@
         <v>2</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>662</v>
+        <v>775</v>
       </c>
       <c r="G142" s="3" t="n">
         <v>0</v>
@@ -6160,7 +6169,7 @@
     </row>
     <row r="143" customHeight="1" ht="15" spans="1:10">
       <c r="A143" s="1" t="n">
-        <v>804221</v>
+        <v>804601</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>147</v>
@@ -6175,7 +6184,7 @@
         <v>2</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>1096</v>
+        <v>662</v>
       </c>
       <c r="G143" s="3" t="n">
         <v>0</v>
@@ -6192,7 +6201,7 @@
     </row>
     <row r="144" customHeight="1" ht="15" spans="1:10">
       <c r="A144" s="1" t="n">
-        <v>804593</v>
+        <v>804221</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>148</v>
@@ -6207,7 +6216,7 @@
         <v>2</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>2101</v>
+        <v>1096</v>
       </c>
       <c r="G144" s="3" t="n">
         <v>0</v>
@@ -6224,7 +6233,7 @@
     </row>
     <row r="145" customHeight="1" ht="15" spans="1:10">
       <c r="A145" s="1" t="n">
-        <v>804355</v>
+        <v>804593</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>149</v>
@@ -6239,7 +6248,7 @@
         <v>2</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>1391</v>
+        <v>2101</v>
       </c>
       <c r="G145" s="3" t="n">
         <v>0</v>
@@ -6256,7 +6265,7 @@
     </row>
     <row r="146" customHeight="1" ht="15" spans="1:10">
       <c r="A146" s="1" t="n">
-        <v>804611</v>
+        <v>804355</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>150</v>
@@ -6271,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>649</v>
+        <v>1391</v>
       </c>
       <c r="G146" s="3" t="n">
         <v>0</v>
@@ -6288,7 +6297,7 @@
     </row>
     <row r="147" customHeight="1" ht="15" spans="1:10">
       <c r="A147" s="1" t="n">
-        <v>804063</v>
+        <v>804611</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>151</v>
@@ -6303,7 +6312,7 @@
         <v>2</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>2329</v>
+        <v>649</v>
       </c>
       <c r="G147" s="3" t="n">
         <v>0</v>
@@ -6320,7 +6329,7 @@
     </row>
     <row r="148" customHeight="1" ht="15" spans="1:10">
       <c r="A148" s="1" t="n">
-        <v>804268</v>
+        <v>804063</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>152</v>
@@ -6335,7 +6344,7 @@
         <v>2</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>1191</v>
+        <v>2329</v>
       </c>
       <c r="G148" s="3" t="n">
         <v>0</v>
@@ -6352,7 +6361,7 @@
     </row>
     <row r="149" customHeight="1" ht="15" spans="1:10">
       <c r="A149" s="1" t="n">
-        <v>804265</v>
+        <v>804268</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>153</v>
@@ -6367,7 +6376,7 @@
         <v>2</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>1291</v>
+        <v>1191</v>
       </c>
       <c r="G149" s="3" t="n">
         <v>0</v>
@@ -6384,7 +6393,7 @@
     </row>
     <row r="150" customHeight="1" ht="15" spans="1:10">
       <c r="A150" s="1" t="n">
-        <v>804354</v>
+        <v>804265</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>154</v>
@@ -6399,7 +6408,7 @@
         <v>2</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>1286</v>
+        <v>1291</v>
       </c>
       <c r="G150" s="3" t="n">
         <v>0</v>
@@ -6416,7 +6425,7 @@
     </row>
     <row r="151" customHeight="1" ht="15" spans="1:10">
       <c r="A151" s="1" t="n">
-        <v>804610</v>
+        <v>804354</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>155</v>
@@ -6431,7 +6440,7 @@
         <v>2</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>565</v>
+        <v>1286</v>
       </c>
       <c r="G151" s="3" t="n">
         <v>0</v>
@@ -6448,13 +6457,13 @@
     </row>
     <row r="152" customHeight="1" ht="15" spans="1:10">
       <c r="A152" s="1" t="n">
-        <v>804348</v>
+        <v>804610</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>6</v>
@@ -6463,7 +6472,7 @@
         <v>2</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>5192</v>
+        <v>565</v>
       </c>
       <c r="G152" s="3" t="n">
         <v>0</v>
@@ -6480,14 +6489,14 @@
     </row>
     <row r="153" customHeight="1" ht="15" spans="1:10">
       <c r="A153" s="1" t="n">
-        <v>804086</v>
+        <v>804348</v>
       </c>
       <c r="B153" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C153" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C153" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="D153" s="2" t="s">
         <v>6</v>
       </c>
@@ -6495,7 +6504,7 @@
         <v>2</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>16033</v>
+        <v>5192</v>
       </c>
       <c r="G153" s="3" t="n">
         <v>0</v>
@@ -6559,7 +6568,7 @@
         <v>2</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>8167</v>
+        <v>4717</v>
       </c>
       <c r="G155" s="3" t="n">
         <v>0</v>
@@ -6614,7 +6623,7 @@
         <v>162</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>6</v>
@@ -6646,7 +6655,7 @@
         <v>163</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>6</v>
@@ -6678,7 +6687,7 @@
         <v>164</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>6</v>
@@ -6719,7 +6728,7 @@
         <v>2</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>25361</v>
+        <v>20550</v>
       </c>
       <c r="G160" s="3" t="n">
         <v>0</v>
@@ -6911,7 +6920,7 @@
         <v>2</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>8400</v>
+        <v>7200</v>
       </c>
       <c r="G166" s="3" t="n">
         <v>0</v>
@@ -6943,7 +6952,7 @@
         <v>2</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>13674</v>
+        <v>10204</v>
       </c>
       <c r="G167" s="3" t="n">
         <v>0</v>
@@ -6975,7 +6984,7 @@
         <v>2</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>55271</v>
+        <v>50772</v>
       </c>
       <c r="G168" s="3" t="n">
         <v>0</v>
@@ -7120,7 +7129,7 @@
     </row>
     <row r="173" customHeight="1" ht="15" spans="1:10">
       <c r="A173" s="1" t="n">
-        <v>804508</v>
+        <v>804444</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>178</v>
@@ -7135,7 +7144,7 @@
         <v>2</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>500</v>
+        <v>7761</v>
       </c>
       <c r="G173" s="3" t="n">
         <v>0</v>
@@ -7152,7 +7161,7 @@
     </row>
     <row r="174" customHeight="1" ht="15" spans="1:10">
       <c r="A174" s="1" t="n">
-        <v>804444</v>
+        <v>804422</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>179</v>
@@ -7167,7 +7176,7 @@
         <v>2</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>7761</v>
+        <v>7993</v>
       </c>
       <c r="G174" s="3" t="n">
         <v>0</v>
@@ -7184,7 +7193,7 @@
     </row>
     <row r="175" customHeight="1" ht="15" spans="1:10">
       <c r="A175" s="1" t="n">
-        <v>804422</v>
+        <v>813529</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>180</v>
@@ -7199,7 +7208,7 @@
         <v>2</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>8063</v>
+        <v>5835</v>
       </c>
       <c r="G175" s="3" t="n">
         <v>0</v>
@@ -7216,7 +7225,7 @@
     </row>
     <row r="176" customHeight="1" ht="15" spans="1:10">
       <c r="A176" s="1" t="n">
-        <v>813529</v>
+        <v>813528</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>181</v>
@@ -7231,7 +7240,7 @@
         <v>2</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>5835</v>
+        <v>7229</v>
       </c>
       <c r="G176" s="3" t="n">
         <v>0</v>
@@ -7248,7 +7257,7 @@
     </row>
     <row r="177" customHeight="1" ht="15" spans="1:10">
       <c r="A177" s="1" t="n">
-        <v>813528</v>
+        <v>804064</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>182</v>
@@ -7263,7 +7272,7 @@
         <v>2</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>7229</v>
+        <v>11755</v>
       </c>
       <c r="G177" s="3" t="n">
         <v>0</v>
@@ -7280,7 +7289,7 @@
     </row>
     <row r="178" customHeight="1" ht="15" spans="1:10">
       <c r="A178" s="1" t="n">
-        <v>804064</v>
+        <v>813041</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>183</v>
@@ -7295,7 +7304,7 @@
         <v>2</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>11900</v>
+        <v>9328</v>
       </c>
       <c r="G178" s="3" t="n">
         <v>0</v>
@@ -7312,7 +7321,7 @@
     </row>
     <row r="179" customHeight="1" ht="15" spans="1:10">
       <c r="A179" s="1" t="n">
-        <v>813041</v>
+        <v>804098</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>184</v>
@@ -7327,7 +7336,7 @@
         <v>2</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>9328</v>
+        <v>232252</v>
       </c>
       <c r="G179" s="3" t="n">
         <v>0</v>
@@ -7344,7 +7353,7 @@
     </row>
     <row r="180" customHeight="1" ht="15" spans="1:10">
       <c r="A180" s="1" t="n">
-        <v>804098</v>
+        <v>804099</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>185</v>
@@ -7359,7 +7368,7 @@
         <v>2</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>232252</v>
+        <v>130730</v>
       </c>
       <c r="G180" s="3" t="n">
         <v>0</v>
@@ -7376,7 +7385,7 @@
     </row>
     <row r="181" customHeight="1" ht="15" spans="1:10">
       <c r="A181" s="1" t="n">
-        <v>804099</v>
+        <v>804212</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>186</v>
@@ -7391,7 +7400,7 @@
         <v>2</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>78273</v>
+        <v>574</v>
       </c>
       <c r="G181" s="3" t="n">
         <v>0</v>
@@ -7408,7 +7417,7 @@
     </row>
     <row r="182" customHeight="1" ht="15" spans="1:10">
       <c r="A182" s="1" t="n">
-        <v>804212</v>
+        <v>813539</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>187</v>
@@ -7423,7 +7432,7 @@
         <v>2</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>574</v>
+        <v>1190</v>
       </c>
       <c r="G182" s="3" t="n">
         <v>0</v>
@@ -7440,7 +7449,7 @@
     </row>
     <row r="183" customHeight="1" ht="15" spans="1:10">
       <c r="A183" s="1" t="n">
-        <v>813539</v>
+        <v>813094</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>188</v>
@@ -7455,7 +7464,7 @@
         <v>2</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>1190</v>
+        <v>1600</v>
       </c>
       <c r="G183" s="3" t="n">
         <v>0</v>
@@ -7472,7 +7481,7 @@
     </row>
     <row r="184" customHeight="1" ht="15" spans="1:10">
       <c r="A184" s="1" t="n">
-        <v>813094</v>
+        <v>813289</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>189</v>
@@ -7487,7 +7496,7 @@
         <v>2</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>1600</v>
+        <v>4800</v>
       </c>
       <c r="G184" s="3" t="n">
         <v>0</v>
@@ -7504,7 +7513,7 @@
     </row>
     <row r="185" customHeight="1" ht="15" spans="1:10">
       <c r="A185" s="1" t="n">
-        <v>813289</v>
+        <v>813506</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>190</v>
@@ -7519,7 +7528,7 @@
         <v>2</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>5269</v>
+        <v>850</v>
       </c>
       <c r="G185" s="3" t="n">
         <v>0</v>
@@ -7536,7 +7545,7 @@
     </row>
     <row r="186" customHeight="1" ht="15" spans="1:10">
       <c r="A186" s="1" t="n">
-        <v>813506</v>
+        <v>804231</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>191</v>
@@ -7551,7 +7560,7 @@
         <v>2</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>850</v>
+        <v>7387</v>
       </c>
       <c r="G186" s="3" t="n">
         <v>0</v>
@@ -7568,7 +7577,7 @@
     </row>
     <row r="187" customHeight="1" ht="15" spans="1:10">
       <c r="A187" s="1" t="n">
-        <v>804231</v>
+        <v>813247</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>192</v>
@@ -7583,7 +7592,7 @@
         <v>2</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>7629</v>
+        <v>1080</v>
       </c>
       <c r="G187" s="3" t="n">
         <v>0</v>
@@ -7600,7 +7609,7 @@
     </row>
     <row r="188" customHeight="1" ht="15" spans="1:10">
       <c r="A188" s="1" t="n">
-        <v>813247</v>
+        <v>813295</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>193</v>
@@ -7615,7 +7624,7 @@
         <v>2</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>1110</v>
+        <v>3646</v>
       </c>
       <c r="G188" s="3" t="n">
         <v>0</v>
@@ -7632,7 +7641,7 @@
     </row>
     <row r="189" customHeight="1" ht="15" spans="1:10">
       <c r="A189" s="1" t="n">
-        <v>813295</v>
+        <v>804586</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>194</v>
@@ -7647,7 +7656,7 @@
         <v>2</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>3646</v>
+        <v>1527</v>
       </c>
       <c r="G189" s="3" t="n">
         <v>0</v>
@@ -7664,7 +7673,7 @@
     </row>
     <row r="190" customHeight="1" ht="15" spans="1:10">
       <c r="A190" s="1" t="n">
-        <v>804586</v>
+        <v>804536</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>195</v>
@@ -7679,7 +7688,7 @@
         <v>2</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>1527</v>
+        <v>416</v>
       </c>
       <c r="G190" s="3" t="n">
         <v>0</v>
@@ -7696,7 +7705,7 @@
     </row>
     <row r="191" customHeight="1" ht="15" spans="1:10">
       <c r="A191" s="1" t="n">
-        <v>804536</v>
+        <v>804356</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>196</v>
@@ -7711,7 +7720,7 @@
         <v>2</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>416</v>
+        <v>23711</v>
       </c>
       <c r="G191" s="3" t="n">
         <v>0</v>
@@ -7728,22 +7737,22 @@
     </row>
     <row r="192" customHeight="1" ht="15" spans="1:10">
       <c r="A192" s="1" t="n">
-        <v>804356</v>
+        <v>105070</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>197</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>2</v>
+        <v>198</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>23711</v>
+        <v>26.7</v>
       </c>
       <c r="G192" s="3" t="n">
         <v>0</v>
@@ -7760,22 +7769,22 @@
     </row>
     <row r="193" customHeight="1" ht="15" spans="1:10">
       <c r="A193" s="1" t="n">
-        <v>105070</v>
+        <v>804105</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>199</v>
+        <v>2</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>26.7</v>
+        <v>1326</v>
       </c>
       <c r="G193" s="3" t="n">
         <v>0</v>
@@ -7792,7 +7801,7 @@
     </row>
     <row r="194" customHeight="1" ht="15" spans="1:10">
       <c r="A194" s="1" t="n">
-        <v>804105</v>
+        <v>804253</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>200</v>
@@ -7807,7 +7816,7 @@
         <v>2</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>1326</v>
+        <v>1737</v>
       </c>
       <c r="G194" s="3" t="n">
         <v>0</v>
@@ -7824,7 +7833,7 @@
     </row>
     <row r="195" customHeight="1" ht="15" spans="1:10">
       <c r="A195" s="1" t="n">
-        <v>804253</v>
+        <v>804254</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>201</v>
@@ -7839,7 +7848,7 @@
         <v>2</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>1737</v>
+        <v>392</v>
       </c>
       <c r="G195" s="3" t="n">
         <v>0</v>
@@ -7856,7 +7865,7 @@
     </row>
     <row r="196" customHeight="1" ht="15" spans="1:10">
       <c r="A196" s="1" t="n">
-        <v>804254</v>
+        <v>804441</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>202</v>
@@ -7871,7 +7880,7 @@
         <v>2</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>392</v>
+        <v>4219</v>
       </c>
       <c r="G196" s="3" t="n">
         <v>0</v>
@@ -7888,7 +7897,7 @@
     </row>
     <row r="197" customHeight="1" ht="15" spans="1:10">
       <c r="A197" s="1" t="n">
-        <v>804441</v>
+        <v>804157</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>203</v>
@@ -7903,7 +7912,7 @@
         <v>2</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>4219</v>
+        <v>762</v>
       </c>
       <c r="G197" s="3" t="n">
         <v>0</v>
@@ -7920,7 +7929,7 @@
     </row>
     <row r="198" customHeight="1" ht="15" spans="1:10">
       <c r="A198" s="1" t="n">
-        <v>804157</v>
+        <v>804018</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>204</v>
@@ -7935,7 +7944,7 @@
         <v>2</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>3837</v>
+        <v>1946</v>
       </c>
       <c r="G198" s="3" t="n">
         <v>0</v>
@@ -7952,7 +7961,7 @@
     </row>
     <row r="199" customHeight="1" ht="15" spans="1:10">
       <c r="A199" s="1" t="n">
-        <v>804018</v>
+        <v>804017</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>205</v>
@@ -7967,7 +7976,7 @@
         <v>2</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>1946</v>
+        <v>2403</v>
       </c>
       <c r="G199" s="3" t="n">
         <v>0</v>
@@ -7984,7 +7993,7 @@
     </row>
     <row r="200" customHeight="1" ht="15" spans="1:10">
       <c r="A200" s="1" t="n">
-        <v>804017</v>
+        <v>804144</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>206</v>
@@ -7999,7 +8008,7 @@
         <v>2</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>2403</v>
+        <v>825</v>
       </c>
       <c r="G200" s="3" t="n">
         <v>0</v>
@@ -8016,7 +8025,7 @@
     </row>
     <row r="201" customHeight="1" ht="15" spans="1:10">
       <c r="A201" s="1" t="n">
-        <v>804144</v>
+        <v>804252</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>207</v>
@@ -8031,7 +8040,7 @@
         <v>2</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>825</v>
+        <v>858</v>
       </c>
       <c r="G201" s="3" t="n">
         <v>0</v>
@@ -8048,7 +8057,7 @@
     </row>
     <row r="202" customHeight="1" ht="15" spans="1:10">
       <c r="A202" s="1" t="n">
-        <v>804252</v>
+        <v>804251</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>208</v>
@@ -8063,7 +8072,7 @@
         <v>2</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>858</v>
+        <v>2907</v>
       </c>
       <c r="G202" s="3" t="n">
         <v>0</v>
@@ -8080,7 +8089,7 @@
     </row>
     <row r="203" customHeight="1" ht="15" spans="1:10">
       <c r="A203" s="1" t="n">
-        <v>804251</v>
+        <v>804004</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>209</v>
@@ -8095,7 +8104,7 @@
         <v>2</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>2907</v>
+        <v>2408</v>
       </c>
       <c r="G203" s="3" t="n">
         <v>0</v>
@@ -8112,7 +8121,7 @@
     </row>
     <row r="204" customHeight="1" ht="15" spans="1:10">
       <c r="A204" s="1" t="n">
-        <v>804004</v>
+        <v>804042</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>210</v>
@@ -8127,7 +8136,7 @@
         <v>2</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>2408</v>
+        <v>5376</v>
       </c>
       <c r="G204" s="3" t="n">
         <v>0</v>
@@ -8144,7 +8153,7 @@
     </row>
     <row r="205" customHeight="1" ht="15" spans="1:10">
       <c r="A205" s="1" t="n">
-        <v>804042</v>
+        <v>804182</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>211</v>
@@ -8159,7 +8168,7 @@
         <v>2</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>2968</v>
+        <v>9434</v>
       </c>
       <c r="G205" s="3" t="n">
         <v>0</v>
@@ -8176,7 +8185,7 @@
     </row>
     <row r="206" customHeight="1" ht="15" spans="1:10">
       <c r="A206" s="1" t="n">
-        <v>804182</v>
+        <v>804488</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>212</v>
@@ -8191,7 +8200,7 @@
         <v>2</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>3013</v>
+        <v>7581</v>
       </c>
       <c r="G206" s="3" t="n">
         <v>0</v>
@@ -8208,7 +8217,7 @@
     </row>
     <row r="207" customHeight="1" ht="15" spans="1:10">
       <c r="A207" s="1" t="n">
-        <v>804488</v>
+        <v>804489</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>213</v>
@@ -8223,7 +8232,7 @@
         <v>2</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>5040</v>
+        <v>2566</v>
       </c>
       <c r="G207" s="3" t="n">
         <v>0</v>
@@ -8240,7 +8249,7 @@
     </row>
     <row r="208" customHeight="1" ht="15" spans="1:10">
       <c r="A208" s="1" t="n">
-        <v>804489</v>
+        <v>804311</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>214</v>
@@ -8255,7 +8264,7 @@
         <v>2</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>2566</v>
+        <v>1015</v>
       </c>
       <c r="G208" s="3" t="n">
         <v>0</v>
@@ -8272,7 +8281,7 @@
     </row>
     <row r="209" customHeight="1" ht="15" spans="1:10">
       <c r="A209" s="1" t="n">
-        <v>804311</v>
+        <v>804184</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>215</v>
@@ -8287,7 +8296,7 @@
         <v>2</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>1015</v>
+        <v>2645</v>
       </c>
       <c r="G209" s="3" t="n">
         <v>0</v>
@@ -8304,7 +8313,7 @@
     </row>
     <row r="210" customHeight="1" ht="15" spans="1:10">
       <c r="A210" s="1" t="n">
-        <v>804184</v>
+        <v>804523</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>216</v>
@@ -8319,7 +8328,7 @@
         <v>2</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>2645</v>
+        <v>704</v>
       </c>
       <c r="G210" s="3" t="n">
         <v>0</v>
@@ -8336,7 +8345,7 @@
     </row>
     <row r="211" customHeight="1" ht="15" spans="1:10">
       <c r="A211" s="1" t="n">
-        <v>804523</v>
+        <v>804522</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>217</v>
@@ -8351,7 +8360,7 @@
         <v>2</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>684</v>
+        <v>2238</v>
       </c>
       <c r="G211" s="3" t="n">
         <v>0</v>
@@ -8368,7 +8377,7 @@
     </row>
     <row r="212" customHeight="1" ht="15" spans="1:10">
       <c r="A212" s="1" t="n">
-        <v>804522</v>
+        <v>804570</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>218</v>
@@ -8383,7 +8392,7 @@
         <v>2</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>2238</v>
+        <v>1431</v>
       </c>
       <c r="G212" s="3" t="n">
         <v>0</v>
@@ -8400,7 +8409,7 @@
     </row>
     <row r="213" customHeight="1" ht="15" spans="1:10">
       <c r="A213" s="1" t="n">
-        <v>804570</v>
+        <v>804552</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>219</v>
@@ -8415,7 +8424,7 @@
         <v>2</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>1431</v>
+        <v>372</v>
       </c>
       <c r="G213" s="3" t="n">
         <v>0</v>
@@ -8432,7 +8441,7 @@
     </row>
     <row r="214" customHeight="1" ht="15" spans="1:10">
       <c r="A214" s="1" t="n">
-        <v>804552</v>
+        <v>804234</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>220</v>
@@ -8447,7 +8456,7 @@
         <v>2</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>372</v>
+        <v>564</v>
       </c>
       <c r="G214" s="3" t="n">
         <v>0</v>
@@ -8464,7 +8473,7 @@
     </row>
     <row r="215" customHeight="1" ht="15" spans="1:10">
       <c r="A215" s="1" t="n">
-        <v>804234</v>
+        <v>804235</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>221</v>
@@ -8479,7 +8488,7 @@
         <v>2</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>517</v>
+        <v>1759</v>
       </c>
       <c r="G215" s="3" t="n">
         <v>0</v>
@@ -8496,7 +8505,7 @@
     </row>
     <row r="216" customHeight="1" ht="15" spans="1:10">
       <c r="A216" s="1" t="n">
-        <v>804235</v>
+        <v>804495</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>222</v>
@@ -8511,7 +8520,7 @@
         <v>2</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>1759</v>
+        <v>1128</v>
       </c>
       <c r="G216" s="3" t="n">
         <v>0</v>
@@ -8528,7 +8537,7 @@
     </row>
     <row r="217" customHeight="1" ht="15" spans="1:10">
       <c r="A217" s="1" t="n">
-        <v>804495</v>
+        <v>804218</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>223</v>
@@ -8543,7 +8552,7 @@
         <v>2</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>1128</v>
+        <v>637</v>
       </c>
       <c r="G217" s="3" t="n">
         <v>0</v>
@@ -8560,7 +8569,7 @@
     </row>
     <row r="218" customHeight="1" ht="15" spans="1:10">
       <c r="A218" s="1" t="n">
-        <v>804218</v>
+        <v>804219</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>224</v>
@@ -8575,7 +8584,7 @@
         <v>2</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>637</v>
+        <v>1509</v>
       </c>
       <c r="G218" s="3" t="n">
         <v>0</v>
@@ -8592,7 +8601,7 @@
     </row>
     <row r="219" customHeight="1" ht="15" spans="1:10">
       <c r="A219" s="1" t="n">
-        <v>804219</v>
+        <v>804082</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>225</v>
@@ -8607,7 +8616,7 @@
         <v>2</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>374</v>
+        <v>1148</v>
       </c>
       <c r="G219" s="3" t="n">
         <v>0</v>
@@ -8624,7 +8633,7 @@
     </row>
     <row r="220" customHeight="1" ht="15" spans="1:10">
       <c r="A220" s="1" t="n">
-        <v>804082</v>
+        <v>804410</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>226</v>
@@ -8639,7 +8648,7 @@
         <v>2</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>1148</v>
+        <v>2783</v>
       </c>
       <c r="G220" s="3" t="n">
         <v>0</v>
@@ -8656,7 +8665,7 @@
     </row>
     <row r="221" customHeight="1" ht="15" spans="1:10">
       <c r="A221" s="1" t="n">
-        <v>804410</v>
+        <v>804067</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>227</v>
@@ -8671,7 +8680,7 @@
         <v>2</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>2783</v>
+        <v>1714</v>
       </c>
       <c r="G221" s="3" t="n">
         <v>0</v>
@@ -8688,7 +8697,7 @@
     </row>
     <row r="222" customHeight="1" ht="15" spans="1:10">
       <c r="A222" s="1" t="n">
-        <v>804067</v>
+        <v>804385</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>228</v>
@@ -8703,7 +8712,7 @@
         <v>2</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>1714</v>
+        <v>3751</v>
       </c>
       <c r="G222" s="3" t="n">
         <v>0</v>
@@ -8720,7 +8729,7 @@
     </row>
     <row r="223" customHeight="1" ht="15" spans="1:10">
       <c r="A223" s="1" t="n">
-        <v>804385</v>
+        <v>804507</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>229</v>
@@ -8735,7 +8744,7 @@
         <v>2</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>3751</v>
+        <v>169</v>
       </c>
       <c r="G223" s="3" t="n">
         <v>0</v>
@@ -8752,7 +8761,7 @@
     </row>
     <row r="224" customHeight="1" ht="15" spans="1:10">
       <c r="A224" s="1" t="n">
-        <v>804507</v>
+        <v>804073</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>230</v>
@@ -8767,7 +8776,7 @@
         <v>2</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>169</v>
+        <v>2439</v>
       </c>
       <c r="G224" s="3" t="n">
         <v>0</v>
@@ -8784,7 +8793,7 @@
     </row>
     <row r="225" customHeight="1" ht="15" spans="1:10">
       <c r="A225" s="1" t="n">
-        <v>804073</v>
+        <v>804074</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>231</v>
@@ -8799,7 +8808,7 @@
         <v>2</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>2439</v>
+        <v>3676</v>
       </c>
       <c r="G225" s="3" t="n">
         <v>0</v>
@@ -8816,7 +8825,7 @@
     </row>
     <row r="226" customHeight="1" ht="15" spans="1:10">
       <c r="A226" s="1" t="n">
-        <v>804074</v>
+        <v>804071</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>232</v>
@@ -8831,7 +8840,7 @@
         <v>2</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>4072</v>
+        <v>251</v>
       </c>
       <c r="G226" s="3" t="n">
         <v>0</v>
@@ -8848,7 +8857,7 @@
     </row>
     <row r="227" customHeight="1" ht="15" spans="1:10">
       <c r="A227" s="1" t="n">
-        <v>804071</v>
+        <v>804072</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>233</v>
@@ -8863,7 +8872,7 @@
         <v>2</v>
       </c>
       <c r="F227" s="3" t="n">
-        <v>731</v>
+        <v>2145</v>
       </c>
       <c r="G227" s="3" t="n">
         <v>0</v>
@@ -8880,7 +8889,7 @@
     </row>
     <row r="228" customHeight="1" ht="15" spans="1:10">
       <c r="A228" s="1" t="n">
-        <v>804072</v>
+        <v>804534</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>234</v>
@@ -8895,7 +8904,7 @@
         <v>2</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>2541</v>
+        <v>360</v>
       </c>
       <c r="G228" s="3" t="n">
         <v>0</v>
@@ -8912,7 +8921,7 @@
     </row>
     <row r="229" customHeight="1" ht="15" spans="1:10">
       <c r="A229" s="1" t="n">
-        <v>804534</v>
+        <v>804612</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>235</v>
@@ -8927,7 +8936,7 @@
         <v>2</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>360</v>
+        <v>122</v>
       </c>
       <c r="G229" s="3" t="n">
         <v>0</v>
@@ -8944,7 +8953,7 @@
     </row>
     <row r="230" customHeight="1" ht="15" spans="1:10">
       <c r="A230" s="1" t="n">
-        <v>804612</v>
+        <v>804532</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>236</v>
@@ -8959,7 +8968,7 @@
         <v>2</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>122</v>
+        <v>268</v>
       </c>
       <c r="G230" s="3" t="n">
         <v>0</v>
@@ -8976,7 +8985,7 @@
     </row>
     <row r="231" customHeight="1" ht="15" spans="1:10">
       <c r="A231" s="1" t="n">
-        <v>804532</v>
+        <v>804480</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>237</v>
@@ -8991,7 +9000,7 @@
         <v>2</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>268</v>
+        <v>1918</v>
       </c>
       <c r="G231" s="3" t="n">
         <v>0</v>
@@ -9008,7 +9017,7 @@
     </row>
     <row r="232" customHeight="1" ht="15" spans="1:10">
       <c r="A232" s="1" t="n">
-        <v>804480</v>
+        <v>804481</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>238</v>
@@ -9023,7 +9032,7 @@
         <v>2</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>1918</v>
+        <v>473</v>
       </c>
       <c r="G232" s="3" t="n">
         <v>0</v>
@@ -9040,7 +9049,7 @@
     </row>
     <row r="233" customHeight="1" ht="15" spans="1:10">
       <c r="A233" s="1" t="n">
-        <v>804481</v>
+        <v>804476</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>239</v>
@@ -9055,7 +9064,7 @@
         <v>2</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>473</v>
+        <v>3350</v>
       </c>
       <c r="G233" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9081,7 @@
     </row>
     <row r="234" customHeight="1" ht="15" spans="1:10">
       <c r="A234" s="1" t="n">
-        <v>804476</v>
+        <v>804479</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>240</v>
@@ -9087,7 +9096,7 @@
         <v>2</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>3350</v>
+        <v>1453</v>
       </c>
       <c r="G234" s="3" t="n">
         <v>0</v>
@@ -9104,7 +9113,7 @@
     </row>
     <row r="235" customHeight="1" ht="15" spans="1:10">
       <c r="A235" s="1" t="n">
-        <v>804479</v>
+        <v>804133</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>241</v>
@@ -9119,7 +9128,7 @@
         <v>2</v>
       </c>
       <c r="F235" s="3" t="n">
-        <v>1453</v>
+        <v>848</v>
       </c>
       <c r="G235" s="3" t="n">
         <v>0</v>
@@ -9136,7 +9145,7 @@
     </row>
     <row r="236" customHeight="1" ht="15" spans="1:10">
       <c r="A236" s="1" t="n">
-        <v>804133</v>
+        <v>804002</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>242</v>
@@ -9151,7 +9160,7 @@
         <v>2</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>848</v>
+        <v>2881</v>
       </c>
       <c r="G236" s="3" t="n">
         <v>0</v>
@@ -9168,7 +9177,7 @@
     </row>
     <row r="237" customHeight="1" ht="15" spans="1:10">
       <c r="A237" s="1" t="n">
-        <v>804002</v>
+        <v>804271</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>243</v>
@@ -9183,7 +9192,7 @@
         <v>2</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>2250</v>
+        <v>4488</v>
       </c>
       <c r="G237" s="3" t="n">
         <v>0</v>
@@ -9200,7 +9209,7 @@
     </row>
     <row r="238" customHeight="1" ht="15" spans="1:10">
       <c r="A238" s="1" t="n">
-        <v>804271</v>
+        <v>804181</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>244</v>
@@ -9215,7 +9224,7 @@
         <v>2</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>4488</v>
+        <v>112</v>
       </c>
       <c r="G238" s="3" t="n">
         <v>0</v>
@@ -9232,7 +9241,7 @@
     </row>
     <row r="239" customHeight="1" ht="15" spans="1:10">
       <c r="A239" s="1" t="n">
-        <v>804181</v>
+        <v>804178</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>245</v>
@@ -9247,7 +9256,7 @@
         <v>2</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>56</v>
+        <v>1407</v>
       </c>
       <c r="G239" s="3" t="n">
         <v>0</v>
@@ -9264,7 +9273,7 @@
     </row>
     <row r="240" customHeight="1" ht="15" spans="1:10">
       <c r="A240" s="1" t="n">
-        <v>804178</v>
+        <v>804039</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>246</v>
@@ -9279,7 +9288,7 @@
         <v>2</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>1407</v>
+        <v>5250</v>
       </c>
       <c r="G240" s="3" t="n">
         <v>0</v>
@@ -9296,7 +9305,7 @@
     </row>
     <row r="241" customHeight="1" ht="15" spans="1:10">
       <c r="A241" s="1" t="n">
-        <v>804039</v>
+        <v>804069</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>247</v>
@@ -9311,7 +9320,7 @@
         <v>2</v>
       </c>
       <c r="F241" s="3" t="n">
-        <v>5250</v>
+        <v>4026</v>
       </c>
       <c r="G241" s="3" t="n">
         <v>0</v>
@@ -9328,7 +9337,7 @@
     </row>
     <row r="242" customHeight="1" ht="15" spans="1:10">
       <c r="A242" s="1" t="n">
-        <v>804069</v>
+        <v>804037</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>248</v>
@@ -9343,7 +9352,7 @@
         <v>2</v>
       </c>
       <c r="F242" s="3" t="n">
-        <v>5414</v>
+        <v>2163</v>
       </c>
       <c r="G242" s="3" t="n">
         <v>0</v>
@@ -9360,7 +9369,7 @@
     </row>
     <row r="243" customHeight="1" ht="15" spans="1:10">
       <c r="A243" s="1" t="n">
-        <v>804037</v>
+        <v>804027</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>249</v>
@@ -9375,7 +9384,7 @@
         <v>2</v>
       </c>
       <c r="F243" s="3" t="n">
-        <v>2163</v>
+        <v>4200</v>
       </c>
       <c r="G243" s="3" t="n">
         <v>0</v>
@@ -9392,7 +9401,7 @@
     </row>
     <row r="244" customHeight="1" ht="15" spans="1:10">
       <c r="A244" s="1" t="n">
-        <v>804027</v>
+        <v>804028</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>250</v>
@@ -9407,7 +9416,7 @@
         <v>2</v>
       </c>
       <c r="F244" s="3" t="n">
-        <v>4200</v>
+        <v>8793</v>
       </c>
       <c r="G244" s="3" t="n">
         <v>0</v>
@@ -9471,7 +9480,7 @@
         <v>2</v>
       </c>
       <c r="F246" s="3" t="n">
-        <v>2332</v>
+        <v>3637</v>
       </c>
       <c r="G246" s="3" t="n">
         <v>0</v>
@@ -9535,7 +9544,7 @@
         <v>2</v>
       </c>
       <c r="F248" s="3" t="n">
-        <v>4928</v>
+        <v>5070</v>
       </c>
       <c r="G248" s="3" t="n">
         <v>0</v>
@@ -9759,7 +9768,7 @@
         <v>2</v>
       </c>
       <c r="F255" s="3" t="n">
-        <v>8113</v>
+        <v>8456</v>
       </c>
       <c r="G255" s="3" t="n">
         <v>0</v>
@@ -10047,7 +10056,7 @@
         <v>2</v>
       </c>
       <c r="F264" s="3" t="n">
-        <v>3359</v>
+        <v>4999</v>
       </c>
       <c r="G264" s="3" t="n">
         <v>0</v>
@@ -10111,7 +10120,7 @@
         <v>2</v>
       </c>
       <c r="F266" s="3" t="n">
-        <v>4496</v>
+        <v>4446</v>
       </c>
       <c r="G266" s="3" t="n">
         <v>0</v>
@@ -10175,7 +10184,7 @@
         <v>2</v>
       </c>
       <c r="F268" s="3" t="n">
-        <v>4937</v>
+        <v>4546</v>
       </c>
       <c r="G268" s="3" t="n">
         <v>0</v>
@@ -10207,7 +10216,7 @@
         <v>2</v>
       </c>
       <c r="F269" s="3" t="n">
-        <v>126123</v>
+        <v>141791</v>
       </c>
       <c r="G269" s="3" t="n">
         <v>0</v>
@@ -10335,7 +10344,7 @@
         <v>2</v>
       </c>
       <c r="F273" s="3" t="n">
-        <v>18124</v>
+        <v>15422</v>
       </c>
       <c r="G273" s="3" t="n">
         <v>0</v>
@@ -10399,7 +10408,7 @@
         <v>2</v>
       </c>
       <c r="F275" s="3" t="n">
-        <v>47780</v>
+        <v>44745</v>
       </c>
       <c r="G275" s="3" t="n">
         <v>0</v>
@@ -10559,7 +10568,7 @@
         <v>2</v>
       </c>
       <c r="F280" s="3" t="n">
-        <v>28905</v>
+        <v>34429</v>
       </c>
       <c r="G280" s="3" t="n">
         <v>0</v>
@@ -10591,7 +10600,7 @@
         <v>2</v>
       </c>
       <c r="F281" s="3" t="n">
-        <v>7078</v>
+        <v>4318</v>
       </c>
       <c r="G281" s="3" t="n">
         <v>0</v>
@@ -10608,7 +10617,7 @@
     </row>
     <row r="282" customHeight="1" ht="15" spans="1:10">
       <c r="A282" s="1" t="n">
-        <v>804446</v>
+        <v>804394</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>288</v>
@@ -10623,7 +10632,7 @@
         <v>2</v>
       </c>
       <c r="F282" s="3" t="n">
-        <v>21498</v>
+        <v>11614</v>
       </c>
       <c r="G282" s="3" t="n">
         <v>0</v>
@@ -10640,7 +10649,7 @@
     </row>
     <row r="283" customHeight="1" ht="15" spans="1:10">
       <c r="A283" s="1" t="n">
-        <v>804128</v>
+        <v>804446</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>289</v>
@@ -10655,7 +10664,7 @@
         <v>2</v>
       </c>
       <c r="F283" s="3" t="n">
-        <v>41629</v>
+        <v>21498</v>
       </c>
       <c r="G283" s="3" t="n">
         <v>0</v>
@@ -10672,7 +10681,7 @@
     </row>
     <row r="284" customHeight="1" ht="15" spans="1:10">
       <c r="A284" s="1" t="n">
-        <v>813040</v>
+        <v>804506</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>290</v>
@@ -10687,7 +10696,7 @@
         <v>2</v>
       </c>
       <c r="F284" s="3" t="n">
-        <v>2455</v>
+        <v>1527</v>
       </c>
       <c r="G284" s="3" t="n">
         <v>0</v>
@@ -10704,7 +10713,7 @@
     </row>
     <row r="285" customHeight="1" ht="15" spans="1:10">
       <c r="A285" s="1" t="n">
-        <v>813054</v>
+        <v>804128</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>291</v>
@@ -10719,7 +10728,7 @@
         <v>2</v>
       </c>
       <c r="F285" s="3" t="n">
-        <v>6466</v>
+        <v>36968</v>
       </c>
       <c r="G285" s="3" t="n">
         <v>0</v>
@@ -10736,7 +10745,7 @@
     </row>
     <row r="286" customHeight="1" ht="15" spans="1:10">
       <c r="A286" s="1" t="n">
-        <v>813048</v>
+        <v>813040</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>292</v>
@@ -10751,7 +10760,7 @@
         <v>2</v>
       </c>
       <c r="F286" s="3" t="n">
-        <v>8048</v>
+        <v>2455</v>
       </c>
       <c r="G286" s="3" t="n">
         <v>0</v>
@@ -10768,7 +10777,7 @@
     </row>
     <row r="287" customHeight="1" ht="15" spans="1:10">
       <c r="A287" s="1" t="n">
-        <v>813317</v>
+        <v>813054</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>293</v>
@@ -10783,7 +10792,7 @@
         <v>2</v>
       </c>
       <c r="F287" s="3" t="n">
-        <v>1170</v>
+        <v>5885</v>
       </c>
       <c r="G287" s="3" t="n">
         <v>0</v>
@@ -10800,7 +10809,7 @@
     </row>
     <row r="288" customHeight="1" ht="15" spans="1:10">
       <c r="A288" s="1" t="n">
-        <v>804213</v>
+        <v>813048</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>294</v>
@@ -10815,7 +10824,7 @@
         <v>2</v>
       </c>
       <c r="F288" s="3" t="n">
-        <v>992</v>
+        <v>7887</v>
       </c>
       <c r="G288" s="3" t="n">
         <v>0</v>
@@ -10832,7 +10841,7 @@
     </row>
     <row r="289" customHeight="1" ht="15" spans="1:10">
       <c r="A289" s="1" t="n">
-        <v>813293</v>
+        <v>813317</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>295</v>
@@ -10847,7 +10856,7 @@
         <v>2</v>
       </c>
       <c r="F289" s="3" t="n">
-        <v>11618</v>
+        <v>1170</v>
       </c>
       <c r="G289" s="3" t="n">
         <v>0</v>
@@ -10864,22 +10873,22 @@
     </row>
     <row r="290" customHeight="1" ht="15" spans="1:10">
       <c r="A290" s="1" t="n">
-        <v>301056</v>
+        <v>804213</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F290" s="3" t="n">
-        <v>2576.7938</v>
+        <v>992</v>
       </c>
       <c r="G290" s="3" t="n">
         <v>0</v>
@@ -10896,22 +10905,22 @@
     </row>
     <row r="291" customHeight="1" ht="15" spans="1:10">
       <c r="A291" s="1" t="n">
-        <v>301038</v>
+        <v>813293</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>297</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F291" s="3" t="n">
-        <v>2618.24</v>
+        <v>10489</v>
       </c>
       <c r="G291" s="3" t="n">
         <v>0</v>
@@ -10928,7 +10937,7 @@
     </row>
     <row r="292" customHeight="1" ht="15" spans="1:10">
       <c r="A292" s="1" t="n">
-        <v>301052</v>
+        <v>301056</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>298</v>
@@ -10937,13 +10946,13 @@
         <v>4</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F292" s="3" t="n">
-        <v>656.899</v>
+        <v>2491.454</v>
       </c>
       <c r="G292" s="3" t="n">
         <v>0</v>
@@ -10960,7 +10969,7 @@
     </row>
     <row r="293" customHeight="1" ht="15" spans="1:10">
       <c r="A293" s="1" t="n">
-        <v>301005</v>
+        <v>301038</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>299</v>
@@ -10975,7 +10984,7 @@
         <v>2</v>
       </c>
       <c r="F293" s="3" t="n">
-        <v>275</v>
+        <v>2561.48</v>
       </c>
       <c r="G293" s="3" t="n">
         <v>0</v>
@@ -10992,13 +11001,13 @@
     </row>
     <row r="294" customHeight="1" ht="15" spans="1:10">
       <c r="A294" s="1" t="n">
-        <v>998861</v>
+        <v>301052</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>300</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>6</v>
@@ -11007,39 +11016,39 @@
         <v>2</v>
       </c>
       <c r="F294" s="3" t="n">
-        <v>1</v>
+        <v>656.899</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>2857.81</v>
+        <v>0</v>
       </c>
       <c r="H294" s="3" t="n">
-        <v>2857.81</v>
+        <v>0</v>
       </c>
       <c r="I294" s="3" t="n">
-        <v>2563.8522</v>
+        <v>0</v>
       </c>
       <c r="J294" s="3" t="n">
-        <v>2563.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" customHeight="1" ht="15" spans="1:10">
       <c r="A295" s="1" t="n">
-        <v>813047</v>
+        <v>301005</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>301</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F295" s="3" t="n">
-        <v>4055</v>
+        <v>275</v>
       </c>
       <c r="G295" s="3" t="n">
         <v>0</v>
@@ -11056,13 +11065,13 @@
     </row>
     <row r="296" customHeight="1" ht="15" spans="1:10">
       <c r="A296" s="1" t="n">
-        <v>813395</v>
+        <v>998861</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>302</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>6</v>
@@ -11071,39 +11080,39 @@
         <v>2</v>
       </c>
       <c r="F296" s="3" t="n">
-        <v>9749</v>
+        <v>1</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>0</v>
+        <v>2857.81</v>
       </c>
       <c r="H296" s="3" t="n">
-        <v>0</v>
+        <v>2857.81</v>
       </c>
       <c r="I296" s="3" t="n">
-        <v>0</v>
+        <v>2563.8522</v>
       </c>
       <c r="J296" s="3" t="n">
-        <v>0</v>
+        <v>2563.85</v>
       </c>
     </row>
     <row r="297" customHeight="1" ht="15" spans="1:10">
       <c r="A297" s="1" t="n">
-        <v>302025</v>
+        <v>813047</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>303</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F297" s="3" t="n">
-        <v>20</v>
+        <v>4055</v>
       </c>
       <c r="G297" s="3" t="n">
         <v>0</v>
@@ -11120,22 +11129,22 @@
     </row>
     <row r="298" customHeight="1" ht="15" spans="1:10">
       <c r="A298" s="1" t="n">
-        <v>302011</v>
+        <v>813395</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>304</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F298" s="3" t="n">
-        <v>22.4</v>
+        <v>8886</v>
       </c>
       <c r="G298" s="3" t="n">
         <v>0</v>
@@ -11152,7 +11161,7 @@
     </row>
     <row r="299" customHeight="1" ht="15" spans="1:10">
       <c r="A299" s="1" t="n">
-        <v>302023</v>
+        <v>302025</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>305</v>
@@ -11167,7 +11176,7 @@
         <v>2</v>
       </c>
       <c r="F299" s="3" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="G299" s="3" t="n">
         <v>0</v>
@@ -11184,7 +11193,7 @@
     </row>
     <row r="300" customHeight="1" ht="15" spans="1:10">
       <c r="A300" s="1" t="n">
-        <v>302020</v>
+        <v>302011</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>306</v>
@@ -11199,7 +11208,7 @@
         <v>2</v>
       </c>
       <c r="F300" s="3" t="n">
-        <v>116</v>
+        <v>22.4</v>
       </c>
       <c r="G300" s="3" t="n">
         <v>0</v>
@@ -11216,22 +11225,22 @@
     </row>
     <row r="301" customHeight="1" ht="15" spans="1:10">
       <c r="A301" s="1" t="n">
-        <v>302015</v>
+        <v>302023</v>
       </c>
       <c r="B301" s="1" t="s">
         <v>307</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F301" s="3" t="n">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="G301" s="3" t="n">
         <v>0</v>
@@ -11248,7 +11257,7 @@
     </row>
     <row r="302" customHeight="1" ht="15" spans="1:10">
       <c r="A302" s="1" t="n">
-        <v>302009</v>
+        <v>302020</v>
       </c>
       <c r="B302" s="1" t="s">
         <v>308</v>
@@ -11257,13 +11266,13 @@
         <v>4</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F302" s="3" t="n">
-        <v>0.924687</v>
+        <v>116</v>
       </c>
       <c r="G302" s="3" t="n">
         <v>0</v>
@@ -11280,22 +11289,22 @@
     </row>
     <row r="303" customHeight="1" ht="15" spans="1:10">
       <c r="A303" s="1" t="n">
-        <v>302022</v>
+        <v>302015</v>
       </c>
       <c r="B303" s="1" t="s">
         <v>309</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F303" s="3" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G303" s="3" t="n">
         <v>0</v>
@@ -11312,7 +11321,7 @@
     </row>
     <row r="304" customHeight="1" ht="15" spans="1:10">
       <c r="A304" s="1" t="n">
-        <v>302008</v>
+        <v>302009</v>
       </c>
       <c r="B304" s="1" t="s">
         <v>310</v>
@@ -11327,7 +11336,7 @@
         <v>2</v>
       </c>
       <c r="F304" s="3" t="n">
-        <v>153</v>
+        <v>0.924687</v>
       </c>
       <c r="G304" s="3" t="n">
         <v>0</v>
@@ -11344,22 +11353,22 @@
     </row>
     <row r="305" customHeight="1" ht="15" spans="1:10">
       <c r="A305" s="1" t="n">
-        <v>302016</v>
+        <v>302022</v>
       </c>
       <c r="B305" s="1" t="s">
         <v>311</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F305" s="3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G305" s="3" t="n">
         <v>0</v>
@@ -11376,22 +11385,22 @@
     </row>
     <row r="306" customHeight="1" ht="15" spans="1:10">
       <c r="A306" s="1" t="n">
-        <v>302012</v>
+        <v>302008</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>312</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F306" s="3" t="n">
-        <v>28</v>
+        <v>144.160946</v>
       </c>
       <c r="G306" s="3" t="n">
         <v>0</v>
@@ -11408,13 +11417,13 @@
     </row>
     <row r="307" customHeight="1" ht="15" spans="1:10">
       <c r="A307" s="1" t="n">
-        <v>813237</v>
+        <v>302016</v>
       </c>
       <c r="B307" s="1" t="s">
         <v>313</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>6</v>
@@ -11423,7 +11432,7 @@
         <v>2</v>
       </c>
       <c r="F307" s="3" t="n">
-        <v>16567</v>
+        <v>25</v>
       </c>
       <c r="G307" s="3" t="n">
         <v>0</v>
@@ -11440,13 +11449,13 @@
     </row>
     <row r="308" customHeight="1" ht="15" spans="1:10">
       <c r="A308" s="1" t="n">
-        <v>804528</v>
+        <v>302012</v>
       </c>
       <c r="B308" s="1" t="s">
         <v>314</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>6</v>
@@ -11455,7 +11464,7 @@
         <v>2</v>
       </c>
       <c r="F308" s="3" t="n">
-        <v>3524</v>
+        <v>28</v>
       </c>
       <c r="G308" s="3" t="n">
         <v>0</v>
@@ -11472,7 +11481,7 @@
     </row>
     <row r="309" customHeight="1" ht="15" spans="1:10">
       <c r="A309" s="1" t="n">
-        <v>804100</v>
+        <v>813237</v>
       </c>
       <c r="B309" s="1" t="s">
         <v>315</v>
@@ -11487,7 +11496,7 @@
         <v>2</v>
       </c>
       <c r="F309" s="3" t="n">
-        <v>41220</v>
+        <v>16567</v>
       </c>
       <c r="G309" s="3" t="n">
         <v>0</v>
@@ -11504,7 +11513,7 @@
     </row>
     <row r="310" customHeight="1" ht="15" spans="1:10">
       <c r="A310" s="1" t="n">
-        <v>804279</v>
+        <v>804528</v>
       </c>
       <c r="B310" s="1" t="s">
         <v>316</v>
@@ -11519,7 +11528,7 @@
         <v>2</v>
       </c>
       <c r="F310" s="3" t="n">
-        <v>254345</v>
+        <v>3524</v>
       </c>
       <c r="G310" s="3" t="n">
         <v>0</v>
@@ -11536,7 +11545,7 @@
     </row>
     <row r="311" customHeight="1" ht="15" spans="1:10">
       <c r="A311" s="1" t="n">
-        <v>804513</v>
+        <v>804100</v>
       </c>
       <c r="B311" s="1" t="s">
         <v>317</v>
@@ -11551,7 +11560,7 @@
         <v>2</v>
       </c>
       <c r="F311" s="3" t="n">
-        <v>9353</v>
+        <v>33548</v>
       </c>
       <c r="G311" s="3" t="n">
         <v>0</v>
@@ -11568,22 +11577,22 @@
     </row>
     <row r="312" customHeight="1" ht="15" spans="1:10">
       <c r="A312" s="1" t="n">
-        <v>301014</v>
+        <v>804279</v>
       </c>
       <c r="B312" s="1" t="s">
         <v>318</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F312" s="3" t="n">
-        <v>479.9942</v>
+        <v>217500</v>
       </c>
       <c r="G312" s="3" t="n">
         <v>0</v>
@@ -11600,22 +11609,22 @@
     </row>
     <row r="313" customHeight="1" ht="15" spans="1:10">
       <c r="A313" s="1" t="n">
-        <v>301025</v>
+        <v>804513</v>
       </c>
       <c r="B313" s="1" t="s">
         <v>319</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F313" s="3" t="n">
-        <v>20915.771569</v>
+        <v>9000</v>
       </c>
       <c r="G313" s="3" t="n">
         <v>0</v>
@@ -11632,7 +11641,7 @@
     </row>
     <row r="314" customHeight="1" ht="15" spans="1:10">
       <c r="A314" s="1" t="n">
-        <v>301059</v>
+        <v>301014</v>
       </c>
       <c r="B314" s="1" t="s">
         <v>320</v>
@@ -11647,7 +11656,7 @@
         <v>2</v>
       </c>
       <c r="F314" s="3" t="n">
-        <v>75</v>
+        <v>479.9942</v>
       </c>
       <c r="G314" s="3" t="n">
         <v>0</v>
@@ -11664,13 +11673,13 @@
     </row>
     <row r="315" customHeight="1" ht="15" spans="1:10">
       <c r="A315" s="1" t="n">
-        <v>301016</v>
+        <v>301025</v>
       </c>
       <c r="B315" s="1" t="s">
         <v>321</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>1</v>
@@ -11679,7 +11688,7 @@
         <v>2</v>
       </c>
       <c r="F315" s="3" t="n">
-        <v>200</v>
+        <v>20911.083669</v>
       </c>
       <c r="G315" s="3" t="n">
         <v>0</v>
@@ -11696,7 +11705,7 @@
     </row>
     <row r="316" customHeight="1" ht="15" spans="1:10">
       <c r="A316" s="1" t="n">
-        <v>301020</v>
+        <v>301059</v>
       </c>
       <c r="B316" s="1" t="s">
         <v>322</v>
@@ -11711,7 +11720,7 @@
         <v>2</v>
       </c>
       <c r="F316" s="3" t="n">
-        <v>300</v>
+        <v>75</v>
       </c>
       <c r="G316" s="3" t="n">
         <v>0</v>
@@ -11728,7 +11737,7 @@
     </row>
     <row r="317" customHeight="1" ht="15" spans="1:10">
       <c r="A317" s="1" t="n">
-        <v>301008</v>
+        <v>301016</v>
       </c>
       <c r="B317" s="1" t="s">
         <v>323</v>
@@ -11743,7 +11752,7 @@
         <v>2</v>
       </c>
       <c r="F317" s="3" t="n">
-        <v>895.761865</v>
+        <v>200</v>
       </c>
       <c r="G317" s="3" t="n">
         <v>0</v>
@@ -11760,7 +11769,7 @@
     </row>
     <row r="318" customHeight="1" ht="15" spans="1:10">
       <c r="A318" s="1" t="n">
-        <v>301024</v>
+        <v>301020</v>
       </c>
       <c r="B318" s="1" t="s">
         <v>324</v>
@@ -11775,7 +11784,7 @@
         <v>2</v>
       </c>
       <c r="F318" s="3" t="n">
-        <v>6875</v>
+        <v>300</v>
       </c>
       <c r="G318" s="3" t="n">
         <v>0</v>
@@ -11792,7 +11801,7 @@
     </row>
     <row r="319" customHeight="1" ht="15" spans="1:10">
       <c r="A319" s="1" t="n">
-        <v>301054</v>
+        <v>301008</v>
       </c>
       <c r="B319" s="1" t="s">
         <v>325</v>
@@ -11807,7 +11816,7 @@
         <v>2</v>
       </c>
       <c r="F319" s="3" t="n">
-        <v>2000</v>
+        <v>783.010865</v>
       </c>
       <c r="G319" s="3" t="n">
         <v>0</v>
@@ -11824,7 +11833,7 @@
     </row>
     <row r="320" customHeight="1" ht="15" spans="1:10">
       <c r="A320" s="1" t="n">
-        <v>301050</v>
+        <v>301024</v>
       </c>
       <c r="B320" s="1" t="s">
         <v>326</v>
@@ -11839,7 +11848,7 @@
         <v>2</v>
       </c>
       <c r="F320" s="3" t="n">
-        <v>5536.7922</v>
+        <v>6875</v>
       </c>
       <c r="G320" s="3" t="n">
         <v>0</v>
@@ -11856,7 +11865,7 @@
     </row>
     <row r="321" customHeight="1" ht="15" spans="1:10">
       <c r="A321" s="1" t="n">
-        <v>301007</v>
+        <v>301054</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>327</v>
@@ -11871,7 +11880,7 @@
         <v>2</v>
       </c>
       <c r="F321" s="3" t="n">
-        <v>225</v>
+        <v>1285.5392</v>
       </c>
       <c r="G321" s="3" t="n">
         <v>0</v>
@@ -11888,22 +11897,22 @@
     </row>
     <row r="322" customHeight="1" ht="15" spans="1:10">
       <c r="A322" s="1" t="n">
-        <v>804468</v>
+        <v>301050</v>
       </c>
       <c r="B322" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F322" s="3" t="n">
-        <v>29817</v>
+        <v>5536.7922</v>
       </c>
       <c r="G322" s="3" t="n">
         <v>0</v>
@@ -11920,22 +11929,22 @@
     </row>
     <row r="323" customHeight="1" ht="15" spans="1:10">
       <c r="A323" s="1" t="n">
-        <v>813480</v>
+        <v>301007</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>329</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F323" s="3" t="n">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="G323" s="3" t="n">
         <v>0</v>
@@ -11952,7 +11961,7 @@
     </row>
     <row r="324" customHeight="1" ht="15" spans="1:10">
       <c r="A324" s="1" t="n">
-        <v>813478</v>
+        <v>804468</v>
       </c>
       <c r="B324" s="1" t="s">
         <v>330</v>
@@ -11967,7 +11976,7 @@
         <v>2</v>
       </c>
       <c r="F324" s="3" t="n">
-        <v>1091</v>
+        <v>29817</v>
       </c>
       <c r="G324" s="3" t="n">
         <v>0</v>
@@ -11984,7 +11993,7 @@
     </row>
     <row r="325" customHeight="1" ht="15" spans="1:10">
       <c r="A325" s="1" t="n">
-        <v>813294</v>
+        <v>813480</v>
       </c>
       <c r="B325" s="1" t="s">
         <v>331</v>
@@ -11999,7 +12008,7 @@
         <v>2</v>
       </c>
       <c r="F325" s="3" t="n">
-        <v>14975</v>
+        <v>156</v>
       </c>
       <c r="G325" s="3" t="n">
         <v>0</v>
@@ -12016,7 +12025,7 @@
     </row>
     <row r="326" customHeight="1" ht="15" spans="1:10">
       <c r="A326" s="1" t="n">
-        <v>813175</v>
+        <v>813478</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>332</v>
@@ -12031,7 +12040,7 @@
         <v>2</v>
       </c>
       <c r="F326" s="3" t="n">
-        <v>342</v>
+        <v>1091</v>
       </c>
       <c r="G326" s="3" t="n">
         <v>0</v>
@@ -12048,7 +12057,7 @@
     </row>
     <row r="327" customHeight="1" ht="15" spans="1:10">
       <c r="A327" s="1" t="n">
-        <v>813305</v>
+        <v>813294</v>
       </c>
       <c r="B327" s="1" t="s">
         <v>333</v>
@@ -12063,7 +12072,7 @@
         <v>2</v>
       </c>
       <c r="F327" s="3" t="n">
-        <v>928</v>
+        <v>13712</v>
       </c>
       <c r="G327" s="3" t="n">
         <v>0</v>
@@ -12080,7 +12089,7 @@
     </row>
     <row r="328" customHeight="1" ht="15" spans="1:10">
       <c r="A328" s="1" t="n">
-        <v>813269</v>
+        <v>813175</v>
       </c>
       <c r="B328" s="1" t="s">
         <v>334</v>
@@ -12095,7 +12104,7 @@
         <v>2</v>
       </c>
       <c r="F328" s="3" t="n">
-        <v>372</v>
+        <v>342</v>
       </c>
       <c r="G328" s="3" t="n">
         <v>0</v>
@@ -12112,7 +12121,7 @@
     </row>
     <row r="329" customHeight="1" ht="15" spans="1:10">
       <c r="A329" s="1" t="n">
-        <v>813316</v>
+        <v>813305</v>
       </c>
       <c r="B329" s="1" t="s">
         <v>335</v>
@@ -12127,7 +12136,7 @@
         <v>2</v>
       </c>
       <c r="F329" s="3" t="n">
-        <v>3000</v>
+        <v>928</v>
       </c>
       <c r="G329" s="3" t="n">
         <v>0</v>
@@ -12144,7 +12153,7 @@
     </row>
     <row r="330" customHeight="1" ht="15" spans="1:10">
       <c r="A330" s="1" t="n">
-        <v>813315</v>
+        <v>813269</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>336</v>
@@ -12159,7 +12168,7 @@
         <v>2</v>
       </c>
       <c r="F330" s="3" t="n">
-        <v>2400</v>
+        <v>372</v>
       </c>
       <c r="G330" s="3" t="n">
         <v>0</v>
@@ -12176,7 +12185,7 @@
     </row>
     <row r="331" customHeight="1" ht="15" spans="1:10">
       <c r="A331" s="1" t="n">
-        <v>813469</v>
+        <v>813316</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>337</v>
@@ -12191,7 +12200,7 @@
         <v>2</v>
       </c>
       <c r="F331" s="3" t="n">
-        <v>5590</v>
+        <v>3000</v>
       </c>
       <c r="G331" s="3" t="n">
         <v>0</v>
@@ -12208,7 +12217,7 @@
     </row>
     <row r="332" customHeight="1" ht="15" spans="1:10">
       <c r="A332" s="1" t="n">
-        <v>813470</v>
+        <v>813315</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>338</v>
@@ -12223,7 +12232,7 @@
         <v>2</v>
       </c>
       <c r="F332" s="3" t="n">
-        <v>5590</v>
+        <v>2400</v>
       </c>
       <c r="G332" s="3" t="n">
         <v>0</v>
@@ -12240,7 +12249,7 @@
     </row>
     <row r="333" customHeight="1" ht="15" spans="1:10">
       <c r="A333" s="1" t="n">
-        <v>804539</v>
+        <v>813469</v>
       </c>
       <c r="B333" s="1" t="s">
         <v>339</v>
@@ -12255,7 +12264,7 @@
         <v>2</v>
       </c>
       <c r="F333" s="3" t="n">
-        <v>38756</v>
+        <v>5590</v>
       </c>
       <c r="G333" s="3" t="n">
         <v>0</v>
@@ -12272,7 +12281,7 @@
     </row>
     <row r="334" customHeight="1" ht="15" spans="1:10">
       <c r="A334" s="1" t="n">
-        <v>804034</v>
+        <v>813470</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>340</v>
@@ -12287,7 +12296,7 @@
         <v>2</v>
       </c>
       <c r="F334" s="3" t="n">
-        <v>12587</v>
+        <v>5590</v>
       </c>
       <c r="G334" s="3" t="n">
         <v>0</v>
@@ -12304,7 +12313,7 @@
     </row>
     <row r="335" customHeight="1" ht="15" spans="1:10">
       <c r="A335" s="1" t="n">
-        <v>804499</v>
+        <v>804539</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>341</v>
@@ -12319,7 +12328,7 @@
         <v>2</v>
       </c>
       <c r="F335" s="3" t="n">
-        <v>36583</v>
+        <v>38666</v>
       </c>
       <c r="G335" s="3" t="n">
         <v>0</v>
@@ -12336,7 +12345,7 @@
     </row>
     <row r="336" customHeight="1" ht="15" spans="1:10">
       <c r="A336" s="1" t="n">
-        <v>804598</v>
+        <v>804034</v>
       </c>
       <c r="B336" s="1" t="s">
         <v>342</v>
@@ -12351,7 +12360,7 @@
         <v>2</v>
       </c>
       <c r="F336" s="3" t="n">
-        <v>17639</v>
+        <v>16857</v>
       </c>
       <c r="G336" s="3" t="n">
         <v>0</v>
@@ -12368,7 +12377,7 @@
     </row>
     <row r="337" customHeight="1" ht="15" spans="1:10">
       <c r="A337" s="1" t="n">
-        <v>813236</v>
+        <v>804499</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>343</v>
@@ -12383,7 +12392,7 @@
         <v>2</v>
       </c>
       <c r="F337" s="3" t="n">
-        <v>3004</v>
+        <v>36583</v>
       </c>
       <c r="G337" s="3" t="n">
         <v>0</v>
@@ -12400,7 +12409,7 @@
     </row>
     <row r="338" customHeight="1" ht="15" spans="1:10">
       <c r="A338" s="1" t="n">
-        <v>804530</v>
+        <v>804598</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>344</v>
@@ -12415,7 +12424,7 @@
         <v>2</v>
       </c>
       <c r="F338" s="3" t="n">
-        <v>4452</v>
+        <v>13920</v>
       </c>
       <c r="G338" s="3" t="n">
         <v>0</v>
@@ -12432,7 +12441,7 @@
     </row>
     <row r="339" customHeight="1" ht="15" spans="1:10">
       <c r="A339" s="1" t="n">
-        <v>804531</v>
+        <v>813236</v>
       </c>
       <c r="B339" s="1" t="s">
         <v>345</v>
@@ -12447,7 +12456,7 @@
         <v>2</v>
       </c>
       <c r="F339" s="3" t="n">
-        <v>5080</v>
+        <v>3004</v>
       </c>
       <c r="G339" s="3" t="n">
         <v>0</v>
@@ -12464,7 +12473,7 @@
     </row>
     <row r="340" customHeight="1" ht="15" spans="1:10">
       <c r="A340" s="1" t="n">
-        <v>804502</v>
+        <v>804530</v>
       </c>
       <c r="B340" s="1" t="s">
         <v>346</v>
@@ -12479,7 +12488,7 @@
         <v>2</v>
       </c>
       <c r="F340" s="3" t="n">
-        <v>2259</v>
+        <v>4452</v>
       </c>
       <c r="G340" s="3" t="n">
         <v>0</v>
@@ -12496,7 +12505,7 @@
     </row>
     <row r="341" customHeight="1" ht="15" spans="1:10">
       <c r="A341" s="1" t="n">
-        <v>804498</v>
+        <v>804531</v>
       </c>
       <c r="B341" s="1" t="s">
         <v>347</v>
@@ -12511,7 +12520,7 @@
         <v>2</v>
       </c>
       <c r="F341" s="3" t="n">
-        <v>4575</v>
+        <v>5080</v>
       </c>
       <c r="G341" s="3" t="n">
         <v>0</v>
@@ -12528,7 +12537,7 @@
     </row>
     <row r="342" customHeight="1" ht="15" spans="1:10">
       <c r="A342" s="1" t="n">
-        <v>804117</v>
+        <v>804502</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>348</v>
@@ -12543,7 +12552,7 @@
         <v>2</v>
       </c>
       <c r="F342" s="3" t="n">
-        <v>49338</v>
+        <v>2259</v>
       </c>
       <c r="G342" s="3" t="n">
         <v>0</v>
@@ -12560,7 +12569,7 @@
     </row>
     <row r="343" customHeight="1" ht="15" spans="1:10">
       <c r="A343" s="1" t="n">
-        <v>804588</v>
+        <v>804498</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>349</v>
@@ -12575,7 +12584,7 @@
         <v>2</v>
       </c>
       <c r="F343" s="3" t="n">
-        <v>3263</v>
+        <v>4575</v>
       </c>
       <c r="G343" s="3" t="n">
         <v>0</v>
@@ -12592,7 +12601,7 @@
     </row>
     <row r="344" customHeight="1" ht="15" spans="1:10">
       <c r="A344" s="1" t="n">
-        <v>804209</v>
+        <v>804117</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>350</v>
@@ -12607,7 +12616,7 @@
         <v>2</v>
       </c>
       <c r="F344" s="3" t="n">
-        <v>980</v>
+        <v>44266</v>
       </c>
       <c r="G344" s="3" t="n">
         <v>0</v>
@@ -12624,7 +12633,7 @@
     </row>
     <row r="345" customHeight="1" ht="15" spans="1:10">
       <c r="A345" s="1" t="n">
-        <v>804250</v>
+        <v>804588</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>351</v>
@@ -12639,7 +12648,7 @@
         <v>2</v>
       </c>
       <c r="F345" s="3" t="n">
-        <v>3600</v>
+        <v>3263</v>
       </c>
       <c r="G345" s="3" t="n">
         <v>0</v>
@@ -12656,7 +12665,7 @@
     </row>
     <row r="346" customHeight="1" ht="15" spans="1:10">
       <c r="A346" s="1" t="n">
-        <v>804249</v>
+        <v>804209</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>352</v>
@@ -12671,7 +12680,7 @@
         <v>2</v>
       </c>
       <c r="F346" s="3" t="n">
-        <v>2306</v>
+        <v>980</v>
       </c>
       <c r="G346" s="3" t="n">
         <v>0</v>
@@ -12688,7 +12697,7 @@
     </row>
     <row r="347" customHeight="1" ht="15" spans="1:10">
       <c r="A347" s="1" t="n">
-        <v>804589</v>
+        <v>804250</v>
       </c>
       <c r="B347" s="1" t="s">
         <v>353</v>
@@ -12703,7 +12712,7 @@
         <v>2</v>
       </c>
       <c r="F347" s="3" t="n">
-        <v>975</v>
+        <v>3600</v>
       </c>
       <c r="G347" s="3" t="n">
         <v>0</v>
@@ -12720,7 +12729,7 @@
     </row>
     <row r="348" customHeight="1" ht="15" spans="1:10">
       <c r="A348" s="1" t="n">
-        <v>804228</v>
+        <v>804249</v>
       </c>
       <c r="B348" s="1" t="s">
         <v>354</v>
@@ -12735,7 +12744,7 @@
         <v>2</v>
       </c>
       <c r="F348" s="3" t="n">
-        <v>1680</v>
+        <v>2306</v>
       </c>
       <c r="G348" s="3" t="n">
         <v>0</v>
@@ -12752,7 +12761,7 @@
     </row>
     <row r="349" customHeight="1" ht="15" spans="1:10">
       <c r="A349" s="1" t="n">
-        <v>804328</v>
+        <v>804589</v>
       </c>
       <c r="B349" s="1" t="s">
         <v>355</v>
@@ -12767,7 +12776,7 @@
         <v>2</v>
       </c>
       <c r="F349" s="3" t="n">
-        <v>24431</v>
+        <v>975</v>
       </c>
       <c r="G349" s="3" t="n">
         <v>0</v>
@@ -12784,7 +12793,7 @@
     </row>
     <row r="350" customHeight="1" ht="15" spans="1:10">
       <c r="A350" s="1" t="n">
-        <v>804035</v>
+        <v>804228</v>
       </c>
       <c r="B350" s="1" t="s">
         <v>356</v>
@@ -12799,7 +12808,7 @@
         <v>2</v>
       </c>
       <c r="F350" s="3" t="n">
-        <v>5093</v>
+        <v>1680</v>
       </c>
       <c r="G350" s="3" t="n">
         <v>0</v>
@@ -12816,7 +12825,7 @@
     </row>
     <row r="351" customHeight="1" ht="15" spans="1:10">
       <c r="A351" s="1" t="n">
-        <v>804438</v>
+        <v>804328</v>
       </c>
       <c r="B351" s="1" t="s">
         <v>357</v>
@@ -12831,7 +12840,7 @@
         <v>2</v>
       </c>
       <c r="F351" s="3" t="n">
-        <v>4229</v>
+        <v>24431</v>
       </c>
       <c r="G351" s="3" t="n">
         <v>0</v>
@@ -12848,7 +12857,7 @@
     </row>
     <row r="352" customHeight="1" ht="15" spans="1:10">
       <c r="A352" s="1" t="n">
-        <v>804048</v>
+        <v>804035</v>
       </c>
       <c r="B352" s="1" t="s">
         <v>358</v>
@@ -12863,7 +12872,7 @@
         <v>2</v>
       </c>
       <c r="F352" s="3" t="n">
-        <v>6008</v>
+        <v>4579</v>
       </c>
       <c r="G352" s="3" t="n">
         <v>0</v>
@@ -12880,7 +12889,7 @@
     </row>
     <row r="353" customHeight="1" ht="15" spans="1:10">
       <c r="A353" s="1" t="n">
-        <v>804454</v>
+        <v>804438</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>359</v>
@@ -12895,7 +12904,7 @@
         <v>2</v>
       </c>
       <c r="F353" s="3" t="n">
-        <v>10441</v>
+        <v>4229</v>
       </c>
       <c r="G353" s="3" t="n">
         <v>0</v>
@@ -12912,7 +12921,7 @@
     </row>
     <row r="354" customHeight="1" ht="15" spans="1:10">
       <c r="A354" s="1" t="n">
-        <v>804465</v>
+        <v>804048</v>
       </c>
       <c r="B354" s="1" t="s">
         <v>360</v>
@@ -12927,7 +12936,7 @@
         <v>2</v>
       </c>
       <c r="F354" s="3" t="n">
-        <v>3010</v>
+        <v>4930</v>
       </c>
       <c r="G354" s="3" t="n">
         <v>0</v>
@@ -12944,7 +12953,7 @@
     </row>
     <row r="355" customHeight="1" ht="15" spans="1:10">
       <c r="A355" s="1" t="n">
-        <v>807015</v>
+        <v>804454</v>
       </c>
       <c r="B355" s="1" t="s">
         <v>361</v>
@@ -12959,7 +12968,7 @@
         <v>2</v>
       </c>
       <c r="F355" s="3" t="n">
-        <v>13624</v>
+        <v>10441</v>
       </c>
       <c r="G355" s="3" t="n">
         <v>0</v>
@@ -12976,7 +12985,7 @@
     </row>
     <row r="356" customHeight="1" ht="15" spans="1:10">
       <c r="A356" s="1" t="n">
-        <v>813277</v>
+        <v>804465</v>
       </c>
       <c r="B356" s="1" t="s">
         <v>362</v>
@@ -12991,7 +13000,7 @@
         <v>2</v>
       </c>
       <c r="F356" s="3" t="n">
-        <v>4103</v>
+        <v>903</v>
       </c>
       <c r="G356" s="3" t="n">
         <v>0</v>
@@ -13008,7 +13017,7 @@
     </row>
     <row r="357" customHeight="1" ht="15" spans="1:10">
       <c r="A357" s="1" t="n">
-        <v>813263</v>
+        <v>807015</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>363</v>
@@ -13023,7 +13032,7 @@
         <v>2</v>
       </c>
       <c r="F357" s="3" t="n">
-        <v>12600</v>
+        <v>13725</v>
       </c>
       <c r="G357" s="3" t="n">
         <v>0</v>
@@ -13040,7 +13049,7 @@
     </row>
     <row r="358" customHeight="1" ht="15" spans="1:10">
       <c r="A358" s="1" t="n">
-        <v>411015</v>
+        <v>813277</v>
       </c>
       <c r="B358" s="1" t="s">
         <v>364</v>
@@ -13055,7 +13064,7 @@
         <v>2</v>
       </c>
       <c r="F358" s="3" t="n">
-        <v>1306</v>
+        <v>3453</v>
       </c>
       <c r="G358" s="3" t="n">
         <v>0</v>
@@ -13072,7 +13081,7 @@
     </row>
     <row r="359" customHeight="1" ht="15" spans="1:10">
       <c r="A359" s="1" t="n">
-        <v>813472</v>
+        <v>813263</v>
       </c>
       <c r="B359" s="1" t="s">
         <v>365</v>
@@ -13087,7 +13096,7 @@
         <v>2</v>
       </c>
       <c r="F359" s="3" t="n">
-        <v>3217</v>
+        <v>12600</v>
       </c>
       <c r="G359" s="3" t="n">
         <v>0</v>
@@ -13104,7 +13113,7 @@
     </row>
     <row r="360" customHeight="1" ht="15" spans="1:10">
       <c r="A360" s="1" t="n">
-        <v>813473</v>
+        <v>411015</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>366</v>
@@ -13119,7 +13128,7 @@
         <v>2</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>3190</v>
+        <v>1306</v>
       </c>
       <c r="G360" s="3" t="n">
         <v>0</v>
@@ -13136,7 +13145,7 @@
     </row>
     <row r="361" customHeight="1" ht="15" spans="1:10">
       <c r="A361" s="1" t="n">
-        <v>804440</v>
+        <v>813472</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>367</v>
@@ -13151,7 +13160,7 @@
         <v>2</v>
       </c>
       <c r="F361" s="3" t="n">
-        <v>2288</v>
+        <v>3217</v>
       </c>
       <c r="G361" s="3" t="n">
         <v>0</v>
@@ -13168,7 +13177,7 @@
     </row>
     <row r="362" customHeight="1" ht="15" spans="1:10">
       <c r="A362" s="1" t="n">
-        <v>804093</v>
+        <v>813473</v>
       </c>
       <c r="B362" s="1" t="s">
         <v>368</v>
@@ -13183,7 +13192,7 @@
         <v>2</v>
       </c>
       <c r="F362" s="3" t="n">
-        <v>15979</v>
+        <v>3190</v>
       </c>
       <c r="G362" s="3" t="n">
         <v>0</v>
@@ -13200,7 +13209,7 @@
     </row>
     <row r="363" customHeight="1" ht="15" spans="1:10">
       <c r="A363" s="1" t="n">
-        <v>804388</v>
+        <v>804440</v>
       </c>
       <c r="B363" s="1" t="s">
         <v>369</v>
@@ -13215,7 +13224,7 @@
         <v>2</v>
       </c>
       <c r="F363" s="3" t="n">
-        <v>8801</v>
+        <v>2288</v>
       </c>
       <c r="G363" s="3" t="n">
         <v>0</v>
@@ -13232,7 +13241,7 @@
     </row>
     <row r="364" customHeight="1" ht="15" spans="1:10">
       <c r="A364" s="1" t="n">
-        <v>804095</v>
+        <v>804093</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>370</v>
@@ -13247,7 +13256,7 @@
         <v>2</v>
       </c>
       <c r="F364" s="3" t="n">
-        <v>7676</v>
+        <v>15979</v>
       </c>
       <c r="G364" s="3" t="n">
         <v>0</v>
@@ -13264,7 +13273,7 @@
     </row>
     <row r="365" customHeight="1" ht="15" spans="1:10">
       <c r="A365" s="1" t="n">
-        <v>811761</v>
+        <v>804388</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>371</v>
@@ -13279,7 +13288,7 @@
         <v>2</v>
       </c>
       <c r="F365" s="3" t="n">
-        <v>500</v>
+        <v>8801</v>
       </c>
       <c r="G365" s="3" t="n">
         <v>0</v>
@@ -13296,7 +13305,7 @@
     </row>
     <row r="366" customHeight="1" ht="15" spans="1:10">
       <c r="A366" s="1" t="n">
-        <v>804428</v>
+        <v>804095</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>372</v>
@@ -13311,7 +13320,7 @@
         <v>2</v>
       </c>
       <c r="F366" s="3" t="n">
-        <v>50618</v>
+        <v>5244</v>
       </c>
       <c r="G366" s="3" t="n">
         <v>0</v>
@@ -13328,22 +13337,22 @@
     </row>
     <row r="367" customHeight="1" ht="15" spans="1:10">
       <c r="A367" s="1" t="n">
-        <v>204027</v>
+        <v>811761</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>373</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>374</v>
+        <v>2</v>
       </c>
       <c r="F367" s="3" t="n">
-        <v>27.091437</v>
+        <v>500</v>
       </c>
       <c r="G367" s="3" t="n">
         <v>0</v>
@@ -13360,22 +13369,22 @@
     </row>
     <row r="368" customHeight="1" ht="15" spans="1:10">
       <c r="A368" s="1" t="n">
-        <v>204028</v>
+        <v>804428</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>374</v>
+        <v>2</v>
       </c>
       <c r="F368" s="3" t="n">
-        <v>132.636982</v>
+        <v>50618</v>
       </c>
       <c r="G368" s="3" t="n">
         <v>0</v>
@@ -13392,10 +13401,10 @@
     </row>
     <row r="369" customHeight="1" ht="15" spans="1:10">
       <c r="A369" s="1" t="n">
-        <v>204009</v>
+        <v>204027</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -13404,10 +13413,10 @@
         <v>1</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F369" s="3" t="n">
-        <v>8211.995709</v>
+        <v>27.091437</v>
       </c>
       <c r="G369" s="3" t="n">
         <v>0</v>
@@ -13424,7 +13433,7 @@
     </row>
     <row r="370" customHeight="1" ht="15" spans="1:10">
       <c r="A370" s="1" t="n">
-        <v>204023</v>
+        <v>204028</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>377</v>
@@ -13436,10 +13445,10 @@
         <v>1</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F370" s="3" t="n">
-        <v>381.705057</v>
+        <v>132.636982</v>
       </c>
       <c r="G370" s="3" t="n">
         <v>0</v>
@@ -13456,7 +13465,7 @@
     </row>
     <row r="371" customHeight="1" ht="15" spans="1:10">
       <c r="A371" s="1" t="n">
-        <v>204030</v>
+        <v>204009</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>378</v>
@@ -13468,10 +13477,10 @@
         <v>1</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F371" s="3" t="n">
-        <v>363.963308</v>
+        <v>8211.565709</v>
       </c>
       <c r="G371" s="3" t="n">
         <v>0</v>
@@ -13488,7 +13497,7 @@
     </row>
     <row r="372" customHeight="1" ht="15" spans="1:10">
       <c r="A372" s="1" t="n">
-        <v>204029</v>
+        <v>204023</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>379</v>
@@ -13500,10 +13509,10 @@
         <v>1</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F372" s="3" t="n">
-        <v>106.989603</v>
+        <v>381.705057</v>
       </c>
       <c r="G372" s="3" t="n">
         <v>0</v>
@@ -13520,22 +13529,22 @@
     </row>
     <row r="373" customHeight="1" ht="15" spans="1:10">
       <c r="A373" s="1" t="n">
-        <v>804556</v>
+        <v>204030</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>380</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>2</v>
+        <v>376</v>
       </c>
       <c r="F373" s="3" t="n">
-        <v>1441</v>
+        <v>363.963308</v>
       </c>
       <c r="G373" s="3" t="n">
         <v>0</v>
@@ -13552,22 +13561,22 @@
     </row>
     <row r="374" customHeight="1" ht="15" spans="1:10">
       <c r="A374" s="1" t="n">
-        <v>813578</v>
+        <v>204029</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>381</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>2</v>
+        <v>376</v>
       </c>
       <c r="F374" s="3" t="n">
-        <v>80</v>
+        <v>106.989603</v>
       </c>
       <c r="G374" s="3" t="n">
         <v>0</v>
@@ -13584,7 +13593,7 @@
     </row>
     <row r="375" customHeight="1" ht="15" spans="1:10">
       <c r="A375" s="1" t="n">
-        <v>804041</v>
+        <v>804556</v>
       </c>
       <c r="B375" s="1" t="s">
         <v>382</v>
@@ -13599,7 +13608,7 @@
         <v>2</v>
       </c>
       <c r="F375" s="3" t="n">
-        <v>7525</v>
+        <v>1441</v>
       </c>
       <c r="G375" s="3" t="n">
         <v>0</v>
@@ -13616,7 +13625,7 @@
     </row>
     <row r="376" customHeight="1" ht="15" spans="1:10">
       <c r="A376" s="1" t="n">
-        <v>804026</v>
+        <v>813578</v>
       </c>
       <c r="B376" s="1" t="s">
         <v>383</v>
@@ -13631,7 +13640,7 @@
         <v>2</v>
       </c>
       <c r="F376" s="3" t="n">
-        <v>875</v>
+        <v>80</v>
       </c>
       <c r="G376" s="3" t="n">
         <v>0</v>
@@ -13648,7 +13657,7 @@
     </row>
     <row r="377" customHeight="1" ht="15" spans="1:10">
       <c r="A377" s="1" t="n">
-        <v>804025</v>
+        <v>804041</v>
       </c>
       <c r="B377" s="1" t="s">
         <v>384</v>
@@ -13663,7 +13672,7 @@
         <v>2</v>
       </c>
       <c r="F377" s="3" t="n">
-        <v>12750</v>
+        <v>7525</v>
       </c>
       <c r="G377" s="3" t="n">
         <v>0</v>
@@ -13680,7 +13689,7 @@
     </row>
     <row r="378" customHeight="1" ht="15" spans="1:10">
       <c r="A378" s="1" t="n">
-        <v>804024</v>
+        <v>804026</v>
       </c>
       <c r="B378" s="1" t="s">
         <v>385</v>
@@ -13695,7 +13704,7 @@
         <v>2</v>
       </c>
       <c r="F378" s="3" t="n">
-        <v>23390</v>
+        <v>905</v>
       </c>
       <c r="G378" s="3" t="n">
         <v>0</v>
@@ -13712,7 +13721,7 @@
     </row>
     <row r="379" customHeight="1" ht="15" spans="1:10">
       <c r="A379" s="1" t="n">
-        <v>804090</v>
+        <v>804025</v>
       </c>
       <c r="B379" s="1" t="s">
         <v>386</v>
@@ -13727,7 +13736,7 @@
         <v>2</v>
       </c>
       <c r="F379" s="3" t="n">
-        <v>25925</v>
+        <v>12750</v>
       </c>
       <c r="G379" s="3" t="n">
         <v>0</v>
@@ -13744,7 +13753,7 @@
     </row>
     <row r="380" customHeight="1" ht="15" spans="1:10">
       <c r="A380" s="1" t="n">
-        <v>804089</v>
+        <v>804024</v>
       </c>
       <c r="B380" s="1" t="s">
         <v>387</v>
@@ -13759,7 +13768,7 @@
         <v>2</v>
       </c>
       <c r="F380" s="3" t="n">
-        <v>6553</v>
+        <v>22340</v>
       </c>
       <c r="G380" s="3" t="n">
         <v>0</v>
@@ -13776,7 +13785,7 @@
     </row>
     <row r="381" customHeight="1" ht="15" spans="1:10">
       <c r="A381" s="1" t="n">
-        <v>804500</v>
+        <v>804090</v>
       </c>
       <c r="B381" s="1" t="s">
         <v>388</v>
@@ -13791,7 +13800,7 @@
         <v>2</v>
       </c>
       <c r="F381" s="3" t="n">
-        <v>1408</v>
+        <v>25925</v>
       </c>
       <c r="G381" s="3" t="n">
         <v>0</v>
@@ -13808,7 +13817,7 @@
     </row>
     <row r="382" customHeight="1" ht="15" spans="1:10">
       <c r="A382" s="1" t="n">
-        <v>804505</v>
+        <v>804089</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>389</v>
@@ -13823,7 +13832,7 @@
         <v>2</v>
       </c>
       <c r="F382" s="3" t="n">
-        <v>1132</v>
+        <v>6553</v>
       </c>
       <c r="G382" s="3" t="n">
         <v>0</v>
@@ -13840,7 +13849,7 @@
     </row>
     <row r="383" customHeight="1" ht="15" spans="1:10">
       <c r="A383" s="1" t="n">
-        <v>804101</v>
+        <v>804500</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>390</v>
@@ -13855,7 +13864,7 @@
         <v>2</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>19191</v>
+        <v>768</v>
       </c>
       <c r="G383" s="3" t="n">
         <v>0</v>
@@ -13872,7 +13881,7 @@
     </row>
     <row r="384" customHeight="1" ht="15" spans="1:10">
       <c r="A384" s="1" t="n">
-        <v>804102</v>
+        <v>804505</v>
       </c>
       <c r="B384" s="1" t="s">
         <v>391</v>
@@ -13887,7 +13896,7 @@
         <v>2</v>
       </c>
       <c r="F384" s="3" t="n">
-        <v>17315</v>
+        <v>1132</v>
       </c>
       <c r="G384" s="3" t="n">
         <v>0</v>
@@ -13904,7 +13913,7 @@
     </row>
     <row r="385" customHeight="1" ht="15" spans="1:10">
       <c r="A385" s="1" t="n">
-        <v>813331</v>
+        <v>804101</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>392</v>
@@ -13919,7 +13928,7 @@
         <v>2</v>
       </c>
       <c r="F385" s="3" t="n">
-        <v>21320</v>
+        <v>19191</v>
       </c>
       <c r="G385" s="3" t="n">
         <v>0</v>
@@ -13936,7 +13945,7 @@
     </row>
     <row r="386" customHeight="1" ht="15" spans="1:10">
       <c r="A386" s="1" t="n">
-        <v>804229</v>
+        <v>804102</v>
       </c>
       <c r="B386" s="1" t="s">
         <v>393</v>
@@ -13951,7 +13960,7 @@
         <v>2</v>
       </c>
       <c r="F386" s="3" t="n">
-        <v>1001</v>
+        <v>17315</v>
       </c>
       <c r="G386" s="3" t="n">
         <v>0</v>
@@ -13968,7 +13977,7 @@
     </row>
     <row r="387" customHeight="1" ht="15" spans="1:10">
       <c r="A387" s="1" t="n">
-        <v>804484</v>
+        <v>804255</v>
       </c>
       <c r="B387" s="1" t="s">
         <v>394</v>
@@ -13983,7 +13992,7 @@
         <v>2</v>
       </c>
       <c r="F387" s="3" t="n">
-        <v>13313</v>
+        <v>1480</v>
       </c>
       <c r="G387" s="3" t="n">
         <v>0</v>
@@ -14000,7 +14009,7 @@
     </row>
     <row r="388" customHeight="1" ht="15" spans="1:10">
       <c r="A388" s="1" t="n">
-        <v>813508</v>
+        <v>813331</v>
       </c>
       <c r="B388" s="1" t="s">
         <v>395</v>
@@ -14015,7 +14024,7 @@
         <v>2</v>
       </c>
       <c r="F388" s="3" t="n">
-        <v>14702</v>
+        <v>20246</v>
       </c>
       <c r="G388" s="3" t="n">
         <v>0</v>
@@ -14032,7 +14041,7 @@
     </row>
     <row r="389" customHeight="1" ht="15" spans="1:10">
       <c r="A389" s="1" t="n">
-        <v>813144</v>
+        <v>804229</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>396</v>
@@ -14047,7 +14056,7 @@
         <v>2</v>
       </c>
       <c r="F389" s="3" t="n">
-        <v>18473</v>
+        <v>8949</v>
       </c>
       <c r="G389" s="3" t="n">
         <v>0</v>
@@ -14064,7 +14073,7 @@
     </row>
     <row r="390" customHeight="1" ht="15" spans="1:10">
       <c r="A390" s="1" t="n">
-        <v>804579</v>
+        <v>804484</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>397</v>
@@ -14079,7 +14088,7 @@
         <v>2</v>
       </c>
       <c r="F390" s="3" t="n">
-        <v>2758</v>
+        <v>11359</v>
       </c>
       <c r="G390" s="3" t="n">
         <v>0</v>
@@ -14096,7 +14105,7 @@
     </row>
     <row r="391" customHeight="1" ht="15" spans="1:10">
       <c r="A391" s="1" t="n">
-        <v>804568</v>
+        <v>813508</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>398</v>
@@ -14111,7 +14120,7 @@
         <v>2</v>
       </c>
       <c r="F391" s="3" t="n">
-        <v>5097</v>
+        <v>14702</v>
       </c>
       <c r="G391" s="3" t="n">
         <v>0</v>
@@ -14128,7 +14137,7 @@
     </row>
     <row r="392" customHeight="1" ht="15" spans="1:10">
       <c r="A392" s="1" t="n">
-        <v>813267</v>
+        <v>813144</v>
       </c>
       <c r="B392" s="1" t="s">
         <v>399</v>
@@ -14143,7 +14152,7 @@
         <v>2</v>
       </c>
       <c r="F392" s="3" t="n">
-        <v>22046</v>
+        <v>18473</v>
       </c>
       <c r="G392" s="3" t="n">
         <v>0</v>
@@ -14160,7 +14169,7 @@
     </row>
     <row r="393" customHeight="1" ht="15" spans="1:10">
       <c r="A393" s="1" t="n">
-        <v>813051</v>
+        <v>804579</v>
       </c>
       <c r="B393" s="1" t="s">
         <v>400</v>
@@ -14175,7 +14184,7 @@
         <v>2</v>
       </c>
       <c r="F393" s="3" t="n">
-        <v>17822</v>
+        <v>2758</v>
       </c>
       <c r="G393" s="3" t="n">
         <v>0</v>
@@ -14192,7 +14201,7 @@
     </row>
     <row r="394" customHeight="1" ht="15" spans="1:10">
       <c r="A394" s="1" t="n">
-        <v>804483</v>
+        <v>804568</v>
       </c>
       <c r="B394" s="1" t="s">
         <v>401</v>
@@ -14207,7 +14216,7 @@
         <v>2</v>
       </c>
       <c r="F394" s="3" t="n">
-        <v>3570</v>
+        <v>5097</v>
       </c>
       <c r="G394" s="3" t="n">
         <v>0</v>
@@ -14224,7 +14233,7 @@
     </row>
     <row r="395" customHeight="1" ht="15" spans="1:10">
       <c r="A395" s="1" t="n">
-        <v>804482</v>
+        <v>813267</v>
       </c>
       <c r="B395" s="1" t="s">
         <v>402</v>
@@ -14239,7 +14248,7 @@
         <v>2</v>
       </c>
       <c r="F395" s="3" t="n">
-        <v>11931</v>
+        <v>22046</v>
       </c>
       <c r="G395" s="3" t="n">
         <v>0</v>
@@ -14256,7 +14265,7 @@
     </row>
     <row r="396" customHeight="1" ht="15" spans="1:10">
       <c r="A396" s="1" t="n">
-        <v>804403</v>
+        <v>813051</v>
       </c>
       <c r="B396" s="1" t="s">
         <v>403</v>
@@ -14271,7 +14280,7 @@
         <v>2</v>
       </c>
       <c r="F396" s="3" t="n">
-        <v>2095</v>
+        <v>14377</v>
       </c>
       <c r="G396" s="3" t="n">
         <v>0</v>
@@ -14288,7 +14297,7 @@
     </row>
     <row r="397" customHeight="1" ht="15" spans="1:10">
       <c r="A397" s="1" t="n">
-        <v>804533</v>
+        <v>804483</v>
       </c>
       <c r="B397" s="1" t="s">
         <v>404</v>
@@ -14303,7 +14312,7 @@
         <v>2</v>
       </c>
       <c r="F397" s="3" t="n">
-        <v>695</v>
+        <v>3570</v>
       </c>
       <c r="G397" s="3" t="n">
         <v>0</v>
@@ -14320,7 +14329,7 @@
     </row>
     <row r="398" customHeight="1" ht="15" spans="1:10">
       <c r="A398" s="1" t="n">
-        <v>804613</v>
+        <v>804482</v>
       </c>
       <c r="B398" s="1" t="s">
         <v>405</v>
@@ -14335,7 +14344,7 @@
         <v>2</v>
       </c>
       <c r="F398" s="3" t="n">
-        <v>122</v>
+        <v>11931</v>
       </c>
       <c r="G398" s="3" t="n">
         <v>0</v>
@@ -14352,7 +14361,7 @@
     </row>
     <row r="399" customHeight="1" ht="15" spans="1:10">
       <c r="A399" s="1" t="n">
-        <v>804038</v>
+        <v>804403</v>
       </c>
       <c r="B399" s="1" t="s">
         <v>406</v>
@@ -14367,7 +14376,7 @@
         <v>2</v>
       </c>
       <c r="F399" s="3" t="n">
-        <v>6926</v>
+        <v>2095</v>
       </c>
       <c r="G399" s="3" t="n">
         <v>0</v>
@@ -14384,7 +14393,7 @@
     </row>
     <row r="400" customHeight="1" ht="15" spans="1:10">
       <c r="A400" s="1" t="n">
-        <v>804434</v>
+        <v>804533</v>
       </c>
       <c r="B400" s="1" t="s">
         <v>407</v>
@@ -14399,7 +14408,7 @@
         <v>2</v>
       </c>
       <c r="F400" s="3" t="n">
-        <v>3481</v>
+        <v>695</v>
       </c>
       <c r="G400" s="3" t="n">
         <v>0</v>
@@ -14416,7 +14425,7 @@
     </row>
     <row r="401" customHeight="1" ht="15" spans="1:10">
       <c r="A401" s="1" t="n">
-        <v>804040</v>
+        <v>804613</v>
       </c>
       <c r="B401" s="1" t="s">
         <v>408</v>
@@ -14431,7 +14440,7 @@
         <v>2</v>
       </c>
       <c r="F401" s="3" t="n">
-        <v>2843</v>
+        <v>122</v>
       </c>
       <c r="G401" s="3" t="n">
         <v>0</v>
@@ -14448,7 +14457,7 @@
     </row>
     <row r="402" customHeight="1" ht="15" spans="1:10">
       <c r="A402" s="1" t="n">
-        <v>813541</v>
+        <v>804038</v>
       </c>
       <c r="B402" s="1" t="s">
         <v>409</v>
@@ -14463,7 +14472,7 @@
         <v>2</v>
       </c>
       <c r="F402" s="3" t="n">
-        <v>3352</v>
+        <v>6926</v>
       </c>
       <c r="G402" s="3" t="n">
         <v>0</v>
@@ -14480,7 +14489,7 @@
     </row>
     <row r="403" customHeight="1" ht="15" spans="1:10">
       <c r="A403" s="1" t="n">
-        <v>804545</v>
+        <v>804434</v>
       </c>
       <c r="B403" s="1" t="s">
         <v>410</v>
@@ -14495,7 +14504,7 @@
         <v>2</v>
       </c>
       <c r="F403" s="3" t="n">
-        <v>5994</v>
+        <v>3481</v>
       </c>
       <c r="G403" s="3" t="n">
         <v>0</v>
@@ -14512,7 +14521,7 @@
     </row>
     <row r="404" customHeight="1" ht="15" spans="1:10">
       <c r="A404" s="1" t="n">
-        <v>804439</v>
+        <v>804040</v>
       </c>
       <c r="B404" s="1" t="s">
         <v>411</v>
@@ -14527,7 +14536,7 @@
         <v>2</v>
       </c>
       <c r="F404" s="3" t="n">
-        <v>1720</v>
+        <v>2441</v>
       </c>
       <c r="G404" s="3" t="n">
         <v>0</v>
@@ -14544,7 +14553,7 @@
     </row>
     <row r="405" customHeight="1" ht="15" spans="1:10">
       <c r="A405" s="1" t="n">
-        <v>804094</v>
+        <v>813541</v>
       </c>
       <c r="B405" s="1" t="s">
         <v>412</v>
@@ -14559,7 +14568,7 @@
         <v>2</v>
       </c>
       <c r="F405" s="3" t="n">
-        <v>11141</v>
+        <v>3352</v>
       </c>
       <c r="G405" s="3" t="n">
         <v>0</v>
@@ -14576,7 +14585,7 @@
     </row>
     <row r="406" customHeight="1" ht="15" spans="1:10">
       <c r="A406" s="1" t="n">
-        <v>804390</v>
+        <v>804545</v>
       </c>
       <c r="B406" s="1" t="s">
         <v>413</v>
@@ -14591,7 +14600,7 @@
         <v>2</v>
       </c>
       <c r="F406" s="3" t="n">
-        <v>4657</v>
+        <v>5994</v>
       </c>
       <c r="G406" s="3" t="n">
         <v>0</v>
@@ -14608,7 +14617,7 @@
     </row>
     <row r="407" customHeight="1" ht="15" spans="1:10">
       <c r="A407" s="1" t="n">
-        <v>804096</v>
+        <v>804439</v>
       </c>
       <c r="B407" s="1" t="s">
         <v>414</v>
@@ -14623,7 +14632,7 @@
         <v>2</v>
       </c>
       <c r="F407" s="3" t="n">
-        <v>22542</v>
+        <v>1720</v>
       </c>
       <c r="G407" s="3" t="n">
         <v>0</v>
@@ -14640,7 +14649,7 @@
     </row>
     <row r="408" customHeight="1" ht="15" spans="1:10">
       <c r="A408" s="1" t="n">
-        <v>804092</v>
+        <v>804094</v>
       </c>
       <c r="B408" s="1" t="s">
         <v>415</v>
@@ -14655,7 +14664,7 @@
         <v>2</v>
       </c>
       <c r="F408" s="3" t="n">
-        <v>8123</v>
+        <v>11141</v>
       </c>
       <c r="G408" s="3" t="n">
         <v>0</v>
@@ -14672,7 +14681,7 @@
     </row>
     <row r="409" customHeight="1" ht="15" spans="1:10">
       <c r="A409" s="1" t="n">
-        <v>804091</v>
+        <v>804390</v>
       </c>
       <c r="B409" s="1" t="s">
         <v>416</v>
@@ -14687,7 +14696,7 @@
         <v>2</v>
       </c>
       <c r="F409" s="3" t="n">
-        <v>15957</v>
+        <v>4657</v>
       </c>
       <c r="G409" s="3" t="n">
         <v>0</v>
@@ -14704,7 +14713,7 @@
     </row>
     <row r="410" customHeight="1" ht="15" spans="1:10">
       <c r="A410" s="1" t="n">
-        <v>813517</v>
+        <v>804096</v>
       </c>
       <c r="B410" s="1" t="s">
         <v>417</v>
@@ -14719,7 +14728,7 @@
         <v>2</v>
       </c>
       <c r="F410" s="3" t="n">
-        <v>5018</v>
+        <v>20318</v>
       </c>
       <c r="G410" s="3" t="n">
         <v>0</v>
@@ -14736,7 +14745,7 @@
     </row>
     <row r="411" customHeight="1" ht="15" spans="1:10">
       <c r="A411" s="1" t="n">
-        <v>804461</v>
+        <v>804092</v>
       </c>
       <c r="B411" s="1" t="s">
         <v>418</v>
@@ -14751,7 +14760,7 @@
         <v>2</v>
       </c>
       <c r="F411" s="3" t="n">
-        <v>822</v>
+        <v>8123</v>
       </c>
       <c r="G411" s="3" t="n">
         <v>0</v>
@@ -14768,7 +14777,7 @@
     </row>
     <row r="412" customHeight="1" ht="15" spans="1:10">
       <c r="A412" s="1" t="n">
-        <v>804580</v>
+        <v>804091</v>
       </c>
       <c r="B412" s="1" t="s">
         <v>419</v>
@@ -14783,7 +14792,7 @@
         <v>2</v>
       </c>
       <c r="F412" s="3" t="n">
-        <v>3228</v>
+        <v>15957</v>
       </c>
       <c r="G412" s="3" t="n">
         <v>0</v>
@@ -14800,7 +14809,7 @@
     </row>
     <row r="413" customHeight="1" ht="15" spans="1:10">
       <c r="A413" s="1" t="n">
-        <v>813504</v>
+        <v>813517</v>
       </c>
       <c r="B413" s="1" t="s">
         <v>420</v>
@@ -14815,7 +14824,7 @@
         <v>2</v>
       </c>
       <c r="F413" s="3" t="n">
-        <v>528</v>
+        <v>4768</v>
       </c>
       <c r="G413" s="3" t="n">
         <v>0</v>
@@ -14832,7 +14841,7 @@
     </row>
     <row r="414" customHeight="1" ht="15" spans="1:10">
       <c r="A414" s="1" t="n">
-        <v>804248</v>
+        <v>804461</v>
       </c>
       <c r="B414" s="1" t="s">
         <v>421</v>
@@ -14847,7 +14856,7 @@
         <v>2</v>
       </c>
       <c r="F414" s="3" t="n">
-        <v>898</v>
+        <v>822</v>
       </c>
       <c r="G414" s="3" t="n">
         <v>0</v>
@@ -14864,7 +14873,7 @@
     </row>
     <row r="415" customHeight="1" ht="15" spans="1:10">
       <c r="A415" s="1" t="n">
-        <v>804426</v>
+        <v>804580</v>
       </c>
       <c r="B415" s="1" t="s">
         <v>422</v>
@@ -14879,7 +14888,7 @@
         <v>2</v>
       </c>
       <c r="F415" s="3" t="n">
-        <v>900</v>
+        <v>3228</v>
       </c>
       <c r="G415" s="3" t="n">
         <v>0</v>
@@ -14896,7 +14905,7 @@
     </row>
     <row r="416" customHeight="1" ht="15" spans="1:10">
       <c r="A416" s="1" t="n">
-        <v>813179</v>
+        <v>813504</v>
       </c>
       <c r="B416" s="1" t="s">
         <v>423</v>
@@ -14911,7 +14920,7 @@
         <v>2</v>
       </c>
       <c r="F416" s="3" t="n">
-        <v>195</v>
+        <v>528</v>
       </c>
       <c r="G416" s="3" t="n">
         <v>0</v>
@@ -14928,7 +14937,7 @@
     </row>
     <row r="417" customHeight="1" ht="15" spans="1:10">
       <c r="A417" s="1" t="n">
-        <v>813256</v>
+        <v>804248</v>
       </c>
       <c r="B417" s="1" t="s">
         <v>424</v>
@@ -14943,7 +14952,7 @@
         <v>2</v>
       </c>
       <c r="F417" s="3" t="n">
-        <v>2836</v>
+        <v>498</v>
       </c>
       <c r="G417" s="3" t="n">
         <v>0</v>
@@ -14960,7 +14969,7 @@
     </row>
     <row r="418" customHeight="1" ht="15" spans="1:10">
       <c r="A418" s="1" t="n">
-        <v>804569</v>
+        <v>804426</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>425</v>
@@ -14975,7 +14984,7 @@
         <v>2</v>
       </c>
       <c r="F418" s="3" t="n">
-        <v>1350</v>
+        <v>900</v>
       </c>
       <c r="G418" s="3" t="n">
         <v>0</v>
@@ -14992,7 +15001,7 @@
     </row>
     <row r="419" customHeight="1" ht="15" spans="1:10">
       <c r="A419" s="1" t="n">
-        <v>804537</v>
+        <v>813179</v>
       </c>
       <c r="B419" s="1" t="s">
         <v>426</v>
@@ -15007,7 +15016,7 @@
         <v>2</v>
       </c>
       <c r="F419" s="3" t="n">
-        <v>1059</v>
+        <v>1561</v>
       </c>
       <c r="G419" s="3" t="n">
         <v>0</v>
@@ -15024,7 +15033,7 @@
     </row>
     <row r="420" customHeight="1" ht="15" spans="1:10">
       <c r="A420" s="1" t="n">
-        <v>804047</v>
+        <v>813256</v>
       </c>
       <c r="B420" s="1" t="s">
         <v>427</v>
@@ -15039,7 +15048,7 @@
         <v>2</v>
       </c>
       <c r="F420" s="3" t="n">
-        <v>7538</v>
+        <v>2660</v>
       </c>
       <c r="G420" s="3" t="n">
         <v>0</v>
@@ -15056,7 +15065,7 @@
     </row>
     <row r="421" customHeight="1" ht="15" spans="1:10">
       <c r="A421" s="1" t="n">
-        <v>804605</v>
+        <v>804569</v>
       </c>
       <c r="B421" s="1" t="s">
         <v>428</v>
@@ -15071,7 +15080,7 @@
         <v>2</v>
       </c>
       <c r="F421" s="3" t="n">
-        <v>6516</v>
+        <v>1350</v>
       </c>
       <c r="G421" s="3" t="n">
         <v>0</v>
@@ -15088,7 +15097,7 @@
     </row>
     <row r="422" customHeight="1" ht="15" spans="1:10">
       <c r="A422" s="1" t="n">
-        <v>804606</v>
+        <v>804537</v>
       </c>
       <c r="B422" s="1" t="s">
         <v>429</v>
@@ -15103,7 +15112,7 @@
         <v>2</v>
       </c>
       <c r="F422" s="3" t="n">
-        <v>6194</v>
+        <v>1059</v>
       </c>
       <c r="G422" s="3" t="n">
         <v>0</v>
@@ -15120,7 +15129,7 @@
     </row>
     <row r="423" customHeight="1" ht="15" spans="1:10">
       <c r="A423" s="1" t="n">
-        <v>804327</v>
+        <v>804047</v>
       </c>
       <c r="B423" s="1" t="s">
         <v>430</v>
@@ -15135,7 +15144,7 @@
         <v>2</v>
       </c>
       <c r="F423" s="3" t="n">
-        <v>2573</v>
+        <v>7538</v>
       </c>
       <c r="G423" s="3" t="n">
         <v>0</v>
@@ -15152,7 +15161,7 @@
     </row>
     <row r="424" customHeight="1" ht="15" spans="1:10">
       <c r="A424" s="1" t="n">
-        <v>813033</v>
+        <v>804605</v>
       </c>
       <c r="B424" s="1" t="s">
         <v>431</v>
@@ -15167,7 +15176,7 @@
         <v>2</v>
       </c>
       <c r="F424" s="3" t="n">
-        <v>929</v>
+        <v>6516</v>
       </c>
       <c r="G424" s="3" t="n">
         <v>0</v>
@@ -15184,7 +15193,7 @@
     </row>
     <row r="425" customHeight="1" ht="15" spans="1:10">
       <c r="A425" s="1" t="n">
-        <v>804501</v>
+        <v>804606</v>
       </c>
       <c r="B425" s="1" t="s">
         <v>432</v>
@@ -15199,7 +15208,7 @@
         <v>2</v>
       </c>
       <c r="F425" s="3" t="n">
-        <v>2259</v>
+        <v>6194</v>
       </c>
       <c r="G425" s="3" t="n">
         <v>0</v>
@@ -15216,7 +15225,7 @@
     </row>
     <row r="426" customHeight="1" ht="15" spans="1:10">
       <c r="A426" s="1" t="n">
-        <v>804398</v>
+        <v>804327</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>433</v>
@@ -15231,7 +15240,7 @@
         <v>2</v>
       </c>
       <c r="F426" s="3" t="n">
-        <v>1535</v>
+        <v>2573</v>
       </c>
       <c r="G426" s="3" t="n">
         <v>0</v>
@@ -15248,7 +15257,7 @@
     </row>
     <row r="427" customHeight="1" ht="15" spans="1:10">
       <c r="A427" s="1" t="n">
-        <v>804504</v>
+        <v>813033</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>434</v>
@@ -15263,7 +15272,7 @@
         <v>2</v>
       </c>
       <c r="F427" s="3" t="n">
-        <v>3040</v>
+        <v>929</v>
       </c>
       <c r="G427" s="3" t="n">
         <v>0</v>
@@ -15280,7 +15289,7 @@
     </row>
     <row r="428" customHeight="1" ht="15" spans="1:10">
       <c r="A428" s="1" t="n">
-        <v>813509</v>
+        <v>804501</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>435</v>
@@ -15295,7 +15304,7 @@
         <v>2</v>
       </c>
       <c r="F428" s="3" t="n">
-        <v>14900</v>
+        <v>2259</v>
       </c>
       <c r="G428" s="3" t="n">
         <v>0</v>
@@ -15312,7 +15321,7 @@
     </row>
     <row r="429" customHeight="1" ht="15" spans="1:10">
       <c r="A429" s="1" t="n">
-        <v>804108</v>
+        <v>804398</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>436</v>
@@ -15327,7 +15336,7 @@
         <v>2</v>
       </c>
       <c r="F429" s="3" t="n">
-        <v>8539</v>
+        <v>1535</v>
       </c>
       <c r="G429" s="3" t="n">
         <v>0</v>
@@ -15344,7 +15353,7 @@
     </row>
     <row r="430" customHeight="1" ht="15" spans="1:10">
       <c r="A430" s="1" t="n">
-        <v>804431</v>
+        <v>804504</v>
       </c>
       <c r="B430" s="1" t="s">
         <v>437</v>
@@ -15359,7 +15368,7 @@
         <v>2</v>
       </c>
       <c r="F430" s="3" t="n">
-        <v>1167</v>
+        <v>631</v>
       </c>
       <c r="G430" s="3" t="n">
         <v>0</v>
@@ -15376,7 +15385,7 @@
     </row>
     <row r="431" customHeight="1" ht="15" spans="1:10">
       <c r="A431" s="1" t="n">
-        <v>804197</v>
+        <v>813509</v>
       </c>
       <c r="B431" s="1" t="s">
         <v>438</v>
@@ -15391,7 +15400,7 @@
         <v>2</v>
       </c>
       <c r="F431" s="3" t="n">
-        <v>2522</v>
+        <v>14900</v>
       </c>
       <c r="G431" s="3" t="n">
         <v>0</v>
@@ -15408,7 +15417,7 @@
     </row>
     <row r="432" customHeight="1" ht="15" spans="1:10">
       <c r="A432" s="1" t="n">
-        <v>804263</v>
+        <v>804108</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>439</v>
@@ -15423,7 +15432,7 @@
         <v>2</v>
       </c>
       <c r="F432" s="3" t="n">
-        <v>1252</v>
+        <v>8539</v>
       </c>
       <c r="G432" s="3" t="n">
         <v>0</v>
@@ -15440,7 +15449,7 @@
     </row>
     <row r="433" customHeight="1" ht="15" spans="1:10">
       <c r="A433" s="1" t="n">
-        <v>804587</v>
+        <v>804431</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>440</v>
@@ -15455,7 +15464,7 @@
         <v>2</v>
       </c>
       <c r="F433" s="3" t="n">
-        <v>3248</v>
+        <v>1160</v>
       </c>
       <c r="G433" s="3" t="n">
         <v>0</v>
@@ -15472,7 +15481,7 @@
     </row>
     <row r="434" customHeight="1" ht="15" spans="1:10">
       <c r="A434" s="1" t="n">
-        <v>804561</v>
+        <v>804197</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>441</v>
@@ -15487,7 +15496,7 @@
         <v>2</v>
       </c>
       <c r="F434" s="3" t="n">
-        <v>678</v>
+        <v>2522</v>
       </c>
       <c r="G434" s="3" t="n">
         <v>0</v>
@@ -15504,7 +15513,7 @@
     </row>
     <row r="435" customHeight="1" ht="15" spans="1:10">
       <c r="A435" s="1" t="n">
-        <v>804538</v>
+        <v>804263</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>442</v>
@@ -15519,7 +15528,7 @@
         <v>2</v>
       </c>
       <c r="F435" s="3" t="n">
-        <v>80</v>
+        <v>1252</v>
       </c>
       <c r="G435" s="3" t="n">
         <v>0</v>
@@ -15536,7 +15545,7 @@
     </row>
     <row r="436" customHeight="1" ht="15" spans="1:10">
       <c r="A436" s="1" t="n">
-        <v>813266</v>
+        <v>804587</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>443</v>
@@ -15551,7 +15560,7 @@
         <v>2</v>
       </c>
       <c r="F436" s="3" t="n">
-        <v>22732</v>
+        <v>3248</v>
       </c>
       <c r="G436" s="3" t="n">
         <v>0</v>
@@ -15568,7 +15577,7 @@
     </row>
     <row r="437" customHeight="1" ht="15" spans="1:10">
       <c r="A437" s="1" t="n">
-        <v>804565</v>
+        <v>804561</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>444</v>
@@ -15583,7 +15592,7 @@
         <v>2</v>
       </c>
       <c r="F437" s="3" t="n">
-        <v>1816</v>
+        <v>678</v>
       </c>
       <c r="G437" s="3" t="n">
         <v>0</v>
@@ -15600,7 +15609,7 @@
     </row>
     <row r="438" customHeight="1" ht="15" spans="1:10">
       <c r="A438" s="1" t="n">
-        <v>804136</v>
+        <v>804538</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>445</v>
@@ -15615,7 +15624,7 @@
         <v>2</v>
       </c>
       <c r="F438" s="3" t="n">
-        <v>10208</v>
+        <v>80</v>
       </c>
       <c r="G438" s="3" t="n">
         <v>0</v>
@@ -15632,7 +15641,7 @@
     </row>
     <row r="439" customHeight="1" ht="15" spans="1:10">
       <c r="A439" s="1" t="n">
-        <v>804141</v>
+        <v>813266</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>446</v>
@@ -15647,7 +15656,7 @@
         <v>2</v>
       </c>
       <c r="F439" s="3" t="n">
-        <v>860</v>
+        <v>22732</v>
       </c>
       <c r="G439" s="3" t="n">
         <v>0</v>
@@ -15664,7 +15673,7 @@
     </row>
     <row r="440" customHeight="1" ht="15" spans="1:10">
       <c r="A440" s="1" t="n">
-        <v>804010</v>
+        <v>804565</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>447</v>
@@ -15679,7 +15688,7 @@
         <v>2</v>
       </c>
       <c r="F440" s="3" t="n">
-        <v>2315</v>
+        <v>1816</v>
       </c>
       <c r="G440" s="3" t="n">
         <v>0</v>
@@ -15696,7 +15705,7 @@
     </row>
     <row r="441" customHeight="1" ht="15" spans="1:10">
       <c r="A441" s="1" t="n">
-        <v>804012</v>
+        <v>804136</v>
       </c>
       <c r="B441" s="1" t="s">
         <v>448</v>
@@ -15711,7 +15720,7 @@
         <v>2</v>
       </c>
       <c r="F441" s="3" t="n">
-        <v>2600</v>
+        <v>8868</v>
       </c>
       <c r="G441" s="3" t="n">
         <v>0</v>
@@ -15728,7 +15737,7 @@
     </row>
     <row r="442" customHeight="1" ht="15" spans="1:10">
       <c r="A442" s="1" t="n">
-        <v>804427</v>
+        <v>804141</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>449</v>
@@ -15743,7 +15752,7 @@
         <v>2</v>
       </c>
       <c r="F442" s="3" t="n">
-        <v>6256</v>
+        <v>860</v>
       </c>
       <c r="G442" s="3" t="n">
         <v>0</v>
@@ -15760,7 +15769,7 @@
     </row>
     <row r="443" customHeight="1" ht="15" spans="1:10">
       <c r="A443" s="1" t="n">
-        <v>804402</v>
+        <v>804010</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>450</v>
@@ -15775,7 +15784,7 @@
         <v>2</v>
       </c>
       <c r="F443" s="3" t="n">
-        <v>590</v>
+        <v>1371</v>
       </c>
       <c r="G443" s="3" t="n">
         <v>0</v>
@@ -15792,7 +15801,7 @@
     </row>
     <row r="444" customHeight="1" ht="15" spans="1:10">
       <c r="A444" s="1" t="n">
-        <v>804423</v>
+        <v>804012</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>451</v>
@@ -15807,7 +15816,7 @@
         <v>2</v>
       </c>
       <c r="F444" s="3" t="n">
-        <v>4654</v>
+        <v>2246</v>
       </c>
       <c r="G444" s="3" t="n">
         <v>0</v>
@@ -15824,7 +15833,7 @@
     </row>
     <row r="445" customHeight="1" ht="15" spans="1:10">
       <c r="A445" s="1" t="n">
-        <v>813034</v>
+        <v>804427</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>452</v>
@@ -15839,7 +15848,7 @@
         <v>2</v>
       </c>
       <c r="F445" s="3" t="n">
-        <v>8101</v>
+        <v>6256</v>
       </c>
       <c r="G445" s="3" t="n">
         <v>0</v>
@@ -15856,7 +15865,7 @@
     </row>
     <row r="446" customHeight="1" ht="15" spans="1:10">
       <c r="A446" s="1" t="n">
-        <v>804520</v>
+        <v>804402</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>453</v>
@@ -15871,7 +15880,7 @@
         <v>2</v>
       </c>
       <c r="F446" s="3" t="n">
-        <v>105</v>
+        <v>590</v>
       </c>
       <c r="G446" s="3" t="n">
         <v>0</v>
@@ -15888,7 +15897,7 @@
     </row>
     <row r="447" customHeight="1" ht="15" spans="1:10">
       <c r="A447" s="1" t="n">
-        <v>804135</v>
+        <v>804423</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>454</v>
@@ -15903,7 +15912,7 @@
         <v>2</v>
       </c>
       <c r="F447" s="3" t="n">
-        <v>1611</v>
+        <v>4654</v>
       </c>
       <c r="G447" s="3" t="n">
         <v>0</v>
@@ -15920,7 +15929,7 @@
     </row>
     <row r="448" customHeight="1" ht="15" spans="1:10">
       <c r="A448" s="1" t="n">
-        <v>804061</v>
+        <v>813034</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>455</v>
@@ -15935,7 +15944,7 @@
         <v>2</v>
       </c>
       <c r="F448" s="3" t="n">
-        <v>5757</v>
+        <v>8101</v>
       </c>
       <c r="G448" s="3" t="n">
         <v>0</v>
@@ -15952,7 +15961,7 @@
     </row>
     <row r="449" customHeight="1" ht="15" spans="1:10">
       <c r="A449" s="1" t="n">
-        <v>804325</v>
+        <v>804520</v>
       </c>
       <c r="B449" s="1" t="s">
         <v>456</v>
@@ -15967,7 +15976,7 @@
         <v>2</v>
       </c>
       <c r="F449" s="3" t="n">
-        <v>8171</v>
+        <v>105</v>
       </c>
       <c r="G449" s="3" t="n">
         <v>0</v>
@@ -15984,7 +15993,7 @@
     </row>
     <row r="450" customHeight="1" ht="15" spans="1:10">
       <c r="A450" s="1" t="n">
-        <v>804331</v>
+        <v>804135</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>457</v>
@@ -15999,7 +16008,7 @@
         <v>2</v>
       </c>
       <c r="F450" s="3" t="n">
-        <v>2338</v>
+        <v>1839</v>
       </c>
       <c r="G450" s="3" t="n">
         <v>0</v>
@@ -16016,7 +16025,7 @@
     </row>
     <row r="451" customHeight="1" ht="15" spans="1:10">
       <c r="A451" s="1" t="n">
-        <v>804473</v>
+        <v>804061</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>458</v>
@@ -16031,7 +16040,7 @@
         <v>2</v>
       </c>
       <c r="F451" s="3" t="n">
-        <v>1011</v>
+        <v>4584</v>
       </c>
       <c r="G451" s="3" t="n">
         <v>0</v>
@@ -16048,7 +16057,7 @@
     </row>
     <row r="452" customHeight="1" ht="15" spans="1:10">
       <c r="A452" s="1" t="n">
-        <v>804460</v>
+        <v>804325</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>459</v>
@@ -16063,7 +16072,7 @@
         <v>2</v>
       </c>
       <c r="F452" s="3" t="n">
-        <v>6067</v>
+        <v>6652</v>
       </c>
       <c r="G452" s="3" t="n">
         <v>0</v>
@@ -16080,7 +16089,7 @@
     </row>
     <row r="453" customHeight="1" ht="15" spans="1:10">
       <c r="A453" s="1" t="n">
-        <v>804306</v>
+        <v>804331</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>460</v>
@@ -16095,7 +16104,7 @@
         <v>2</v>
       </c>
       <c r="F453" s="3" t="n">
-        <v>6824</v>
+        <v>2338</v>
       </c>
       <c r="G453" s="3" t="n">
         <v>0</v>
@@ -16112,7 +16121,7 @@
     </row>
     <row r="454" customHeight="1" ht="15" spans="1:10">
       <c r="A454" s="1" t="n">
-        <v>813203</v>
+        <v>804473</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>461</v>
@@ -16127,7 +16136,7 @@
         <v>2</v>
       </c>
       <c r="F454" s="3" t="n">
-        <v>1330</v>
+        <v>1011</v>
       </c>
       <c r="G454" s="3" t="n">
         <v>0</v>
@@ -16144,7 +16153,7 @@
     </row>
     <row r="455" customHeight="1" ht="15" spans="1:10">
       <c r="A455" s="1" t="n">
-        <v>813036</v>
+        <v>804460</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>462</v>
@@ -16159,7 +16168,7 @@
         <v>2</v>
       </c>
       <c r="F455" s="3" t="n">
-        <v>1985</v>
+        <v>6067</v>
       </c>
       <c r="G455" s="3" t="n">
         <v>0</v>
@@ -16176,7 +16185,7 @@
     </row>
     <row r="456" customHeight="1" ht="15" spans="1:10">
       <c r="A456" s="1" t="n">
-        <v>813248</v>
+        <v>804306</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>463</v>
@@ -16191,7 +16200,7 @@
         <v>2</v>
       </c>
       <c r="F456" s="3" t="n">
-        <v>1996</v>
+        <v>6824</v>
       </c>
       <c r="G456" s="3" t="n">
         <v>0</v>
@@ -16208,7 +16217,7 @@
     </row>
     <row r="457" customHeight="1" ht="15" spans="1:10">
       <c r="A457" s="1" t="n">
-        <v>813024</v>
+        <v>813203</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>464</v>
@@ -16223,7 +16232,7 @@
         <v>2</v>
       </c>
       <c r="F457" s="3" t="n">
-        <v>3611</v>
+        <v>1330</v>
       </c>
       <c r="G457" s="3" t="n">
         <v>0</v>
@@ -16240,7 +16249,7 @@
     </row>
     <row r="458" customHeight="1" ht="15" spans="1:10">
       <c r="A458" s="1" t="n">
-        <v>804521</v>
+        <v>813036</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>465</v>
@@ -16255,7 +16264,7 @@
         <v>2</v>
       </c>
       <c r="F458" s="3" t="n">
-        <v>748</v>
+        <v>1985</v>
       </c>
       <c r="G458" s="3" t="n">
         <v>0</v>
@@ -16272,7 +16281,7 @@
     </row>
     <row r="459" customHeight="1" ht="15" spans="1:10">
       <c r="A459" s="1" t="n">
-        <v>804307</v>
+        <v>813248</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>466</v>
@@ -16287,7 +16296,7 @@
         <v>2</v>
       </c>
       <c r="F459" s="3" t="n">
-        <v>1526</v>
+        <v>1996</v>
       </c>
       <c r="G459" s="3" t="n">
         <v>0</v>
@@ -16304,7 +16313,7 @@
     </row>
     <row r="460" customHeight="1" ht="15" spans="1:10">
       <c r="A460" s="1" t="n">
-        <v>804578</v>
+        <v>813024</v>
       </c>
       <c r="B460" s="1" t="s">
         <v>467</v>
@@ -16319,7 +16328,7 @@
         <v>2</v>
       </c>
       <c r="F460" s="3" t="n">
-        <v>2484</v>
+        <v>3011</v>
       </c>
       <c r="G460" s="3" t="n">
         <v>0</v>
@@ -16336,7 +16345,7 @@
     </row>
     <row r="461" customHeight="1" ht="15" spans="1:10">
       <c r="A461" s="1" t="n">
-        <v>804567</v>
+        <v>804521</v>
       </c>
       <c r="B461" s="1" t="s">
         <v>468</v>
@@ -16351,7 +16360,7 @@
         <v>2</v>
       </c>
       <c r="F461" s="3" t="n">
-        <v>3841</v>
+        <v>748</v>
       </c>
       <c r="G461" s="3" t="n">
         <v>0</v>
@@ -16368,7 +16377,7 @@
     </row>
     <row r="462" customHeight="1" ht="15" spans="1:10">
       <c r="A462" s="1" t="n">
-        <v>804269</v>
+        <v>804307</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>469</v>
@@ -16383,7 +16392,7 @@
         <v>2</v>
       </c>
       <c r="F462" s="3" t="n">
-        <v>1191</v>
+        <v>1526</v>
       </c>
       <c r="G462" s="3" t="n">
         <v>0</v>
@@ -16400,7 +16409,7 @@
     </row>
     <row r="463" customHeight="1" ht="15" spans="1:10">
       <c r="A463" s="1" t="n">
-        <v>804266</v>
+        <v>804578</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>470</v>
@@ -16415,7 +16424,7 @@
         <v>2</v>
       </c>
       <c r="F463" s="3" t="n">
-        <v>1291</v>
+        <v>2484</v>
       </c>
       <c r="G463" s="3" t="n">
         <v>0</v>
@@ -16432,7 +16441,7 @@
     </row>
     <row r="464" customHeight="1" ht="15" spans="1:10">
       <c r="A464" s="1" t="n">
-        <v>804602</v>
+        <v>804567</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>471</v>
@@ -16447,7 +16456,7 @@
         <v>2</v>
       </c>
       <c r="F464" s="3" t="n">
-        <v>662</v>
+        <v>3841</v>
       </c>
       <c r="G464" s="3" t="n">
         <v>0</v>
@@ -16464,7 +16473,7 @@
     </row>
     <row r="465" customHeight="1" ht="15" spans="1:10">
       <c r="A465" s="1" t="n">
-        <v>804594</v>
+        <v>804269</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>472</v>
@@ -16479,7 +16488,7 @@
         <v>2</v>
       </c>
       <c r="F465" s="3" t="n">
-        <v>2101</v>
+        <v>1191</v>
       </c>
       <c r="G465" s="3" t="n">
         <v>0</v>
@@ -16496,7 +16505,7 @@
     </row>
     <row r="466" customHeight="1" ht="15" spans="1:10">
       <c r="A466" s="1" t="n">
-        <v>804223</v>
+        <v>804266</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>473</v>
@@ -16511,7 +16520,7 @@
         <v>2</v>
       </c>
       <c r="F466" s="3" t="n">
-        <v>1712</v>
+        <v>1291</v>
       </c>
       <c r="G466" s="3" t="n">
         <v>0</v>
@@ -16528,7 +16537,7 @@
     </row>
     <row r="467" customHeight="1" ht="15" spans="1:10">
       <c r="A467" s="1" t="n">
-        <v>804222</v>
+        <v>804602</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>474</v>
@@ -16543,7 +16552,7 @@
         <v>2</v>
       </c>
       <c r="F467" s="3" t="n">
-        <v>2673</v>
+        <v>662</v>
       </c>
       <c r="G467" s="3" t="n">
         <v>0</v>
@@ -16560,7 +16569,7 @@
     </row>
     <row r="468" customHeight="1" ht="15" spans="1:10">
       <c r="A468" s="1" t="n">
-        <v>813409</v>
+        <v>804594</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>475</v>
@@ -16575,7 +16584,7 @@
         <v>2</v>
       </c>
       <c r="F468" s="3" t="n">
-        <v>9035</v>
+        <v>2101</v>
       </c>
       <c r="G468" s="3" t="n">
         <v>0</v>
@@ -16592,7 +16601,7 @@
     </row>
     <row r="469" customHeight="1" ht="15" spans="1:10">
       <c r="A469" s="1" t="n">
-        <v>804206</v>
+        <v>804223</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>476</v>
@@ -16607,7 +16616,7 @@
         <v>2</v>
       </c>
       <c r="F469" s="3" t="n">
-        <v>5076</v>
+        <v>1712</v>
       </c>
       <c r="G469" s="3" t="n">
         <v>0</v>
@@ -16624,7 +16633,7 @@
     </row>
     <row r="470" customHeight="1" ht="15" spans="1:10">
       <c r="A470" s="1" t="n">
-        <v>804207</v>
+        <v>804222</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>477</v>
@@ -16639,7 +16648,7 @@
         <v>2</v>
       </c>
       <c r="F470" s="3" t="n">
-        <v>7954</v>
+        <v>2673</v>
       </c>
       <c r="G470" s="3" t="n">
         <v>0</v>
@@ -16656,7 +16665,7 @@
     </row>
     <row r="471" customHeight="1" ht="15" spans="1:10">
       <c r="A471" s="1" t="n">
-        <v>813274</v>
+        <v>813409</v>
       </c>
       <c r="B471" s="1" t="s">
         <v>478</v>
@@ -16671,7 +16680,7 @@
         <v>2</v>
       </c>
       <c r="F471" s="3" t="n">
-        <v>2519</v>
+        <v>8205</v>
       </c>
       <c r="G471" s="3" t="n">
         <v>0</v>
@@ -16688,7 +16697,7 @@
     </row>
     <row r="472" customHeight="1" ht="15" spans="1:10">
       <c r="A472" s="1" t="n">
-        <v>804497</v>
+        <v>804206</v>
       </c>
       <c r="B472" s="1" t="s">
         <v>479</v>
@@ -16703,7 +16712,7 @@
         <v>2</v>
       </c>
       <c r="F472" s="3" t="n">
-        <v>26387</v>
+        <v>5950</v>
       </c>
       <c r="G472" s="3" t="n">
         <v>0</v>
@@ -16720,7 +16729,7 @@
     </row>
     <row r="473" customHeight="1" ht="15" spans="1:10">
       <c r="A473" s="1" t="n">
-        <v>804496</v>
+        <v>804207</v>
       </c>
       <c r="B473" s="1" t="s">
         <v>480</v>
@@ -16735,7 +16744,7 @@
         <v>2</v>
       </c>
       <c r="F473" s="3" t="n">
-        <v>6432</v>
+        <v>6271</v>
       </c>
       <c r="G473" s="3" t="n">
         <v>0</v>
@@ -16752,7 +16761,7 @@
     </row>
     <row r="474" customHeight="1" ht="15" spans="1:10">
       <c r="A474" s="1" t="n">
-        <v>804129</v>
+        <v>813274</v>
       </c>
       <c r="B474" s="1" t="s">
         <v>481</v>
@@ -16767,7 +16776,7 @@
         <v>2</v>
       </c>
       <c r="F474" s="3" t="n">
-        <v>17395</v>
+        <v>2519</v>
       </c>
       <c r="G474" s="3" t="n">
         <v>0</v>
@@ -16784,7 +16793,7 @@
     </row>
     <row r="475" customHeight="1" ht="15" spans="1:10">
       <c r="A475" s="1" t="n">
-        <v>804458</v>
+        <v>804497</v>
       </c>
       <c r="B475" s="1" t="s">
         <v>482</v>
@@ -16799,7 +16808,7 @@
         <v>2</v>
       </c>
       <c r="F475" s="3" t="n">
-        <v>4249</v>
+        <v>25431</v>
       </c>
       <c r="G475" s="3" t="n">
         <v>0</v>
@@ -16816,7 +16825,7 @@
     </row>
     <row r="476" customHeight="1" ht="15" spans="1:10">
       <c r="A476" s="1" t="n">
-        <v>804563</v>
+        <v>804496</v>
       </c>
       <c r="B476" s="1" t="s">
         <v>483</v>
@@ -16831,7 +16840,7 @@
         <v>2</v>
       </c>
       <c r="F476" s="3" t="n">
-        <v>1080</v>
+        <v>11126</v>
       </c>
       <c r="G476" s="3" t="n">
         <v>0</v>
@@ -16848,7 +16857,7 @@
     </row>
     <row r="477" customHeight="1" ht="15" spans="1:10">
       <c r="A477" s="1" t="n">
-        <v>804525</v>
+        <v>804129</v>
       </c>
       <c r="B477" s="1" t="s">
         <v>484</v>
@@ -16863,7 +16872,7 @@
         <v>2</v>
       </c>
       <c r="F477" s="3" t="n">
-        <v>12285</v>
+        <v>8932</v>
       </c>
       <c r="G477" s="3" t="n">
         <v>0</v>
@@ -16880,7 +16889,7 @@
     </row>
     <row r="478" customHeight="1" ht="15" spans="1:10">
       <c r="A478" s="1" t="n">
-        <v>804526</v>
+        <v>804458</v>
       </c>
       <c r="B478" s="1" t="s">
         <v>485</v>
@@ -16895,7 +16904,7 @@
         <v>2</v>
       </c>
       <c r="F478" s="3" t="n">
-        <v>15435</v>
+        <v>4249</v>
       </c>
       <c r="G478" s="3" t="n">
         <v>0</v>
@@ -16912,7 +16921,7 @@
     </row>
     <row r="479" customHeight="1" ht="15" spans="1:10">
       <c r="A479" s="1" t="n">
-        <v>813039</v>
+        <v>804563</v>
       </c>
       <c r="B479" s="1" t="s">
         <v>486</v>
@@ -16927,7 +16936,7 @@
         <v>2</v>
       </c>
       <c r="F479" s="3" t="n">
-        <v>7768</v>
+        <v>1080</v>
       </c>
       <c r="G479" s="3" t="n">
         <v>0</v>
@@ -16944,7 +16953,7 @@
     </row>
     <row r="480" customHeight="1" ht="15" spans="1:10">
       <c r="A480" s="1" t="n">
-        <v>813025</v>
+        <v>804525</v>
       </c>
       <c r="B480" s="1" t="s">
         <v>487</v>
@@ -16959,7 +16968,7 @@
         <v>2</v>
       </c>
       <c r="F480" s="3" t="n">
-        <v>17810</v>
+        <v>12345</v>
       </c>
       <c r="G480" s="3" t="n">
         <v>0</v>
@@ -16976,7 +16985,7 @@
     </row>
     <row r="481" customHeight="1" ht="15" spans="1:10">
       <c r="A481" s="1" t="n">
-        <v>804267</v>
+        <v>804526</v>
       </c>
       <c r="B481" s="1" t="s">
         <v>488</v>
@@ -16991,7 +17000,7 @@
         <v>2</v>
       </c>
       <c r="F481" s="3" t="n">
-        <v>1478</v>
+        <v>13894</v>
       </c>
       <c r="G481" s="3" t="n">
         <v>0</v>
@@ -17008,7 +17017,7 @@
     </row>
     <row r="482" customHeight="1" ht="15" spans="1:10">
       <c r="A482" s="1" t="n">
-        <v>804381</v>
+        <v>813039</v>
       </c>
       <c r="B482" s="1" t="s">
         <v>489</v>
@@ -17023,7 +17032,7 @@
         <v>2</v>
       </c>
       <c r="F482" s="3" t="n">
-        <v>2928</v>
+        <v>7768</v>
       </c>
       <c r="G482" s="3" t="n">
         <v>0</v>
@@ -17040,7 +17049,7 @@
     </row>
     <row r="483" customHeight="1" ht="15" spans="1:10">
       <c r="A483" s="1" t="n">
-        <v>804315</v>
+        <v>813025</v>
       </c>
       <c r="B483" s="1" t="s">
         <v>490</v>
@@ -17055,7 +17064,7 @@
         <v>2</v>
       </c>
       <c r="F483" s="3" t="n">
-        <v>10045</v>
+        <v>17810</v>
       </c>
       <c r="G483" s="3" t="n">
         <v>0</v>
@@ -17072,7 +17081,7 @@
     </row>
     <row r="484" customHeight="1" ht="15" spans="1:10">
       <c r="A484" s="1" t="n">
-        <v>804045</v>
+        <v>804267</v>
       </c>
       <c r="B484" s="1" t="s">
         <v>491</v>
@@ -17087,7 +17096,7 @@
         <v>2</v>
       </c>
       <c r="F484" s="3" t="n">
-        <v>60232</v>
+        <v>1478</v>
       </c>
       <c r="G484" s="3" t="n">
         <v>0</v>
@@ -17104,7 +17113,7 @@
     </row>
     <row r="485" customHeight="1" ht="15" spans="1:10">
       <c r="A485" s="1" t="n">
-        <v>804078</v>
+        <v>804381</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>492</v>
@@ -17119,7 +17128,7 @@
         <v>2</v>
       </c>
       <c r="F485" s="3" t="n">
-        <v>4219</v>
+        <v>2928</v>
       </c>
       <c r="G485" s="3" t="n">
         <v>0</v>
@@ -17136,7 +17145,7 @@
     </row>
     <row r="486" customHeight="1" ht="15" spans="1:10">
       <c r="A486" s="1" t="n">
-        <v>804044</v>
+        <v>804315</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>493</v>
@@ -17151,7 +17160,7 @@
         <v>2</v>
       </c>
       <c r="F486" s="3" t="n">
-        <v>17063</v>
+        <v>10045</v>
       </c>
       <c r="G486" s="3" t="n">
         <v>0</v>
@@ -17168,7 +17177,7 @@
     </row>
     <row r="487" customHeight="1" ht="15" spans="1:10">
       <c r="A487" s="1" t="n">
-        <v>804079</v>
+        <v>804045</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>494</v>
@@ -17183,7 +17192,7 @@
         <v>2</v>
       </c>
       <c r="F487" s="3" t="n">
-        <v>11838</v>
+        <v>69436</v>
       </c>
       <c r="G487" s="3" t="n">
         <v>0</v>
@@ -17200,7 +17209,7 @@
     </row>
     <row r="488" customHeight="1" ht="15" spans="1:10">
       <c r="A488" s="1" t="n">
-        <v>804314</v>
+        <v>804078</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>495</v>
@@ -17215,7 +17224,7 @@
         <v>2</v>
       </c>
       <c r="F488" s="3" t="n">
-        <v>10647</v>
+        <v>14989</v>
       </c>
       <c r="G488" s="3" t="n">
         <v>0</v>
@@ -17227,6 +17236,102 @@
         <v>0</v>
       </c>
       <c r="J488" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" customHeight="1" ht="15" spans="1:10">
+      <c r="A489" s="1" t="n">
+        <v>804044</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C489" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D489" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E489" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F489" s="3" t="n">
+        <v>7023</v>
+      </c>
+      <c r="G489" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H489" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I489" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J489" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" customHeight="1" ht="15" spans="1:10">
+      <c r="A490" s="1" t="n">
+        <v>804079</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C490" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D490" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E490" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F490" s="3" t="n">
+        <v>11838</v>
+      </c>
+      <c r="G490" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H490" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I490" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J490" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" customHeight="1" ht="15" spans="1:10">
+      <c r="A491" s="1" t="n">
+        <v>804314</v>
+      </c>
+      <c r="B491" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C491" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D491" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E491" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F491" s="3" t="n">
+        <v>11360</v>
+      </c>
+      <c r="G491" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H491" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I491" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J491" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/temp/diversos/Plastico.xlsx
+++ b/temp/diversos/Plastico.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1964" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="498">
   <si>
     <t>ABS ALTO BRILHO PRETO</t>
   </si>
@@ -1109,9 +1109,6 @@
   </si>
   <si>
     <t>ROLAMENTO PLÁSTICO EIXO ENGRENAGEM</t>
-  </si>
-  <si>
-    <t>ROLAMENTO 6004 ZZ / 2RS</t>
   </si>
   <si>
     <t>ROLDANA DE NYLON DO BV CADENA - PEÇA FÊMEA</t>
@@ -1609,7 +1606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J491"/>
+  <dimension ref="A1:J490"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" width="7.33203125" min="1" max="1"/>
@@ -2504,7 +2501,7 @@
         <v>2</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>7302</v>
+        <v>6602</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
@@ -2856,7 +2853,7 @@
         <v>2</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3529</v>
+        <v>3445</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
@@ -3304,7 +3301,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>13305</v>
+        <v>12029</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>0</v>
@@ -3432,7 +3429,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>6850</v>
+        <v>6800</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0</v>
@@ -3528,7 +3525,7 @@
         <v>2</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>8066</v>
+        <v>5804</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>0</v>
@@ -5064,7 +5061,7 @@
         <v>2</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>63037</v>
+        <v>61947</v>
       </c>
       <c r="G108" s="3" t="n">
         <v>0</v>
@@ -5160,7 +5157,7 @@
         <v>2</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>42748</v>
+        <v>36002</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -6280,7 +6277,7 @@
         <v>2</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>1391</v>
+        <v>391</v>
       </c>
       <c r="G146" s="3" t="n">
         <v>0</v>
@@ -6440,7 +6437,7 @@
         <v>2</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>1286</v>
+        <v>286</v>
       </c>
       <c r="G151" s="3" t="n">
         <v>0</v>
@@ -7624,7 +7621,7 @@
         <v>2</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>3646</v>
+        <v>3546</v>
       </c>
       <c r="G188" s="3" t="n">
         <v>0</v>
@@ -8680,7 +8677,7 @@
         <v>2</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>1714</v>
+        <v>1414</v>
       </c>
       <c r="G221" s="3" t="n">
         <v>0</v>
@@ -8776,7 +8773,7 @@
         <v>2</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>2439</v>
+        <v>2139</v>
       </c>
       <c r="G224" s="3" t="n">
         <v>0</v>
@@ -9384,7 +9381,7 @@
         <v>2</v>
       </c>
       <c r="F243" s="3" t="n">
-        <v>4200</v>
+        <v>3850</v>
       </c>
       <c r="G243" s="3" t="n">
         <v>0</v>
@@ -10216,7 +10213,7 @@
         <v>2</v>
       </c>
       <c r="F269" s="3" t="n">
-        <v>141791</v>
+        <v>138791</v>
       </c>
       <c r="G269" s="3" t="n">
         <v>0</v>
@@ -10824,7 +10821,7 @@
         <v>2</v>
       </c>
       <c r="F288" s="3" t="n">
-        <v>7887</v>
+        <v>7726</v>
       </c>
       <c r="G288" s="3" t="n">
         <v>0</v>
@@ -12104,7 +12101,7 @@
         <v>2</v>
       </c>
       <c r="F328" s="3" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G328" s="3" t="n">
         <v>0</v>
@@ -12168,7 +12165,7 @@
         <v>2</v>
       </c>
       <c r="F330" s="3" t="n">
-        <v>372</v>
+        <v>222</v>
       </c>
       <c r="G330" s="3" t="n">
         <v>0</v>
@@ -12360,7 +12357,7 @@
         <v>2</v>
       </c>
       <c r="F336" s="3" t="n">
-        <v>16857</v>
+        <v>10833</v>
       </c>
       <c r="G336" s="3" t="n">
         <v>0</v>
@@ -13113,7 +13110,7 @@
     </row>
     <row r="360" customHeight="1" ht="15" spans="1:10">
       <c r="A360" s="1" t="n">
-        <v>411015</v>
+        <v>813472</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>366</v>
@@ -13128,7 +13125,7 @@
         <v>2</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>1306</v>
+        <v>3217</v>
       </c>
       <c r="G360" s="3" t="n">
         <v>0</v>
@@ -13145,7 +13142,7 @@
     </row>
     <row r="361" customHeight="1" ht="15" spans="1:10">
       <c r="A361" s="1" t="n">
-        <v>813472</v>
+        <v>813473</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>367</v>
@@ -13160,7 +13157,7 @@
         <v>2</v>
       </c>
       <c r="F361" s="3" t="n">
-        <v>3217</v>
+        <v>3190</v>
       </c>
       <c r="G361" s="3" t="n">
         <v>0</v>
@@ -13177,7 +13174,7 @@
     </row>
     <row r="362" customHeight="1" ht="15" spans="1:10">
       <c r="A362" s="1" t="n">
-        <v>813473</v>
+        <v>804440</v>
       </c>
       <c r="B362" s="1" t="s">
         <v>368</v>
@@ -13192,7 +13189,7 @@
         <v>2</v>
       </c>
       <c r="F362" s="3" t="n">
-        <v>3190</v>
+        <v>2288</v>
       </c>
       <c r="G362" s="3" t="n">
         <v>0</v>
@@ -13209,7 +13206,7 @@
     </row>
     <row r="363" customHeight="1" ht="15" spans="1:10">
       <c r="A363" s="1" t="n">
-        <v>804440</v>
+        <v>804093</v>
       </c>
       <c r="B363" s="1" t="s">
         <v>369</v>
@@ -13224,7 +13221,7 @@
         <v>2</v>
       </c>
       <c r="F363" s="3" t="n">
-        <v>2288</v>
+        <v>15979</v>
       </c>
       <c r="G363" s="3" t="n">
         <v>0</v>
@@ -13241,7 +13238,7 @@
     </row>
     <row r="364" customHeight="1" ht="15" spans="1:10">
       <c r="A364" s="1" t="n">
-        <v>804093</v>
+        <v>804388</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>370</v>
@@ -13256,7 +13253,7 @@
         <v>2</v>
       </c>
       <c r="F364" s="3" t="n">
-        <v>15979</v>
+        <v>8801</v>
       </c>
       <c r="G364" s="3" t="n">
         <v>0</v>
@@ -13273,7 +13270,7 @@
     </row>
     <row r="365" customHeight="1" ht="15" spans="1:10">
       <c r="A365" s="1" t="n">
-        <v>804388</v>
+        <v>804095</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>371</v>
@@ -13288,7 +13285,7 @@
         <v>2</v>
       </c>
       <c r="F365" s="3" t="n">
-        <v>8801</v>
+        <v>5244</v>
       </c>
       <c r="G365" s="3" t="n">
         <v>0</v>
@@ -13305,7 +13302,7 @@
     </row>
     <row r="366" customHeight="1" ht="15" spans="1:10">
       <c r="A366" s="1" t="n">
-        <v>804095</v>
+        <v>811761</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>372</v>
@@ -13320,7 +13317,7 @@
         <v>2</v>
       </c>
       <c r="F366" s="3" t="n">
-        <v>5244</v>
+        <v>500</v>
       </c>
       <c r="G366" s="3" t="n">
         <v>0</v>
@@ -13337,7 +13334,7 @@
     </row>
     <row r="367" customHeight="1" ht="15" spans="1:10">
       <c r="A367" s="1" t="n">
-        <v>811761</v>
+        <v>804428</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>373</v>
@@ -13352,7 +13349,7 @@
         <v>2</v>
       </c>
       <c r="F367" s="3" t="n">
-        <v>500</v>
+        <v>50618</v>
       </c>
       <c r="G367" s="3" t="n">
         <v>0</v>
@@ -13369,22 +13366,22 @@
     </row>
     <row r="368" customHeight="1" ht="15" spans="1:10">
       <c r="A368" s="1" t="n">
-        <v>804428</v>
+        <v>204027</v>
       </c>
       <c r="B368" s="1" t="s">
         <v>374</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>2</v>
+        <v>375</v>
       </c>
       <c r="F368" s="3" t="n">
-        <v>50618</v>
+        <v>27.091437</v>
       </c>
       <c r="G368" s="3" t="n">
         <v>0</v>
@@ -13401,10 +13398,10 @@
     </row>
     <row r="369" customHeight="1" ht="15" spans="1:10">
       <c r="A369" s="1" t="n">
-        <v>204027</v>
+        <v>204028</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -13413,10 +13410,10 @@
         <v>1</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F369" s="3" t="n">
-        <v>27.091437</v>
+        <v>132.636982</v>
       </c>
       <c r="G369" s="3" t="n">
         <v>0</v>
@@ -13433,7 +13430,7 @@
     </row>
     <row r="370" customHeight="1" ht="15" spans="1:10">
       <c r="A370" s="1" t="n">
-        <v>204028</v>
+        <v>204009</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>377</v>
@@ -13445,10 +13442,10 @@
         <v>1</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F370" s="3" t="n">
-        <v>132.636982</v>
+        <v>8211.565709</v>
       </c>
       <c r="G370" s="3" t="n">
         <v>0</v>
@@ -13465,7 +13462,7 @@
     </row>
     <row r="371" customHeight="1" ht="15" spans="1:10">
       <c r="A371" s="1" t="n">
-        <v>204009</v>
+        <v>204023</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>378</v>
@@ -13477,10 +13474,10 @@
         <v>1</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F371" s="3" t="n">
-        <v>8211.565709</v>
+        <v>381.705057</v>
       </c>
       <c r="G371" s="3" t="n">
         <v>0</v>
@@ -13497,7 +13494,7 @@
     </row>
     <row r="372" customHeight="1" ht="15" spans="1:10">
       <c r="A372" s="1" t="n">
-        <v>204023</v>
+        <v>204030</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>379</v>
@@ -13509,10 +13506,10 @@
         <v>1</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F372" s="3" t="n">
-        <v>381.705057</v>
+        <v>363.963308</v>
       </c>
       <c r="G372" s="3" t="n">
         <v>0</v>
@@ -13529,7 +13526,7 @@
     </row>
     <row r="373" customHeight="1" ht="15" spans="1:10">
       <c r="A373" s="1" t="n">
-        <v>204030</v>
+        <v>204029</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>380</v>
@@ -13541,10 +13538,10 @@
         <v>1</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F373" s="3" t="n">
-        <v>363.963308</v>
+        <v>106.989603</v>
       </c>
       <c r="G373" s="3" t="n">
         <v>0</v>
@@ -13561,22 +13558,22 @@
     </row>
     <row r="374" customHeight="1" ht="15" spans="1:10">
       <c r="A374" s="1" t="n">
-        <v>204029</v>
+        <v>804556</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>381</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>376</v>
+        <v>2</v>
       </c>
       <c r="F374" s="3" t="n">
-        <v>106.989603</v>
+        <v>1441</v>
       </c>
       <c r="G374" s="3" t="n">
         <v>0</v>
@@ -13593,7 +13590,7 @@
     </row>
     <row r="375" customHeight="1" ht="15" spans="1:10">
       <c r="A375" s="1" t="n">
-        <v>804556</v>
+        <v>813578</v>
       </c>
       <c r="B375" s="1" t="s">
         <v>382</v>
@@ -13608,7 +13605,7 @@
         <v>2</v>
       </c>
       <c r="F375" s="3" t="n">
-        <v>1441</v>
+        <v>80</v>
       </c>
       <c r="G375" s="3" t="n">
         <v>0</v>
@@ -13625,7 +13622,7 @@
     </row>
     <row r="376" customHeight="1" ht="15" spans="1:10">
       <c r="A376" s="1" t="n">
-        <v>813578</v>
+        <v>804041</v>
       </c>
       <c r="B376" s="1" t="s">
         <v>383</v>
@@ -13640,7 +13637,7 @@
         <v>2</v>
       </c>
       <c r="F376" s="3" t="n">
-        <v>80</v>
+        <v>7525</v>
       </c>
       <c r="G376" s="3" t="n">
         <v>0</v>
@@ -13657,7 +13654,7 @@
     </row>
     <row r="377" customHeight="1" ht="15" spans="1:10">
       <c r="A377" s="1" t="n">
-        <v>804041</v>
+        <v>804026</v>
       </c>
       <c r="B377" s="1" t="s">
         <v>384</v>
@@ -13672,7 +13669,7 @@
         <v>2</v>
       </c>
       <c r="F377" s="3" t="n">
-        <v>7525</v>
+        <v>905</v>
       </c>
       <c r="G377" s="3" t="n">
         <v>0</v>
@@ -13689,7 +13686,7 @@
     </row>
     <row r="378" customHeight="1" ht="15" spans="1:10">
       <c r="A378" s="1" t="n">
-        <v>804026</v>
+        <v>804025</v>
       </c>
       <c r="B378" s="1" t="s">
         <v>385</v>
@@ -13704,7 +13701,7 @@
         <v>2</v>
       </c>
       <c r="F378" s="3" t="n">
-        <v>905</v>
+        <v>12750</v>
       </c>
       <c r="G378" s="3" t="n">
         <v>0</v>
@@ -13721,7 +13718,7 @@
     </row>
     <row r="379" customHeight="1" ht="15" spans="1:10">
       <c r="A379" s="1" t="n">
-        <v>804025</v>
+        <v>804024</v>
       </c>
       <c r="B379" s="1" t="s">
         <v>386</v>
@@ -13736,7 +13733,7 @@
         <v>2</v>
       </c>
       <c r="F379" s="3" t="n">
-        <v>12750</v>
+        <v>22340</v>
       </c>
       <c r="G379" s="3" t="n">
         <v>0</v>
@@ -13753,7 +13750,7 @@
     </row>
     <row r="380" customHeight="1" ht="15" spans="1:10">
       <c r="A380" s="1" t="n">
-        <v>804024</v>
+        <v>804090</v>
       </c>
       <c r="B380" s="1" t="s">
         <v>387</v>
@@ -13768,7 +13765,7 @@
         <v>2</v>
       </c>
       <c r="F380" s="3" t="n">
-        <v>22340</v>
+        <v>25925</v>
       </c>
       <c r="G380" s="3" t="n">
         <v>0</v>
@@ -13785,7 +13782,7 @@
     </row>
     <row r="381" customHeight="1" ht="15" spans="1:10">
       <c r="A381" s="1" t="n">
-        <v>804090</v>
+        <v>804089</v>
       </c>
       <c r="B381" s="1" t="s">
         <v>388</v>
@@ -13800,7 +13797,7 @@
         <v>2</v>
       </c>
       <c r="F381" s="3" t="n">
-        <v>25925</v>
+        <v>6553</v>
       </c>
       <c r="G381" s="3" t="n">
         <v>0</v>
@@ -13817,7 +13814,7 @@
     </row>
     <row r="382" customHeight="1" ht="15" spans="1:10">
       <c r="A382" s="1" t="n">
-        <v>804089</v>
+        <v>804500</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>389</v>
@@ -13832,7 +13829,7 @@
         <v>2</v>
       </c>
       <c r="F382" s="3" t="n">
-        <v>6553</v>
+        <v>768</v>
       </c>
       <c r="G382" s="3" t="n">
         <v>0</v>
@@ -13849,7 +13846,7 @@
     </row>
     <row r="383" customHeight="1" ht="15" spans="1:10">
       <c r="A383" s="1" t="n">
-        <v>804500</v>
+        <v>804505</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>390</v>
@@ -13864,7 +13861,7 @@
         <v>2</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>768</v>
+        <v>1132</v>
       </c>
       <c r="G383" s="3" t="n">
         <v>0</v>
@@ -13881,7 +13878,7 @@
     </row>
     <row r="384" customHeight="1" ht="15" spans="1:10">
       <c r="A384" s="1" t="n">
-        <v>804505</v>
+        <v>804101</v>
       </c>
       <c r="B384" s="1" t="s">
         <v>391</v>
@@ -13896,7 +13893,7 @@
         <v>2</v>
       </c>
       <c r="F384" s="3" t="n">
-        <v>1132</v>
+        <v>19191</v>
       </c>
       <c r="G384" s="3" t="n">
         <v>0</v>
@@ -13913,7 +13910,7 @@
     </row>
     <row r="385" customHeight="1" ht="15" spans="1:10">
       <c r="A385" s="1" t="n">
-        <v>804101</v>
+        <v>804102</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>392</v>
@@ -13928,7 +13925,7 @@
         <v>2</v>
       </c>
       <c r="F385" s="3" t="n">
-        <v>19191</v>
+        <v>17315</v>
       </c>
       <c r="G385" s="3" t="n">
         <v>0</v>
@@ -13945,7 +13942,7 @@
     </row>
     <row r="386" customHeight="1" ht="15" spans="1:10">
       <c r="A386" s="1" t="n">
-        <v>804102</v>
+        <v>804255</v>
       </c>
       <c r="B386" s="1" t="s">
         <v>393</v>
@@ -13960,7 +13957,7 @@
         <v>2</v>
       </c>
       <c r="F386" s="3" t="n">
-        <v>17315</v>
+        <v>1480</v>
       </c>
       <c r="G386" s="3" t="n">
         <v>0</v>
@@ -13977,7 +13974,7 @@
     </row>
     <row r="387" customHeight="1" ht="15" spans="1:10">
       <c r="A387" s="1" t="n">
-        <v>804255</v>
+        <v>813331</v>
       </c>
       <c r="B387" s="1" t="s">
         <v>394</v>
@@ -13992,7 +13989,7 @@
         <v>2</v>
       </c>
       <c r="F387" s="3" t="n">
-        <v>1480</v>
+        <v>19706</v>
       </c>
       <c r="G387" s="3" t="n">
         <v>0</v>
@@ -14009,7 +14006,7 @@
     </row>
     <row r="388" customHeight="1" ht="15" spans="1:10">
       <c r="A388" s="1" t="n">
-        <v>813331</v>
+        <v>804229</v>
       </c>
       <c r="B388" s="1" t="s">
         <v>395</v>
@@ -14024,7 +14021,7 @@
         <v>2</v>
       </c>
       <c r="F388" s="3" t="n">
-        <v>20246</v>
+        <v>8949</v>
       </c>
       <c r="G388" s="3" t="n">
         <v>0</v>
@@ -14041,7 +14038,7 @@
     </row>
     <row r="389" customHeight="1" ht="15" spans="1:10">
       <c r="A389" s="1" t="n">
-        <v>804229</v>
+        <v>804484</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>396</v>
@@ -14056,7 +14053,7 @@
         <v>2</v>
       </c>
       <c r="F389" s="3" t="n">
-        <v>8949</v>
+        <v>11359</v>
       </c>
       <c r="G389" s="3" t="n">
         <v>0</v>
@@ -14073,7 +14070,7 @@
     </row>
     <row r="390" customHeight="1" ht="15" spans="1:10">
       <c r="A390" s="1" t="n">
-        <v>804484</v>
+        <v>813508</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>397</v>
@@ -14088,7 +14085,7 @@
         <v>2</v>
       </c>
       <c r="F390" s="3" t="n">
-        <v>11359</v>
+        <v>14702</v>
       </c>
       <c r="G390" s="3" t="n">
         <v>0</v>
@@ -14105,7 +14102,7 @@
     </row>
     <row r="391" customHeight="1" ht="15" spans="1:10">
       <c r="A391" s="1" t="n">
-        <v>813508</v>
+        <v>813144</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>398</v>
@@ -14120,7 +14117,7 @@
         <v>2</v>
       </c>
       <c r="F391" s="3" t="n">
-        <v>14702</v>
+        <v>16779</v>
       </c>
       <c r="G391" s="3" t="n">
         <v>0</v>
@@ -14137,7 +14134,7 @@
     </row>
     <row r="392" customHeight="1" ht="15" spans="1:10">
       <c r="A392" s="1" t="n">
-        <v>813144</v>
+        <v>804579</v>
       </c>
       <c r="B392" s="1" t="s">
         <v>399</v>
@@ -14152,7 +14149,7 @@
         <v>2</v>
       </c>
       <c r="F392" s="3" t="n">
-        <v>18473</v>
+        <v>2758</v>
       </c>
       <c r="G392" s="3" t="n">
         <v>0</v>
@@ -14169,7 +14166,7 @@
     </row>
     <row r="393" customHeight="1" ht="15" spans="1:10">
       <c r="A393" s="1" t="n">
-        <v>804579</v>
+        <v>804568</v>
       </c>
       <c r="B393" s="1" t="s">
         <v>400</v>
@@ -14184,7 +14181,7 @@
         <v>2</v>
       </c>
       <c r="F393" s="3" t="n">
-        <v>2758</v>
+        <v>5097</v>
       </c>
       <c r="G393" s="3" t="n">
         <v>0</v>
@@ -14201,7 +14198,7 @@
     </row>
     <row r="394" customHeight="1" ht="15" spans="1:10">
       <c r="A394" s="1" t="n">
-        <v>804568</v>
+        <v>813267</v>
       </c>
       <c r="B394" s="1" t="s">
         <v>401</v>
@@ -14216,7 +14213,7 @@
         <v>2</v>
       </c>
       <c r="F394" s="3" t="n">
-        <v>5097</v>
+        <v>22046</v>
       </c>
       <c r="G394" s="3" t="n">
         <v>0</v>
@@ -14233,7 +14230,7 @@
     </row>
     <row r="395" customHeight="1" ht="15" spans="1:10">
       <c r="A395" s="1" t="n">
-        <v>813267</v>
+        <v>813051</v>
       </c>
       <c r="B395" s="1" t="s">
         <v>402</v>
@@ -14248,7 +14245,7 @@
         <v>2</v>
       </c>
       <c r="F395" s="3" t="n">
-        <v>22046</v>
+        <v>14377</v>
       </c>
       <c r="G395" s="3" t="n">
         <v>0</v>
@@ -14265,7 +14262,7 @@
     </row>
     <row r="396" customHeight="1" ht="15" spans="1:10">
       <c r="A396" s="1" t="n">
-        <v>813051</v>
+        <v>804483</v>
       </c>
       <c r="B396" s="1" t="s">
         <v>403</v>
@@ -14280,7 +14277,7 @@
         <v>2</v>
       </c>
       <c r="F396" s="3" t="n">
-        <v>14377</v>
+        <v>2960</v>
       </c>
       <c r="G396" s="3" t="n">
         <v>0</v>
@@ -14297,7 +14294,7 @@
     </row>
     <row r="397" customHeight="1" ht="15" spans="1:10">
       <c r="A397" s="1" t="n">
-        <v>804483</v>
+        <v>804482</v>
       </c>
       <c r="B397" s="1" t="s">
         <v>404</v>
@@ -14312,7 +14309,7 @@
         <v>2</v>
       </c>
       <c r="F397" s="3" t="n">
-        <v>3570</v>
+        <v>11331</v>
       </c>
       <c r="G397" s="3" t="n">
         <v>0</v>
@@ -14329,7 +14326,7 @@
     </row>
     <row r="398" customHeight="1" ht="15" spans="1:10">
       <c r="A398" s="1" t="n">
-        <v>804482</v>
+        <v>804403</v>
       </c>
       <c r="B398" s="1" t="s">
         <v>405</v>
@@ -14344,7 +14341,7 @@
         <v>2</v>
       </c>
       <c r="F398" s="3" t="n">
-        <v>11931</v>
+        <v>2095</v>
       </c>
       <c r="G398" s="3" t="n">
         <v>0</v>
@@ -14361,7 +14358,7 @@
     </row>
     <row r="399" customHeight="1" ht="15" spans="1:10">
       <c r="A399" s="1" t="n">
-        <v>804403</v>
+        <v>804533</v>
       </c>
       <c r="B399" s="1" t="s">
         <v>406</v>
@@ -14376,7 +14373,7 @@
         <v>2</v>
       </c>
       <c r="F399" s="3" t="n">
-        <v>2095</v>
+        <v>695</v>
       </c>
       <c r="G399" s="3" t="n">
         <v>0</v>
@@ -14393,7 +14390,7 @@
     </row>
     <row r="400" customHeight="1" ht="15" spans="1:10">
       <c r="A400" s="1" t="n">
-        <v>804533</v>
+        <v>804613</v>
       </c>
       <c r="B400" s="1" t="s">
         <v>407</v>
@@ -14408,7 +14405,7 @@
         <v>2</v>
       </c>
       <c r="F400" s="3" t="n">
-        <v>695</v>
+        <v>122</v>
       </c>
       <c r="G400" s="3" t="n">
         <v>0</v>
@@ -14425,7 +14422,7 @@
     </row>
     <row r="401" customHeight="1" ht="15" spans="1:10">
       <c r="A401" s="1" t="n">
-        <v>804613</v>
+        <v>804038</v>
       </c>
       <c r="B401" s="1" t="s">
         <v>408</v>
@@ -14440,7 +14437,7 @@
         <v>2</v>
       </c>
       <c r="F401" s="3" t="n">
-        <v>122</v>
+        <v>6926</v>
       </c>
       <c r="G401" s="3" t="n">
         <v>0</v>
@@ -14457,7 +14454,7 @@
     </row>
     <row r="402" customHeight="1" ht="15" spans="1:10">
       <c r="A402" s="1" t="n">
-        <v>804038</v>
+        <v>804434</v>
       </c>
       <c r="B402" s="1" t="s">
         <v>409</v>
@@ -14472,7 +14469,7 @@
         <v>2</v>
       </c>
       <c r="F402" s="3" t="n">
-        <v>6926</v>
+        <v>3481</v>
       </c>
       <c r="G402" s="3" t="n">
         <v>0</v>
@@ -14489,7 +14486,7 @@
     </row>
     <row r="403" customHeight="1" ht="15" spans="1:10">
       <c r="A403" s="1" t="n">
-        <v>804434</v>
+        <v>804040</v>
       </c>
       <c r="B403" s="1" t="s">
         <v>410</v>
@@ -14504,7 +14501,7 @@
         <v>2</v>
       </c>
       <c r="F403" s="3" t="n">
-        <v>3481</v>
+        <v>2441</v>
       </c>
       <c r="G403" s="3" t="n">
         <v>0</v>
@@ -14521,7 +14518,7 @@
     </row>
     <row r="404" customHeight="1" ht="15" spans="1:10">
       <c r="A404" s="1" t="n">
-        <v>804040</v>
+        <v>813541</v>
       </c>
       <c r="B404" s="1" t="s">
         <v>411</v>
@@ -14536,7 +14533,7 @@
         <v>2</v>
       </c>
       <c r="F404" s="3" t="n">
-        <v>2441</v>
+        <v>3352</v>
       </c>
       <c r="G404" s="3" t="n">
         <v>0</v>
@@ -14553,7 +14550,7 @@
     </row>
     <row r="405" customHeight="1" ht="15" spans="1:10">
       <c r="A405" s="1" t="n">
-        <v>813541</v>
+        <v>804545</v>
       </c>
       <c r="B405" s="1" t="s">
         <v>412</v>
@@ -14568,7 +14565,7 @@
         <v>2</v>
       </c>
       <c r="F405" s="3" t="n">
-        <v>3352</v>
+        <v>5994</v>
       </c>
       <c r="G405" s="3" t="n">
         <v>0</v>
@@ -14585,7 +14582,7 @@
     </row>
     <row r="406" customHeight="1" ht="15" spans="1:10">
       <c r="A406" s="1" t="n">
-        <v>804545</v>
+        <v>804439</v>
       </c>
       <c r="B406" s="1" t="s">
         <v>413</v>
@@ -14600,7 +14597,7 @@
         <v>2</v>
       </c>
       <c r="F406" s="3" t="n">
-        <v>5994</v>
+        <v>1720</v>
       </c>
       <c r="G406" s="3" t="n">
         <v>0</v>
@@ -14617,7 +14614,7 @@
     </row>
     <row r="407" customHeight="1" ht="15" spans="1:10">
       <c r="A407" s="1" t="n">
-        <v>804439</v>
+        <v>804094</v>
       </c>
       <c r="B407" s="1" t="s">
         <v>414</v>
@@ -14632,7 +14629,7 @@
         <v>2</v>
       </c>
       <c r="F407" s="3" t="n">
-        <v>1720</v>
+        <v>11141</v>
       </c>
       <c r="G407" s="3" t="n">
         <v>0</v>
@@ -14649,7 +14646,7 @@
     </row>
     <row r="408" customHeight="1" ht="15" spans="1:10">
       <c r="A408" s="1" t="n">
-        <v>804094</v>
+        <v>804390</v>
       </c>
       <c r="B408" s="1" t="s">
         <v>415</v>
@@ -14664,7 +14661,7 @@
         <v>2</v>
       </c>
       <c r="F408" s="3" t="n">
-        <v>11141</v>
+        <v>4657</v>
       </c>
       <c r="G408" s="3" t="n">
         <v>0</v>
@@ -14681,7 +14678,7 @@
     </row>
     <row r="409" customHeight="1" ht="15" spans="1:10">
       <c r="A409" s="1" t="n">
-        <v>804390</v>
+        <v>804096</v>
       </c>
       <c r="B409" s="1" t="s">
         <v>416</v>
@@ -14696,7 +14693,7 @@
         <v>2</v>
       </c>
       <c r="F409" s="3" t="n">
-        <v>4657</v>
+        <v>20318</v>
       </c>
       <c r="G409" s="3" t="n">
         <v>0</v>
@@ -14713,7 +14710,7 @@
     </row>
     <row r="410" customHeight="1" ht="15" spans="1:10">
       <c r="A410" s="1" t="n">
-        <v>804096</v>
+        <v>804092</v>
       </c>
       <c r="B410" s="1" t="s">
         <v>417</v>
@@ -14728,7 +14725,7 @@
         <v>2</v>
       </c>
       <c r="F410" s="3" t="n">
-        <v>20318</v>
+        <v>8123</v>
       </c>
       <c r="G410" s="3" t="n">
         <v>0</v>
@@ -14745,7 +14742,7 @@
     </row>
     <row r="411" customHeight="1" ht="15" spans="1:10">
       <c r="A411" s="1" t="n">
-        <v>804092</v>
+        <v>804091</v>
       </c>
       <c r="B411" s="1" t="s">
         <v>418</v>
@@ -14760,7 +14757,7 @@
         <v>2</v>
       </c>
       <c r="F411" s="3" t="n">
-        <v>8123</v>
+        <v>15957</v>
       </c>
       <c r="G411" s="3" t="n">
         <v>0</v>
@@ -14777,7 +14774,7 @@
     </row>
     <row r="412" customHeight="1" ht="15" spans="1:10">
       <c r="A412" s="1" t="n">
-        <v>804091</v>
+        <v>813517</v>
       </c>
       <c r="B412" s="1" t="s">
         <v>419</v>
@@ -14792,7 +14789,7 @@
         <v>2</v>
       </c>
       <c r="F412" s="3" t="n">
-        <v>15957</v>
+        <v>4768</v>
       </c>
       <c r="G412" s="3" t="n">
         <v>0</v>
@@ -14809,7 +14806,7 @@
     </row>
     <row r="413" customHeight="1" ht="15" spans="1:10">
       <c r="A413" s="1" t="n">
-        <v>813517</v>
+        <v>804461</v>
       </c>
       <c r="B413" s="1" t="s">
         <v>420</v>
@@ -14824,7 +14821,7 @@
         <v>2</v>
       </c>
       <c r="F413" s="3" t="n">
-        <v>4768</v>
+        <v>768</v>
       </c>
       <c r="G413" s="3" t="n">
         <v>0</v>
@@ -14841,7 +14838,7 @@
     </row>
     <row r="414" customHeight="1" ht="15" spans="1:10">
       <c r="A414" s="1" t="n">
-        <v>804461</v>
+        <v>804580</v>
       </c>
       <c r="B414" s="1" t="s">
         <v>421</v>
@@ -14856,7 +14853,7 @@
         <v>2</v>
       </c>
       <c r="F414" s="3" t="n">
-        <v>822</v>
+        <v>3228</v>
       </c>
       <c r="G414" s="3" t="n">
         <v>0</v>
@@ -14873,7 +14870,7 @@
     </row>
     <row r="415" customHeight="1" ht="15" spans="1:10">
       <c r="A415" s="1" t="n">
-        <v>804580</v>
+        <v>813504</v>
       </c>
       <c r="B415" s="1" t="s">
         <v>422</v>
@@ -14888,7 +14885,7 @@
         <v>2</v>
       </c>
       <c r="F415" s="3" t="n">
-        <v>3228</v>
+        <v>528</v>
       </c>
       <c r="G415" s="3" t="n">
         <v>0</v>
@@ -14905,7 +14902,7 @@
     </row>
     <row r="416" customHeight="1" ht="15" spans="1:10">
       <c r="A416" s="1" t="n">
-        <v>813504</v>
+        <v>804248</v>
       </c>
       <c r="B416" s="1" t="s">
         <v>423</v>
@@ -14920,7 +14917,7 @@
         <v>2</v>
       </c>
       <c r="F416" s="3" t="n">
-        <v>528</v>
+        <v>498</v>
       </c>
       <c r="G416" s="3" t="n">
         <v>0</v>
@@ -14937,7 +14934,7 @@
     </row>
     <row r="417" customHeight="1" ht="15" spans="1:10">
       <c r="A417" s="1" t="n">
-        <v>804248</v>
+        <v>804426</v>
       </c>
       <c r="B417" s="1" t="s">
         <v>424</v>
@@ -14952,7 +14949,7 @@
         <v>2</v>
       </c>
       <c r="F417" s="3" t="n">
-        <v>498</v>
+        <v>900</v>
       </c>
       <c r="G417" s="3" t="n">
         <v>0</v>
@@ -14969,7 +14966,7 @@
     </row>
     <row r="418" customHeight="1" ht="15" spans="1:10">
       <c r="A418" s="1" t="n">
-        <v>804426</v>
+        <v>813179</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>425</v>
@@ -14984,7 +14981,7 @@
         <v>2</v>
       </c>
       <c r="F418" s="3" t="n">
-        <v>900</v>
+        <v>1561</v>
       </c>
       <c r="G418" s="3" t="n">
         <v>0</v>
@@ -15001,7 +14998,7 @@
     </row>
     <row r="419" customHeight="1" ht="15" spans="1:10">
       <c r="A419" s="1" t="n">
-        <v>813179</v>
+        <v>813256</v>
       </c>
       <c r="B419" s="1" t="s">
         <v>426</v>
@@ -15016,7 +15013,7 @@
         <v>2</v>
       </c>
       <c r="F419" s="3" t="n">
-        <v>1561</v>
+        <v>2458</v>
       </c>
       <c r="G419" s="3" t="n">
         <v>0</v>
@@ -15033,7 +15030,7 @@
     </row>
     <row r="420" customHeight="1" ht="15" spans="1:10">
       <c r="A420" s="1" t="n">
-        <v>813256</v>
+        <v>804569</v>
       </c>
       <c r="B420" s="1" t="s">
         <v>427</v>
@@ -15048,7 +15045,7 @@
         <v>2</v>
       </c>
       <c r="F420" s="3" t="n">
-        <v>2660</v>
+        <v>1350</v>
       </c>
       <c r="G420" s="3" t="n">
         <v>0</v>
@@ -15065,7 +15062,7 @@
     </row>
     <row r="421" customHeight="1" ht="15" spans="1:10">
       <c r="A421" s="1" t="n">
-        <v>804569</v>
+        <v>804537</v>
       </c>
       <c r="B421" s="1" t="s">
         <v>428</v>
@@ -15080,7 +15077,7 @@
         <v>2</v>
       </c>
       <c r="F421" s="3" t="n">
-        <v>1350</v>
+        <v>1059</v>
       </c>
       <c r="G421" s="3" t="n">
         <v>0</v>
@@ -15097,7 +15094,7 @@
     </row>
     <row r="422" customHeight="1" ht="15" spans="1:10">
       <c r="A422" s="1" t="n">
-        <v>804537</v>
+        <v>804047</v>
       </c>
       <c r="B422" s="1" t="s">
         <v>429</v>
@@ -15112,7 +15109,7 @@
         <v>2</v>
       </c>
       <c r="F422" s="3" t="n">
-        <v>1059</v>
+        <v>7538</v>
       </c>
       <c r="G422" s="3" t="n">
         <v>0</v>
@@ -15129,7 +15126,7 @@
     </row>
     <row r="423" customHeight="1" ht="15" spans="1:10">
       <c r="A423" s="1" t="n">
-        <v>804047</v>
+        <v>804605</v>
       </c>
       <c r="B423" s="1" t="s">
         <v>430</v>
@@ -15144,7 +15141,7 @@
         <v>2</v>
       </c>
       <c r="F423" s="3" t="n">
-        <v>7538</v>
+        <v>6516</v>
       </c>
       <c r="G423" s="3" t="n">
         <v>0</v>
@@ -15161,7 +15158,7 @@
     </row>
     <row r="424" customHeight="1" ht="15" spans="1:10">
       <c r="A424" s="1" t="n">
-        <v>804605</v>
+        <v>804606</v>
       </c>
       <c r="B424" s="1" t="s">
         <v>431</v>
@@ -15176,7 +15173,7 @@
         <v>2</v>
       </c>
       <c r="F424" s="3" t="n">
-        <v>6516</v>
+        <v>6194</v>
       </c>
       <c r="G424" s="3" t="n">
         <v>0</v>
@@ -15193,7 +15190,7 @@
     </row>
     <row r="425" customHeight="1" ht="15" spans="1:10">
       <c r="A425" s="1" t="n">
-        <v>804606</v>
+        <v>804327</v>
       </c>
       <c r="B425" s="1" t="s">
         <v>432</v>
@@ -15208,7 +15205,7 @@
         <v>2</v>
       </c>
       <c r="F425" s="3" t="n">
-        <v>6194</v>
+        <v>2573</v>
       </c>
       <c r="G425" s="3" t="n">
         <v>0</v>
@@ -15225,7 +15222,7 @@
     </row>
     <row r="426" customHeight="1" ht="15" spans="1:10">
       <c r="A426" s="1" t="n">
-        <v>804327</v>
+        <v>813033</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>433</v>
@@ -15240,7 +15237,7 @@
         <v>2</v>
       </c>
       <c r="F426" s="3" t="n">
-        <v>2573</v>
+        <v>929</v>
       </c>
       <c r="G426" s="3" t="n">
         <v>0</v>
@@ -15257,7 +15254,7 @@
     </row>
     <row r="427" customHeight="1" ht="15" spans="1:10">
       <c r="A427" s="1" t="n">
-        <v>813033</v>
+        <v>804501</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>434</v>
@@ -15272,7 +15269,7 @@
         <v>2</v>
       </c>
       <c r="F427" s="3" t="n">
-        <v>929</v>
+        <v>2259</v>
       </c>
       <c r="G427" s="3" t="n">
         <v>0</v>
@@ -15289,7 +15286,7 @@
     </row>
     <row r="428" customHeight="1" ht="15" spans="1:10">
       <c r="A428" s="1" t="n">
-        <v>804501</v>
+        <v>804398</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>435</v>
@@ -15304,7 +15301,7 @@
         <v>2</v>
       </c>
       <c r="F428" s="3" t="n">
-        <v>2259</v>
+        <v>1535</v>
       </c>
       <c r="G428" s="3" t="n">
         <v>0</v>
@@ -15321,7 +15318,7 @@
     </row>
     <row r="429" customHeight="1" ht="15" spans="1:10">
       <c r="A429" s="1" t="n">
-        <v>804398</v>
+        <v>804504</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>436</v>
@@ -15336,7 +15333,7 @@
         <v>2</v>
       </c>
       <c r="F429" s="3" t="n">
-        <v>1535</v>
+        <v>631</v>
       </c>
       <c r="G429" s="3" t="n">
         <v>0</v>
@@ -15353,7 +15350,7 @@
     </row>
     <row r="430" customHeight="1" ht="15" spans="1:10">
       <c r="A430" s="1" t="n">
-        <v>804504</v>
+        <v>813509</v>
       </c>
       <c r="B430" s="1" t="s">
         <v>437</v>
@@ -15368,7 +15365,7 @@
         <v>2</v>
       </c>
       <c r="F430" s="3" t="n">
-        <v>631</v>
+        <v>14900</v>
       </c>
       <c r="G430" s="3" t="n">
         <v>0</v>
@@ -15385,7 +15382,7 @@
     </row>
     <row r="431" customHeight="1" ht="15" spans="1:10">
       <c r="A431" s="1" t="n">
-        <v>813509</v>
+        <v>804108</v>
       </c>
       <c r="B431" s="1" t="s">
         <v>438</v>
@@ -15400,7 +15397,7 @@
         <v>2</v>
       </c>
       <c r="F431" s="3" t="n">
-        <v>14900</v>
+        <v>5223</v>
       </c>
       <c r="G431" s="3" t="n">
         <v>0</v>
@@ -15417,7 +15414,7 @@
     </row>
     <row r="432" customHeight="1" ht="15" spans="1:10">
       <c r="A432" s="1" t="n">
-        <v>804108</v>
+        <v>804431</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>439</v>
@@ -15432,7 +15429,7 @@
         <v>2</v>
       </c>
       <c r="F432" s="3" t="n">
-        <v>8539</v>
+        <v>1158</v>
       </c>
       <c r="G432" s="3" t="n">
         <v>0</v>
@@ -15449,7 +15446,7 @@
     </row>
     <row r="433" customHeight="1" ht="15" spans="1:10">
       <c r="A433" s="1" t="n">
-        <v>804431</v>
+        <v>804197</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>440</v>
@@ -15464,7 +15461,7 @@
         <v>2</v>
       </c>
       <c r="F433" s="3" t="n">
-        <v>1160</v>
+        <v>2522</v>
       </c>
       <c r="G433" s="3" t="n">
         <v>0</v>
@@ -15481,7 +15478,7 @@
     </row>
     <row r="434" customHeight="1" ht="15" spans="1:10">
       <c r="A434" s="1" t="n">
-        <v>804197</v>
+        <v>804263</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>441</v>
@@ -15496,7 +15493,7 @@
         <v>2</v>
       </c>
       <c r="F434" s="3" t="n">
-        <v>2522</v>
+        <v>1252</v>
       </c>
       <c r="G434" s="3" t="n">
         <v>0</v>
@@ -15513,7 +15510,7 @@
     </row>
     <row r="435" customHeight="1" ht="15" spans="1:10">
       <c r="A435" s="1" t="n">
-        <v>804263</v>
+        <v>804587</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>442</v>
@@ -15528,7 +15525,7 @@
         <v>2</v>
       </c>
       <c r="F435" s="3" t="n">
-        <v>1252</v>
+        <v>3248</v>
       </c>
       <c r="G435" s="3" t="n">
         <v>0</v>
@@ -15545,7 +15542,7 @@
     </row>
     <row r="436" customHeight="1" ht="15" spans="1:10">
       <c r="A436" s="1" t="n">
-        <v>804587</v>
+        <v>804561</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>443</v>
@@ -15560,7 +15557,7 @@
         <v>2</v>
       </c>
       <c r="F436" s="3" t="n">
-        <v>3248</v>
+        <v>678</v>
       </c>
       <c r="G436" s="3" t="n">
         <v>0</v>
@@ -15577,7 +15574,7 @@
     </row>
     <row r="437" customHeight="1" ht="15" spans="1:10">
       <c r="A437" s="1" t="n">
-        <v>804561</v>
+        <v>804538</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>444</v>
@@ -15592,7 +15589,7 @@
         <v>2</v>
       </c>
       <c r="F437" s="3" t="n">
-        <v>678</v>
+        <v>80</v>
       </c>
       <c r="G437" s="3" t="n">
         <v>0</v>
@@ -15609,7 +15606,7 @@
     </row>
     <row r="438" customHeight="1" ht="15" spans="1:10">
       <c r="A438" s="1" t="n">
-        <v>804538</v>
+        <v>813266</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>445</v>
@@ -15624,7 +15621,7 @@
         <v>2</v>
       </c>
       <c r="F438" s="3" t="n">
-        <v>80</v>
+        <v>22732</v>
       </c>
       <c r="G438" s="3" t="n">
         <v>0</v>
@@ -15641,7 +15638,7 @@
     </row>
     <row r="439" customHeight="1" ht="15" spans="1:10">
       <c r="A439" s="1" t="n">
-        <v>813266</v>
+        <v>804565</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>446</v>
@@ -15656,7 +15653,7 @@
         <v>2</v>
       </c>
       <c r="F439" s="3" t="n">
-        <v>22732</v>
+        <v>1816</v>
       </c>
       <c r="G439" s="3" t="n">
         <v>0</v>
@@ -15673,7 +15670,7 @@
     </row>
     <row r="440" customHeight="1" ht="15" spans="1:10">
       <c r="A440" s="1" t="n">
-        <v>804565</v>
+        <v>804136</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>447</v>
@@ -15688,7 +15685,7 @@
         <v>2</v>
       </c>
       <c r="F440" s="3" t="n">
-        <v>1816</v>
+        <v>7912</v>
       </c>
       <c r="G440" s="3" t="n">
         <v>0</v>
@@ -15705,7 +15702,7 @@
     </row>
     <row r="441" customHeight="1" ht="15" spans="1:10">
       <c r="A441" s="1" t="n">
-        <v>804136</v>
+        <v>804141</v>
       </c>
       <c r="B441" s="1" t="s">
         <v>448</v>
@@ -15720,7 +15717,7 @@
         <v>2</v>
       </c>
       <c r="F441" s="3" t="n">
-        <v>8868</v>
+        <v>860</v>
       </c>
       <c r="G441" s="3" t="n">
         <v>0</v>
@@ -15737,7 +15734,7 @@
     </row>
     <row r="442" customHeight="1" ht="15" spans="1:10">
       <c r="A442" s="1" t="n">
-        <v>804141</v>
+        <v>804010</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>449</v>
@@ -15752,7 +15749,7 @@
         <v>2</v>
       </c>
       <c r="F442" s="3" t="n">
-        <v>860</v>
+        <v>1371</v>
       </c>
       <c r="G442" s="3" t="n">
         <v>0</v>
@@ -15769,7 +15766,7 @@
     </row>
     <row r="443" customHeight="1" ht="15" spans="1:10">
       <c r="A443" s="1" t="n">
-        <v>804010</v>
+        <v>804012</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>450</v>
@@ -15784,7 +15781,7 @@
         <v>2</v>
       </c>
       <c r="F443" s="3" t="n">
-        <v>1371</v>
+        <v>2246</v>
       </c>
       <c r="G443" s="3" t="n">
         <v>0</v>
@@ -15801,7 +15798,7 @@
     </row>
     <row r="444" customHeight="1" ht="15" spans="1:10">
       <c r="A444" s="1" t="n">
-        <v>804012</v>
+        <v>804427</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>451</v>
@@ -15816,7 +15813,7 @@
         <v>2</v>
       </c>
       <c r="F444" s="3" t="n">
-        <v>2246</v>
+        <v>6256</v>
       </c>
       <c r="G444" s="3" t="n">
         <v>0</v>
@@ -15833,7 +15830,7 @@
     </row>
     <row r="445" customHeight="1" ht="15" spans="1:10">
       <c r="A445" s="1" t="n">
-        <v>804427</v>
+        <v>804402</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>452</v>
@@ -15848,7 +15845,7 @@
         <v>2</v>
       </c>
       <c r="F445" s="3" t="n">
-        <v>6256</v>
+        <v>590</v>
       </c>
       <c r="G445" s="3" t="n">
         <v>0</v>
@@ -15865,7 +15862,7 @@
     </row>
     <row r="446" customHeight="1" ht="15" spans="1:10">
       <c r="A446" s="1" t="n">
-        <v>804402</v>
+        <v>804423</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>453</v>
@@ -15880,7 +15877,7 @@
         <v>2</v>
       </c>
       <c r="F446" s="3" t="n">
-        <v>590</v>
+        <v>4604</v>
       </c>
       <c r="G446" s="3" t="n">
         <v>0</v>
@@ -15897,7 +15894,7 @@
     </row>
     <row r="447" customHeight="1" ht="15" spans="1:10">
       <c r="A447" s="1" t="n">
-        <v>804423</v>
+        <v>813034</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>454</v>
@@ -15912,7 +15909,7 @@
         <v>2</v>
       </c>
       <c r="F447" s="3" t="n">
-        <v>4654</v>
+        <v>8101</v>
       </c>
       <c r="G447" s="3" t="n">
         <v>0</v>
@@ -15929,7 +15926,7 @@
     </row>
     <row r="448" customHeight="1" ht="15" spans="1:10">
       <c r="A448" s="1" t="n">
-        <v>813034</v>
+        <v>804520</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>455</v>
@@ -15944,7 +15941,7 @@
         <v>2</v>
       </c>
       <c r="F448" s="3" t="n">
-        <v>8101</v>
+        <v>105</v>
       </c>
       <c r="G448" s="3" t="n">
         <v>0</v>
@@ -15961,7 +15958,7 @@
     </row>
     <row r="449" customHeight="1" ht="15" spans="1:10">
       <c r="A449" s="1" t="n">
-        <v>804520</v>
+        <v>804135</v>
       </c>
       <c r="B449" s="1" t="s">
         <v>456</v>
@@ -15976,7 +15973,7 @@
         <v>2</v>
       </c>
       <c r="F449" s="3" t="n">
-        <v>105</v>
+        <v>1839</v>
       </c>
       <c r="G449" s="3" t="n">
         <v>0</v>
@@ -15993,7 +15990,7 @@
     </row>
     <row r="450" customHeight="1" ht="15" spans="1:10">
       <c r="A450" s="1" t="n">
-        <v>804135</v>
+        <v>804061</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>457</v>
@@ -16008,7 +16005,7 @@
         <v>2</v>
       </c>
       <c r="F450" s="3" t="n">
-        <v>1839</v>
+        <v>2611</v>
       </c>
       <c r="G450" s="3" t="n">
         <v>0</v>
@@ -16025,7 +16022,7 @@
     </row>
     <row r="451" customHeight="1" ht="15" spans="1:10">
       <c r="A451" s="1" t="n">
-        <v>804061</v>
+        <v>804325</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>458</v>
@@ -16040,7 +16037,7 @@
         <v>2</v>
       </c>
       <c r="F451" s="3" t="n">
-        <v>4584</v>
+        <v>6652</v>
       </c>
       <c r="G451" s="3" t="n">
         <v>0</v>
@@ -16057,7 +16054,7 @@
     </row>
     <row r="452" customHeight="1" ht="15" spans="1:10">
       <c r="A452" s="1" t="n">
-        <v>804325</v>
+        <v>804331</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>459</v>
@@ -16072,7 +16069,7 @@
         <v>2</v>
       </c>
       <c r="F452" s="3" t="n">
-        <v>6652</v>
+        <v>2338</v>
       </c>
       <c r="G452" s="3" t="n">
         <v>0</v>
@@ -16089,7 +16086,7 @@
     </row>
     <row r="453" customHeight="1" ht="15" spans="1:10">
       <c r="A453" s="1" t="n">
-        <v>804331</v>
+        <v>804473</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>460</v>
@@ -16104,7 +16101,7 @@
         <v>2</v>
       </c>
       <c r="F453" s="3" t="n">
-        <v>2338</v>
+        <v>1011</v>
       </c>
       <c r="G453" s="3" t="n">
         <v>0</v>
@@ -16121,7 +16118,7 @@
     </row>
     <row r="454" customHeight="1" ht="15" spans="1:10">
       <c r="A454" s="1" t="n">
-        <v>804473</v>
+        <v>804460</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>461</v>
@@ -16136,7 +16133,7 @@
         <v>2</v>
       </c>
       <c r="F454" s="3" t="n">
-        <v>1011</v>
+        <v>6067</v>
       </c>
       <c r="G454" s="3" t="n">
         <v>0</v>
@@ -16153,7 +16150,7 @@
     </row>
     <row r="455" customHeight="1" ht="15" spans="1:10">
       <c r="A455" s="1" t="n">
-        <v>804460</v>
+        <v>804306</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>462</v>
@@ -16168,7 +16165,7 @@
         <v>2</v>
       </c>
       <c r="F455" s="3" t="n">
-        <v>6067</v>
+        <v>6824</v>
       </c>
       <c r="G455" s="3" t="n">
         <v>0</v>
@@ -16185,7 +16182,7 @@
     </row>
     <row r="456" customHeight="1" ht="15" spans="1:10">
       <c r="A456" s="1" t="n">
-        <v>804306</v>
+        <v>813203</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>463</v>
@@ -16200,7 +16197,7 @@
         <v>2</v>
       </c>
       <c r="F456" s="3" t="n">
-        <v>6824</v>
+        <v>1324</v>
       </c>
       <c r="G456" s="3" t="n">
         <v>0</v>
@@ -16217,7 +16214,7 @@
     </row>
     <row r="457" customHeight="1" ht="15" spans="1:10">
       <c r="A457" s="1" t="n">
-        <v>813203</v>
+        <v>813036</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>464</v>
@@ -16232,7 +16229,7 @@
         <v>2</v>
       </c>
       <c r="F457" s="3" t="n">
-        <v>1330</v>
+        <v>1985</v>
       </c>
       <c r="G457" s="3" t="n">
         <v>0</v>
@@ -16249,7 +16246,7 @@
     </row>
     <row r="458" customHeight="1" ht="15" spans="1:10">
       <c r="A458" s="1" t="n">
-        <v>813036</v>
+        <v>813248</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>465</v>
@@ -16264,7 +16261,7 @@
         <v>2</v>
       </c>
       <c r="F458" s="3" t="n">
-        <v>1985</v>
+        <v>1396</v>
       </c>
       <c r="G458" s="3" t="n">
         <v>0</v>
@@ -16281,7 +16278,7 @@
     </row>
     <row r="459" customHeight="1" ht="15" spans="1:10">
       <c r="A459" s="1" t="n">
-        <v>813248</v>
+        <v>813024</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>466</v>
@@ -16296,7 +16293,7 @@
         <v>2</v>
       </c>
       <c r="F459" s="3" t="n">
-        <v>1996</v>
+        <v>3011</v>
       </c>
       <c r="G459" s="3" t="n">
         <v>0</v>
@@ -16313,7 +16310,7 @@
     </row>
     <row r="460" customHeight="1" ht="15" spans="1:10">
       <c r="A460" s="1" t="n">
-        <v>813024</v>
+        <v>804521</v>
       </c>
       <c r="B460" s="1" t="s">
         <v>467</v>
@@ -16328,7 +16325,7 @@
         <v>2</v>
       </c>
       <c r="F460" s="3" t="n">
-        <v>3011</v>
+        <v>748</v>
       </c>
       <c r="G460" s="3" t="n">
         <v>0</v>
@@ -16345,7 +16342,7 @@
     </row>
     <row r="461" customHeight="1" ht="15" spans="1:10">
       <c r="A461" s="1" t="n">
-        <v>804521</v>
+        <v>804307</v>
       </c>
       <c r="B461" s="1" t="s">
         <v>468</v>
@@ -16360,7 +16357,7 @@
         <v>2</v>
       </c>
       <c r="F461" s="3" t="n">
-        <v>748</v>
+        <v>1526</v>
       </c>
       <c r="G461" s="3" t="n">
         <v>0</v>
@@ -16377,7 +16374,7 @@
     </row>
     <row r="462" customHeight="1" ht="15" spans="1:10">
       <c r="A462" s="1" t="n">
-        <v>804307</v>
+        <v>804578</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>469</v>
@@ -16392,7 +16389,7 @@
         <v>2</v>
       </c>
       <c r="F462" s="3" t="n">
-        <v>1526</v>
+        <v>2484</v>
       </c>
       <c r="G462" s="3" t="n">
         <v>0</v>
@@ -16409,7 +16406,7 @@
     </row>
     <row r="463" customHeight="1" ht="15" spans="1:10">
       <c r="A463" s="1" t="n">
-        <v>804578</v>
+        <v>804567</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>470</v>
@@ -16424,7 +16421,7 @@
         <v>2</v>
       </c>
       <c r="F463" s="3" t="n">
-        <v>2484</v>
+        <v>3841</v>
       </c>
       <c r="G463" s="3" t="n">
         <v>0</v>
@@ -16441,7 +16438,7 @@
     </row>
     <row r="464" customHeight="1" ht="15" spans="1:10">
       <c r="A464" s="1" t="n">
-        <v>804567</v>
+        <v>804269</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>471</v>
@@ -16456,7 +16453,7 @@
         <v>2</v>
       </c>
       <c r="F464" s="3" t="n">
-        <v>3841</v>
+        <v>1191</v>
       </c>
       <c r="G464" s="3" t="n">
         <v>0</v>
@@ -16473,7 +16470,7 @@
     </row>
     <row r="465" customHeight="1" ht="15" spans="1:10">
       <c r="A465" s="1" t="n">
-        <v>804269</v>
+        <v>804266</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>472</v>
@@ -16488,7 +16485,7 @@
         <v>2</v>
       </c>
       <c r="F465" s="3" t="n">
-        <v>1191</v>
+        <v>1291</v>
       </c>
       <c r="G465" s="3" t="n">
         <v>0</v>
@@ -16505,7 +16502,7 @@
     </row>
     <row r="466" customHeight="1" ht="15" spans="1:10">
       <c r="A466" s="1" t="n">
-        <v>804266</v>
+        <v>804602</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>473</v>
@@ -16520,7 +16517,7 @@
         <v>2</v>
       </c>
       <c r="F466" s="3" t="n">
-        <v>1291</v>
+        <v>662</v>
       </c>
       <c r="G466" s="3" t="n">
         <v>0</v>
@@ -16537,7 +16534,7 @@
     </row>
     <row r="467" customHeight="1" ht="15" spans="1:10">
       <c r="A467" s="1" t="n">
-        <v>804602</v>
+        <v>804594</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>474</v>
@@ -16552,7 +16549,7 @@
         <v>2</v>
       </c>
       <c r="F467" s="3" t="n">
-        <v>662</v>
+        <v>2101</v>
       </c>
       <c r="G467" s="3" t="n">
         <v>0</v>
@@ -16569,7 +16566,7 @@
     </row>
     <row r="468" customHeight="1" ht="15" spans="1:10">
       <c r="A468" s="1" t="n">
-        <v>804594</v>
+        <v>804223</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>475</v>
@@ -16584,7 +16581,7 @@
         <v>2</v>
       </c>
       <c r="F468" s="3" t="n">
-        <v>2101</v>
+        <v>1712</v>
       </c>
       <c r="G468" s="3" t="n">
         <v>0</v>
@@ -16601,7 +16598,7 @@
     </row>
     <row r="469" customHeight="1" ht="15" spans="1:10">
       <c r="A469" s="1" t="n">
-        <v>804223</v>
+        <v>804222</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>476</v>
@@ -16616,7 +16613,7 @@
         <v>2</v>
       </c>
       <c r="F469" s="3" t="n">
-        <v>1712</v>
+        <v>2673</v>
       </c>
       <c r="G469" s="3" t="n">
         <v>0</v>
@@ -16633,7 +16630,7 @@
     </row>
     <row r="470" customHeight="1" ht="15" spans="1:10">
       <c r="A470" s="1" t="n">
-        <v>804222</v>
+        <v>813409</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>477</v>
@@ -16648,7 +16645,7 @@
         <v>2</v>
       </c>
       <c r="F470" s="3" t="n">
-        <v>2673</v>
+        <v>8205</v>
       </c>
       <c r="G470" s="3" t="n">
         <v>0</v>
@@ -16665,7 +16662,7 @@
     </row>
     <row r="471" customHeight="1" ht="15" spans="1:10">
       <c r="A471" s="1" t="n">
-        <v>813409</v>
+        <v>804206</v>
       </c>
       <c r="B471" s="1" t="s">
         <v>478</v>
@@ -16680,7 +16677,7 @@
         <v>2</v>
       </c>
       <c r="F471" s="3" t="n">
-        <v>8205</v>
+        <v>5950</v>
       </c>
       <c r="G471" s="3" t="n">
         <v>0</v>
@@ -16697,7 +16694,7 @@
     </row>
     <row r="472" customHeight="1" ht="15" spans="1:10">
       <c r="A472" s="1" t="n">
-        <v>804206</v>
+        <v>804207</v>
       </c>
       <c r="B472" s="1" t="s">
         <v>479</v>
@@ -16712,7 +16709,7 @@
         <v>2</v>
       </c>
       <c r="F472" s="3" t="n">
-        <v>5950</v>
+        <v>6271</v>
       </c>
       <c r="G472" s="3" t="n">
         <v>0</v>
@@ -16729,7 +16726,7 @@
     </row>
     <row r="473" customHeight="1" ht="15" spans="1:10">
       <c r="A473" s="1" t="n">
-        <v>804207</v>
+        <v>813274</v>
       </c>
       <c r="B473" s="1" t="s">
         <v>480</v>
@@ -16744,7 +16741,7 @@
         <v>2</v>
       </c>
       <c r="F473" s="3" t="n">
-        <v>6271</v>
+        <v>2519</v>
       </c>
       <c r="G473" s="3" t="n">
         <v>0</v>
@@ -16761,7 +16758,7 @@
     </row>
     <row r="474" customHeight="1" ht="15" spans="1:10">
       <c r="A474" s="1" t="n">
-        <v>813274</v>
+        <v>804497</v>
       </c>
       <c r="B474" s="1" t="s">
         <v>481</v>
@@ -16776,7 +16773,7 @@
         <v>2</v>
       </c>
       <c r="F474" s="3" t="n">
-        <v>2519</v>
+        <v>25431</v>
       </c>
       <c r="G474" s="3" t="n">
         <v>0</v>
@@ -16793,7 +16790,7 @@
     </row>
     <row r="475" customHeight="1" ht="15" spans="1:10">
       <c r="A475" s="1" t="n">
-        <v>804497</v>
+        <v>804496</v>
       </c>
       <c r="B475" s="1" t="s">
         <v>482</v>
@@ -16808,7 +16805,7 @@
         <v>2</v>
       </c>
       <c r="F475" s="3" t="n">
-        <v>25431</v>
+        <v>11126</v>
       </c>
       <c r="G475" s="3" t="n">
         <v>0</v>
@@ -16825,7 +16822,7 @@
     </row>
     <row r="476" customHeight="1" ht="15" spans="1:10">
       <c r="A476" s="1" t="n">
-        <v>804496</v>
+        <v>804129</v>
       </c>
       <c r="B476" s="1" t="s">
         <v>483</v>
@@ -16840,7 +16837,7 @@
         <v>2</v>
       </c>
       <c r="F476" s="3" t="n">
-        <v>11126</v>
+        <v>8932</v>
       </c>
       <c r="G476" s="3" t="n">
         <v>0</v>
@@ -16857,7 +16854,7 @@
     </row>
     <row r="477" customHeight="1" ht="15" spans="1:10">
       <c r="A477" s="1" t="n">
-        <v>804129</v>
+        <v>804458</v>
       </c>
       <c r="B477" s="1" t="s">
         <v>484</v>
@@ -16872,7 +16869,7 @@
         <v>2</v>
       </c>
       <c r="F477" s="3" t="n">
-        <v>8932</v>
+        <v>4249</v>
       </c>
       <c r="G477" s="3" t="n">
         <v>0</v>
@@ -16889,7 +16886,7 @@
     </row>
     <row r="478" customHeight="1" ht="15" spans="1:10">
       <c r="A478" s="1" t="n">
-        <v>804458</v>
+        <v>804563</v>
       </c>
       <c r="B478" s="1" t="s">
         <v>485</v>
@@ -16904,7 +16901,7 @@
         <v>2</v>
       </c>
       <c r="F478" s="3" t="n">
-        <v>4249</v>
+        <v>1080</v>
       </c>
       <c r="G478" s="3" t="n">
         <v>0</v>
@@ -16921,7 +16918,7 @@
     </row>
     <row r="479" customHeight="1" ht="15" spans="1:10">
       <c r="A479" s="1" t="n">
-        <v>804563</v>
+        <v>804525</v>
       </c>
       <c r="B479" s="1" t="s">
         <v>486</v>
@@ -16936,7 +16933,7 @@
         <v>2</v>
       </c>
       <c r="F479" s="3" t="n">
-        <v>1080</v>
+        <v>12345</v>
       </c>
       <c r="G479" s="3" t="n">
         <v>0</v>
@@ -16953,7 +16950,7 @@
     </row>
     <row r="480" customHeight="1" ht="15" spans="1:10">
       <c r="A480" s="1" t="n">
-        <v>804525</v>
+        <v>804526</v>
       </c>
       <c r="B480" s="1" t="s">
         <v>487</v>
@@ -16968,7 +16965,7 @@
         <v>2</v>
       </c>
       <c r="F480" s="3" t="n">
-        <v>12345</v>
+        <v>13894</v>
       </c>
       <c r="G480" s="3" t="n">
         <v>0</v>
@@ -16985,7 +16982,7 @@
     </row>
     <row r="481" customHeight="1" ht="15" spans="1:10">
       <c r="A481" s="1" t="n">
-        <v>804526</v>
+        <v>813039</v>
       </c>
       <c r="B481" s="1" t="s">
         <v>488</v>
@@ -17000,7 +16997,7 @@
         <v>2</v>
       </c>
       <c r="F481" s="3" t="n">
-        <v>13894</v>
+        <v>7768</v>
       </c>
       <c r="G481" s="3" t="n">
         <v>0</v>
@@ -17017,7 +17014,7 @@
     </row>
     <row r="482" customHeight="1" ht="15" spans="1:10">
       <c r="A482" s="1" t="n">
-        <v>813039</v>
+        <v>813025</v>
       </c>
       <c r="B482" s="1" t="s">
         <v>489</v>
@@ -17032,7 +17029,7 @@
         <v>2</v>
       </c>
       <c r="F482" s="3" t="n">
-        <v>7768</v>
+        <v>17810</v>
       </c>
       <c r="G482" s="3" t="n">
         <v>0</v>
@@ -17049,7 +17046,7 @@
     </row>
     <row r="483" customHeight="1" ht="15" spans="1:10">
       <c r="A483" s="1" t="n">
-        <v>813025</v>
+        <v>804267</v>
       </c>
       <c r="B483" s="1" t="s">
         <v>490</v>
@@ -17064,7 +17061,7 @@
         <v>2</v>
       </c>
       <c r="F483" s="3" t="n">
-        <v>17810</v>
+        <v>1478</v>
       </c>
       <c r="G483" s="3" t="n">
         <v>0</v>
@@ -17081,7 +17078,7 @@
     </row>
     <row r="484" customHeight="1" ht="15" spans="1:10">
       <c r="A484" s="1" t="n">
-        <v>804267</v>
+        <v>804381</v>
       </c>
       <c r="B484" s="1" t="s">
         <v>491</v>
@@ -17096,7 +17093,7 @@
         <v>2</v>
       </c>
       <c r="F484" s="3" t="n">
-        <v>1478</v>
+        <v>2928</v>
       </c>
       <c r="G484" s="3" t="n">
         <v>0</v>
@@ -17113,7 +17110,7 @@
     </row>
     <row r="485" customHeight="1" ht="15" spans="1:10">
       <c r="A485" s="1" t="n">
-        <v>804381</v>
+        <v>804315</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>492</v>
@@ -17128,7 +17125,7 @@
         <v>2</v>
       </c>
       <c r="F485" s="3" t="n">
-        <v>2928</v>
+        <v>10045</v>
       </c>
       <c r="G485" s="3" t="n">
         <v>0</v>
@@ -17145,7 +17142,7 @@
     </row>
     <row r="486" customHeight="1" ht="15" spans="1:10">
       <c r="A486" s="1" t="n">
-        <v>804315</v>
+        <v>804045</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>493</v>
@@ -17160,7 +17157,7 @@
         <v>2</v>
       </c>
       <c r="F486" s="3" t="n">
-        <v>10045</v>
+        <v>69436</v>
       </c>
       <c r="G486" s="3" t="n">
         <v>0</v>
@@ -17177,7 +17174,7 @@
     </row>
     <row r="487" customHeight="1" ht="15" spans="1:10">
       <c r="A487" s="1" t="n">
-        <v>804045</v>
+        <v>804078</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>494</v>
@@ -17192,7 +17189,7 @@
         <v>2</v>
       </c>
       <c r="F487" s="3" t="n">
-        <v>69436</v>
+        <v>14989</v>
       </c>
       <c r="G487" s="3" t="n">
         <v>0</v>
@@ -17209,7 +17206,7 @@
     </row>
     <row r="488" customHeight="1" ht="15" spans="1:10">
       <c r="A488" s="1" t="n">
-        <v>804078</v>
+        <v>804044</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>495</v>
@@ -17224,7 +17221,7 @@
         <v>2</v>
       </c>
       <c r="F488" s="3" t="n">
-        <v>14989</v>
+        <v>7023</v>
       </c>
       <c r="G488" s="3" t="n">
         <v>0</v>
@@ -17241,7 +17238,7 @@
     </row>
     <row r="489" customHeight="1" ht="15" spans="1:10">
       <c r="A489" s="1" t="n">
-        <v>804044</v>
+        <v>804079</v>
       </c>
       <c r="B489" s="1" t="s">
         <v>496</v>
@@ -17256,7 +17253,7 @@
         <v>2</v>
       </c>
       <c r="F489" s="3" t="n">
-        <v>7023</v>
+        <v>11838</v>
       </c>
       <c r="G489" s="3" t="n">
         <v>0</v>
@@ -17273,7 +17270,7 @@
     </row>
     <row r="490" customHeight="1" ht="15" spans="1:10">
       <c r="A490" s="1" t="n">
-        <v>804079</v>
+        <v>804314</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>497</v>
@@ -17288,7 +17285,7 @@
         <v>2</v>
       </c>
       <c r="F490" s="3" t="n">
-        <v>11838</v>
+        <v>11360</v>
       </c>
       <c r="G490" s="3" t="n">
         <v>0</v>
@@ -17300,38 +17297,6 @@
         <v>0</v>
       </c>
       <c r="J490" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="491" customHeight="1" ht="15" spans="1:10">
-      <c r="A491" s="1" t="n">
-        <v>804314</v>
-      </c>
-      <c r="B491" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="C491" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D491" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E491" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F491" s="3" t="n">
-        <v>11360</v>
-      </c>
-      <c r="G491" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H491" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I491" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J491" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/temp/diversos/Plastico.xlsx
+++ b/temp/diversos/Plastico.xlsx
@@ -2757,7 +2757,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>6121</v>
+        <v>2074</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
@@ -3525,7 +3525,7 @@
         <v>2</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>5804</v>
+        <v>8016</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>0</v>
@@ -5797,7 +5797,7 @@
         <v>2</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>9120</v>
+        <v>8400</v>
       </c>
       <c r="G131" s="3" t="n">
         <v>0</v>
@@ -6277,7 +6277,7 @@
         <v>2</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>391</v>
+        <v>1293</v>
       </c>
       <c r="G146" s="3" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
         <v>2</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>286</v>
+        <v>1187</v>
       </c>
       <c r="G151" s="3" t="n">
         <v>0</v>
@@ -6949,7 +6949,7 @@
         <v>2</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>10204</v>
+        <v>6734</v>
       </c>
       <c r="G167" s="3" t="n">
         <v>0</v>
@@ -8677,7 +8677,7 @@
         <v>2</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>1414</v>
+        <v>1282</v>
       </c>
       <c r="G221" s="3" t="n">
         <v>0</v>
@@ -9829,7 +9829,7 @@
         <v>2</v>
       </c>
       <c r="F257" s="3" t="n">
-        <v>5280</v>
+        <v>5230</v>
       </c>
       <c r="G257" s="3" t="n">
         <v>0</v>
@@ -10757,7 +10757,7 @@
         <v>2</v>
       </c>
       <c r="F286" s="3" t="n">
-        <v>2455</v>
+        <v>1847</v>
       </c>
       <c r="G286" s="3" t="n">
         <v>0</v>
@@ -11493,7 +11493,7 @@
         <v>2</v>
       </c>
       <c r="F309" s="3" t="n">
-        <v>16567</v>
+        <v>16157</v>
       </c>
       <c r="G309" s="3" t="n">
         <v>0</v>
@@ -12197,7 +12197,7 @@
         <v>2</v>
       </c>
       <c r="F331" s="3" t="n">
-        <v>3000</v>
+        <v>2750</v>
       </c>
       <c r="G331" s="3" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>2</v>
       </c>
       <c r="F352" s="3" t="n">
-        <v>4579</v>
+        <v>3995</v>
       </c>
       <c r="G352" s="3" t="n">
         <v>0</v>
@@ -13093,7 +13093,7 @@
         <v>2</v>
       </c>
       <c r="F359" s="3" t="n">
-        <v>12600</v>
+        <v>12150</v>
       </c>
       <c r="G359" s="3" t="n">
         <v>0</v>
@@ -13989,7 +13989,7 @@
         <v>2</v>
       </c>
       <c r="F387" s="3" t="n">
-        <v>19706</v>
+        <v>19160</v>
       </c>
       <c r="G387" s="3" t="n">
         <v>0</v>
@@ -14245,7 +14245,7 @@
         <v>2</v>
       </c>
       <c r="F395" s="3" t="n">
-        <v>14377</v>
+        <v>12612</v>
       </c>
       <c r="G395" s="3" t="n">
         <v>0</v>
@@ -14277,7 +14277,7 @@
         <v>2</v>
       </c>
       <c r="F396" s="3" t="n">
-        <v>2960</v>
+        <v>2360</v>
       </c>
       <c r="G396" s="3" t="n">
         <v>0</v>
@@ -14309,7 +14309,7 @@
         <v>2</v>
       </c>
       <c r="F397" s="3" t="n">
-        <v>11331</v>
+        <v>10681</v>
       </c>
       <c r="G397" s="3" t="n">
         <v>0</v>
@@ -14693,7 +14693,7 @@
         <v>2</v>
       </c>
       <c r="F409" s="3" t="n">
-        <v>20318</v>
+        <v>18083</v>
       </c>
       <c r="G409" s="3" t="n">
         <v>0</v>
@@ -14917,7 +14917,7 @@
         <v>2</v>
       </c>
       <c r="F416" s="3" t="n">
-        <v>498</v>
+        <v>98</v>
       </c>
       <c r="G416" s="3" t="n">
         <v>0</v>
@@ -16005,7 +16005,7 @@
         <v>2</v>
       </c>
       <c r="F450" s="3" t="n">
-        <v>2611</v>
+        <v>1047</v>
       </c>
       <c r="G450" s="3" t="n">
         <v>0</v>
